--- a/alcohol_filtrado.xlsx
+++ b/alcohol_filtrado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F247"/>
+  <dimension ref="A1:G247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,11 @@
           <t>rango</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>temporada</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -469,6 +474,11 @@
       <c r="F2" t="n">
         <v>2.59</v>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -491,6 +501,11 @@
       <c r="F3" t="n">
         <v>2.57</v>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -513,6 +528,11 @@
       <c r="F4" t="n">
         <v>2.6</v>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -535,6 +555,11 @@
       <c r="F5" t="n">
         <v>2.65</v>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -557,6 +582,11 @@
       <c r="F6" t="n">
         <v>2.5</v>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -579,6 +609,11 @@
       <c r="F7" t="n">
         <v>2.79</v>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -601,6 +636,11 @@
       <c r="F8" t="n">
         <v>3.91</v>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -623,6 +663,11 @@
       <c r="F9" t="n">
         <v>3.77</v>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -645,6 +690,11 @@
       <c r="F10" t="n">
         <v>3.74</v>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -667,6 +717,11 @@
       <c r="F11" t="n">
         <v>3.42</v>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -689,6 +744,11 @@
       <c r="F12" t="n">
         <v>3.26</v>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -711,6 +771,11 @@
       <c r="F13" t="n">
         <v>3.41</v>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -733,6 +798,11 @@
       <c r="F14" t="n">
         <v>3.82</v>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -755,6 +825,11 @@
       <c r="F15" t="n">
         <v>3.98</v>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -777,6 +852,11 @@
       <c r="F16" t="n">
         <v>3.93</v>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -799,6 +879,11 @@
       <c r="F17" t="n">
         <v>3.97</v>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -821,6 +906,11 @@
       <c r="F18" t="n">
         <v>3.51</v>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -843,6 +933,11 @@
       <c r="F19" t="n">
         <v>3.49</v>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -865,6 +960,11 @@
       <c r="F20" t="n">
         <v>3.33</v>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -887,6 +987,11 @@
       <c r="F21" t="n">
         <v>3.29</v>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -909,6 +1014,11 @@
       <c r="F22" t="n">
         <v>3.38</v>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -931,6 +1041,11 @@
       <c r="F23" t="n">
         <v>3.43</v>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -953,6 +1068,11 @@
       <c r="F24" t="n">
         <v>3.66</v>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -975,6 +1095,11 @@
       <c r="F25" t="n">
         <v>3.42</v>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -997,6 +1122,11 @@
       <c r="F26" t="n">
         <v>3.2</v>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1019,6 +1149,11 @@
       <c r="F27" t="n">
         <v>3.1</v>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1041,6 +1176,11 @@
       <c r="F28" t="n">
         <v>3.21</v>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1063,6 +1203,11 @@
       <c r="F29" t="n">
         <v>3.34</v>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1085,6 +1230,11 @@
       <c r="F30" t="n">
         <v>3.3</v>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1107,6 +1257,11 @@
       <c r="F31" t="n">
         <v>3.07</v>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1129,6 +1284,11 @@
       <c r="F32" t="n">
         <v>2.91</v>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1151,6 +1311,11 @@
       <c r="F33" t="n">
         <v>2.85</v>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1173,6 +1338,11 @@
       <c r="F34" t="n">
         <v>2.64</v>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1195,6 +1365,11 @@
       <c r="F35" t="n">
         <v>2.68</v>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1217,6 +1392,11 @@
       <c r="F36" t="n">
         <v>2.77</v>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1239,6 +1419,11 @@
       <c r="F37" t="n">
         <v>2.91</v>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1261,6 +1446,11 @@
       <c r="F38" t="n">
         <v>3.59</v>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1283,6 +1473,11 @@
       <c r="F39" t="n">
         <v>3.61</v>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1305,6 +1500,11 @@
       <c r="F40" t="n">
         <v>3.55</v>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1327,6 +1527,11 @@
       <c r="F41" t="n">
         <v>3.59</v>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1349,6 +1554,11 @@
       <c r="F42" t="n">
         <v>3.81</v>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1371,6 +1581,11 @@
       <c r="F43" t="n">
         <v>3.62</v>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1393,6 +1608,11 @@
       <c r="F44" t="n">
         <v>3.82</v>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1415,6 +1635,11 @@
       <c r="F45" t="n">
         <v>3.59</v>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1437,6 +1662,11 @@
       <c r="F46" t="n">
         <v>3.61</v>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1459,6 +1689,11 @@
       <c r="F47" t="n">
         <v>3.69</v>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1481,6 +1716,11 @@
       <c r="F48" t="n">
         <v>3.67</v>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1503,6 +1743,11 @@
       <c r="F49" t="n">
         <v>3.65</v>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1525,6 +1770,11 @@
       <c r="F50" t="n">
         <v>2.89</v>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1547,6 +1797,11 @@
       <c r="F51" t="n">
         <v>3.17</v>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1569,6 +1824,11 @@
       <c r="F52" t="n">
         <v>3.02</v>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1591,6 +1851,11 @@
       <c r="F53" t="n">
         <v>2.9</v>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1613,6 +1878,11 @@
       <c r="F54" t="n">
         <v>2.68</v>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1635,6 +1905,11 @@
       <c r="F55" t="n">
         <v>2.55</v>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1657,6 +1932,11 @@
       <c r="F56" t="n">
         <v>3.85</v>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1679,6 +1959,11 @@
       <c r="F57" t="n">
         <v>3.78</v>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1701,6 +1986,11 @@
       <c r="F58" t="n">
         <v>3.72</v>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1723,6 +2013,11 @@
       <c r="F59" t="n">
         <v>3.89</v>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1745,6 +2040,11 @@
       <c r="F60" t="n">
         <v>3.6</v>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1767,6 +2067,11 @@
       <c r="F61" t="n">
         <v>3.77</v>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1789,6 +2094,11 @@
       <c r="F62" t="n">
         <v>3.53</v>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1811,6 +2121,11 @@
       <c r="F63" t="n">
         <v>3.6</v>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1833,6 +2148,11 @@
       <c r="F64" t="n">
         <v>3.45</v>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1855,6 +2175,11 @@
       <c r="F65" t="n">
         <v>3.32</v>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1877,6 +2202,11 @@
       <c r="F66" t="n">
         <v>3.35</v>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1899,6 +2229,11 @@
       <c r="F67" t="n">
         <v>3.4</v>
       </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1921,6 +2256,11 @@
       <c r="F68" t="n">
         <v>5.94</v>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1943,6 +2283,11 @@
       <c r="F69" t="n">
         <v>5.44</v>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1965,6 +2310,11 @@
       <c r="F70" t="n">
         <v>5.1</v>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1987,6 +2337,11 @@
       <c r="F71" t="n">
         <v>4.64</v>
       </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2009,6 +2364,11 @@
       <c r="F72" t="n">
         <v>4.82</v>
       </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2031,6 +2391,11 @@
       <c r="F73" t="n">
         <v>4.72</v>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2053,6 +2418,11 @@
       <c r="F74" t="n">
         <v>3.81</v>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2075,6 +2445,11 @@
       <c r="F75" t="n">
         <v>3.9</v>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2097,6 +2472,11 @@
       <c r="F76" t="n">
         <v>3.79</v>
       </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2119,6 +2499,11 @@
       <c r="F77" t="n">
         <v>3.86</v>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2141,6 +2526,11 @@
       <c r="F78" t="n">
         <v>3.6</v>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2163,6 +2553,11 @@
       <c r="F79" t="n">
         <v>3.4</v>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2185,6 +2580,11 @@
       <c r="F80" t="n">
         <v>3.59</v>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2207,6 +2607,11 @@
       <c r="F81" t="n">
         <v>3.77</v>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2229,6 +2634,11 @@
       <c r="F82" t="n">
         <v>3.77</v>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2251,6 +2661,11 @@
       <c r="F83" t="n">
         <v>3.61</v>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2273,6 +2688,11 @@
       <c r="F84" t="n">
         <v>3.64</v>
       </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2295,6 +2715,11 @@
       <c r="F85" t="n">
         <v>3.59</v>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2317,6 +2742,11 @@
       <c r="F86" t="n">
         <v>3.56</v>
       </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2339,6 +2769,11 @@
       <c r="F87" t="n">
         <v>3.39</v>
       </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2361,6 +2796,11 @@
       <c r="F88" t="n">
         <v>3.37</v>
       </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2383,6 +2823,11 @@
       <c r="F89" t="n">
         <v>3.55</v>
       </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2405,6 +2850,11 @@
       <c r="F90" t="n">
         <v>3.6</v>
       </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2427,6 +2877,11 @@
       <c r="F91" t="n">
         <v>3.47</v>
       </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2449,6 +2904,11 @@
       <c r="F92" t="n">
         <v>3.06</v>
       </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2471,6 +2931,11 @@
       <c r="F93" t="n">
         <v>3.04</v>
       </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2493,6 +2958,11 @@
       <c r="F94" t="n">
         <v>2.92</v>
       </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2515,6 +2985,11 @@
       <c r="F95" t="n">
         <v>3.04</v>
       </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2537,6 +3012,11 @@
       <c r="F96" t="n">
         <v>2.88</v>
       </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2559,6 +3039,11 @@
       <c r="F97" t="n">
         <v>2.9</v>
       </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2581,6 +3066,11 @@
       <c r="F98" t="n">
         <v>3.5</v>
       </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2603,6 +3093,11 @@
       <c r="F99" t="n">
         <v>3.67</v>
       </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2625,6 +3120,11 @@
       <c r="F100" t="n">
         <v>3.58</v>
       </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2647,6 +3147,11 @@
       <c r="F101" t="n">
         <v>3.64</v>
       </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2669,6 +3174,11 @@
       <c r="F102" t="n">
         <v>3.58</v>
       </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2691,6 +3201,11 @@
       <c r="F103" t="n">
         <v>3.41</v>
       </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2713,6 +3228,11 @@
       <c r="F104" t="n">
         <v>3.39</v>
       </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2735,6 +3255,11 @@
       <c r="F105" t="n">
         <v>3.32</v>
       </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2757,6 +3282,11 @@
       <c r="F106" t="n">
         <v>3.45</v>
       </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2779,6 +3309,11 @@
       <c r="F107" t="n">
         <v>3.29</v>
       </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2801,6 +3336,11 @@
       <c r="F108" t="n">
         <v>3.17</v>
       </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2823,6 +3363,11 @@
       <c r="F109" t="n">
         <v>3.03</v>
       </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2845,6 +3390,11 @@
       <c r="F110" t="n">
         <v>3.47</v>
       </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2867,6 +3417,11 @@
       <c r="F111" t="n">
         <v>3.61</v>
       </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2889,6 +3444,11 @@
       <c r="F112" t="n">
         <v>3.47</v>
       </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2911,6 +3471,11 @@
       <c r="F113" t="n">
         <v>3.64</v>
       </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2933,6 +3498,11 @@
       <c r="F114" t="n">
         <v>3.49</v>
       </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2955,6 +3525,11 @@
       <c r="F115" t="n">
         <v>3.47</v>
       </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2977,6 +3552,11 @@
       <c r="F116" t="n">
         <v>2.7</v>
       </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2999,6 +3579,11 @@
       <c r="F117" t="n">
         <v>2.68</v>
       </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3021,6 +3606,11 @@
       <c r="F118" t="n">
         <v>2.77</v>
       </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3043,6 +3633,11 @@
       <c r="F119" t="n">
         <v>2.96</v>
       </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3065,6 +3660,11 @@
       <c r="F120" t="n">
         <v>3.04</v>
       </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3087,6 +3687,11 @@
       <c r="F121" t="n">
         <v>3.03</v>
       </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3109,6 +3714,11 @@
       <c r="F122" t="n">
         <v>5.09</v>
       </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3131,6 +3741,11 @@
       <c r="F123" t="n">
         <v>5.1</v>
       </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3153,6 +3768,11 @@
       <c r="F124" t="n">
         <v>5.2</v>
       </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3175,6 +3795,11 @@
       <c r="F125" t="n">
         <v>4.88</v>
       </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3197,6 +3822,11 @@
       <c r="F126" t="n">
         <v>4.85</v>
       </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3219,6 +3849,11 @@
       <c r="F127" t="n">
         <v>4.67</v>
       </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3241,6 +3876,11 @@
       <c r="F128" t="n">
         <v>4.02</v>
       </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3263,6 +3903,11 @@
       <c r="F129" t="n">
         <v>3.79</v>
       </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3285,6 +3930,11 @@
       <c r="F130" t="n">
         <v>3.64</v>
       </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3307,6 +3957,11 @@
       <c r="F131" t="n">
         <v>3.59</v>
       </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3329,6 +3984,11 @@
       <c r="F132" t="n">
         <v>3.65</v>
       </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3351,6 +4011,11 @@
       <c r="F133" t="n">
         <v>3.51</v>
       </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3373,6 +4038,11 @@
       <c r="F134" t="n">
         <v>3.6</v>
       </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3395,6 +4065,11 @@
       <c r="F135" t="n">
         <v>3.6</v>
       </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3417,6 +4092,11 @@
       <c r="F136" t="n">
         <v>3.7</v>
       </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3439,6 +4119,11 @@
       <c r="F137" t="n">
         <v>3.58</v>
       </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3461,6 +4146,11 @@
       <c r="F138" t="n">
         <v>3.61</v>
       </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3483,6 +4173,11 @@
       <c r="F139" t="n">
         <v>3.53</v>
       </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3505,6 +4200,11 @@
       <c r="F140" t="n">
         <v>3.25</v>
       </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3527,6 +4227,11 @@
       <c r="F141" t="n">
         <v>3.21</v>
       </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3549,6 +4254,11 @@
       <c r="F142" t="n">
         <v>3.34</v>
       </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3571,6 +4281,11 @@
       <c r="F143" t="n">
         <v>3.11</v>
       </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3593,6 +4308,11 @@
       <c r="F144" t="n">
         <v>2.93</v>
       </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3615,6 +4335,11 @@
       <c r="F145" t="n">
         <v>2.79</v>
       </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3637,6 +4362,11 @@
       <c r="F146" t="n">
         <v>4.26</v>
       </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3659,6 +4389,11 @@
       <c r="F147" t="n">
         <v>4.09</v>
       </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3681,6 +4416,11 @@
       <c r="F148" t="n">
         <v>4.15</v>
       </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3703,6 +4443,11 @@
       <c r="F149" t="n">
         <v>4.16</v>
       </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3725,6 +4470,11 @@
       <c r="F150" t="n">
         <v>4.15</v>
       </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3747,6 +4497,11 @@
       <c r="F151" t="n">
         <v>4.19</v>
       </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3769,6 +4524,11 @@
       <c r="F152" t="n">
         <v>3.45</v>
       </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3791,6 +4551,11 @@
       <c r="F153" t="n">
         <v>3.55</v>
       </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3813,6 +4578,11 @@
       <c r="F154" t="n">
         <v>3.43</v>
       </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3835,6 +4605,11 @@
       <c r="F155" t="n">
         <v>3.48</v>
       </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3857,6 +4632,11 @@
       <c r="F156" t="n">
         <v>3.24</v>
       </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3879,6 +4659,11 @@
       <c r="F157" t="n">
         <v>3.18</v>
       </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3901,6 +4686,11 @@
       <c r="F158" t="n">
         <v>3.14</v>
       </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3923,6 +4713,11 @@
       <c r="F159" t="n">
         <v>2.98</v>
       </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3945,6 +4740,11 @@
       <c r="F160" t="n">
         <v>3.24</v>
       </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3967,6 +4767,11 @@
       <c r="F161" t="n">
         <v>3.13</v>
       </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3989,6 +4794,11 @@
       <c r="F162" t="n">
         <v>2.99</v>
       </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4011,6 +4821,11 @@
       <c r="F163" t="n">
         <v>3.04</v>
       </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4033,6 +4848,11 @@
       <c r="F164" t="n">
         <v>2.77</v>
       </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4055,6 +4875,11 @@
       <c r="F165" t="n">
         <v>2.7</v>
       </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -4077,6 +4902,11 @@
       <c r="F166" t="n">
         <v>2.52</v>
       </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -4099,6 +4929,11 @@
       <c r="F167" t="n">
         <v>2.56</v>
       </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4121,6 +4956,11 @@
       <c r="F168" t="n">
         <v>2.62</v>
       </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4143,6 +4983,11 @@
       <c r="F169" t="n">
         <v>2.67</v>
       </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -4165,6 +5010,11 @@
       <c r="F170" t="n">
         <v>2.73</v>
       </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -4187,6 +5037,11 @@
       <c r="F171" t="n">
         <v>2.7</v>
       </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -4209,6 +5064,11 @@
       <c r="F172" t="n">
         <v>2.85</v>
       </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -4231,6 +5091,11 @@
       <c r="F173" t="n">
         <v>2.71</v>
       </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -4253,6 +5118,11 @@
       <c r="F174" t="n">
         <v>2.76</v>
       </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -4275,6 +5145,11 @@
       <c r="F175" t="n">
         <v>2.83</v>
       </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -4297,6 +5172,11 @@
       <c r="F176" t="n">
         <v>3.64</v>
       </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -4319,6 +5199,11 @@
       <c r="F177" t="n">
         <v>3.83</v>
       </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -4341,6 +5226,11 @@
       <c r="F178" t="n">
         <v>3.86</v>
       </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -4363,6 +5253,11 @@
       <c r="F179" t="n">
         <v>3.86</v>
       </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -4385,6 +5280,11 @@
       <c r="F180" t="n">
         <v>3.71</v>
       </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -4407,6 +5307,11 @@
       <c r="F181" t="n">
         <v>3.72</v>
       </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -4429,6 +5334,11 @@
       <c r="F182" t="n">
         <v>3.47</v>
       </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -4451,6 +5361,11 @@
       <c r="F183" t="n">
         <v>3.64</v>
       </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -4473,6 +5388,11 @@
       <c r="F184" t="n">
         <v>3.58</v>
       </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -4495,6 +5415,11 @@
       <c r="F185" t="n">
         <v>3.29</v>
       </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -4517,6 +5442,11 @@
       <c r="F186" t="n">
         <v>3.42</v>
       </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -4539,6 +5469,11 @@
       <c r="F187" t="n">
         <v>3.52</v>
       </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -4561,6 +5496,11 @@
       <c r="F188" t="n">
         <v>5.18</v>
       </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -4583,6 +5523,11 @@
       <c r="F189" t="n">
         <v>5.36</v>
       </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -4605,6 +5550,11 @@
       <c r="F190" t="n">
         <v>5.09</v>
       </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -4627,6 +5577,11 @@
       <c r="F191" t="n">
         <v>5.34</v>
       </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -4649,6 +5604,11 @@
       <c r="F192" t="n">
         <v>5.24</v>
       </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -4671,6 +5631,11 @@
       <c r="F193" t="n">
         <v>5.23</v>
       </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -4693,6 +5658,11 @@
       <c r="F194" t="n">
         <v>4.04</v>
       </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -4715,6 +5685,11 @@
       <c r="F195" t="n">
         <v>3.95</v>
       </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -4737,6 +5712,11 @@
       <c r="F196" t="n">
         <v>3.93</v>
       </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -4759,6 +5739,11 @@
       <c r="F197" t="n">
         <v>3.93</v>
       </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -4781,6 +5766,11 @@
       <c r="F198" t="n">
         <v>3.96</v>
       </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -4803,6 +5793,11 @@
       <c r="F199" t="n">
         <v>3.97</v>
       </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -4825,6 +5820,11 @@
       <c r="F200" t="n">
         <v>3.38</v>
       </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -4847,6 +5847,11 @@
       <c r="F201" t="n">
         <v>3.29</v>
       </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -4869,6 +5874,11 @@
       <c r="F202" t="n">
         <v>3.22</v>
       </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -4891,6 +5901,11 @@
       <c r="F203" t="n">
         <v>3.24</v>
       </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -4913,6 +5928,11 @@
       <c r="F204" t="n">
         <v>3.37</v>
       </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -4935,6 +5955,11 @@
       <c r="F205" t="n">
         <v>3.36</v>
       </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -4957,6 +5982,11 @@
       <c r="F206" t="n">
         <v>3.4</v>
       </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -4979,6 +6009,11 @@
       <c r="F207" t="n">
         <v>3.59</v>
       </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -5001,6 +6036,11 @@
       <c r="F208" t="n">
         <v>3.42</v>
       </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -5023,6 +6063,11 @@
       <c r="F209" t="n">
         <v>3.43</v>
       </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -5045,6 +6090,11 @@
       <c r="F210" t="n">
         <v>3.45</v>
       </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -5067,6 +6117,11 @@
       <c r="F211" t="n">
         <v>3.53</v>
       </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -5089,6 +6144,11 @@
       <c r="F212" t="n">
         <v>3.6</v>
       </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -5111,6 +6171,11 @@
       <c r="F213" t="n">
         <v>3.48</v>
       </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -5133,6 +6198,11 @@
       <c r="F214" t="n">
         <v>3.62</v>
       </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -5155,6 +6225,11 @@
       <c r="F215" t="n">
         <v>3.5</v>
       </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -5177,6 +6252,11 @@
       <c r="F216" t="n">
         <v>3.67</v>
       </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -5199,6 +6279,11 @@
       <c r="F217" t="n">
         <v>3.51</v>
       </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -5221,6 +6306,11 @@
       <c r="F218" t="n">
         <v>3.47</v>
       </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -5243,6 +6333,11 @@
       <c r="F219" t="n">
         <v>3.51</v>
       </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -5265,6 +6360,11 @@
       <c r="F220" t="n">
         <v>3.71</v>
       </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -5287,6 +6387,11 @@
       <c r="F221" t="n">
         <v>3.5</v>
       </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -5309,6 +6414,11 @@
       <c r="F222" t="n">
         <v>3.44</v>
       </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -5331,6 +6441,11 @@
       <c r="F223" t="n">
         <v>3.42</v>
       </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -5353,6 +6468,11 @@
       <c r="F224" t="n">
         <v>3.76</v>
       </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -5375,6 +6495,11 @@
       <c r="F225" t="n">
         <v>3.75</v>
       </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -5397,6 +6522,11 @@
       <c r="F226" t="n">
         <v>3.58</v>
       </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -5419,6 +6549,11 @@
       <c r="F227" t="n">
         <v>3.44</v>
       </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -5441,6 +6576,11 @@
       <c r="F228" t="n">
         <v>3.46</v>
       </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -5463,6 +6603,11 @@
       <c r="F229" t="n">
         <v>3.61</v>
       </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -5485,6 +6630,11 @@
       <c r="F230" t="n">
         <v>3.38</v>
       </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -5507,6 +6657,11 @@
       <c r="F231" t="n">
         <v>3.25</v>
       </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -5529,6 +6684,11 @@
       <c r="F232" t="n">
         <v>3.32</v>
       </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -5551,6 +6711,11 @@
       <c r="F233" t="n">
         <v>3.18</v>
       </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -5573,6 +6738,11 @@
       <c r="F234" t="n">
         <v>3.11</v>
       </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -5595,6 +6765,11 @@
       <c r="F235" t="n">
         <v>3.19</v>
       </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -5617,6 +6792,11 @@
       <c r="F236" t="n">
         <v>3.59</v>
       </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -5639,6 +6819,11 @@
       <c r="F237" t="n">
         <v>3.62</v>
       </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -5661,6 +6846,11 @@
       <c r="F238" t="n">
         <v>3.76</v>
       </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -5683,6 +6873,11 @@
       <c r="F239" t="n">
         <v>3.62</v>
       </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -5705,6 +6900,11 @@
       <c r="F240" t="n">
         <v>3.54</v>
       </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -5727,6 +6927,11 @@
       <c r="F241" t="n">
         <v>3.42</v>
       </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -5749,6 +6954,11 @@
       <c r="F242" t="n">
         <v>3.61</v>
       </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -5771,6 +6981,11 @@
       <c r="F243" t="n">
         <v>3.37</v>
       </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -5793,6 +7008,11 @@
       <c r="F244" t="n">
         <v>3.41</v>
       </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -5815,6 +7035,11 @@
       <c r="F245" t="n">
         <v>3.33</v>
       </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -5837,6 +7062,11 @@
       <c r="F246" t="n">
         <v>3.56</v>
       </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -5858,6 +7088,11 @@
       </c>
       <c r="F247" t="n">
         <v>3.36</v>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/alcohol_filtrado.xlsx
+++ b/alcohol_filtrado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G247"/>
+  <dimension ref="A1:G316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C7" t="n">
         <v>4.97</v>
@@ -611,34 +611,34 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Andorra</t>
+          <t>Albania</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="C8" t="n">
-        <v>11.9</v>
+        <v>4.97</v>
       </c>
       <c r="D8" t="n">
-        <v>9.92</v>
+        <v>3.56</v>
       </c>
       <c r="E8" t="n">
-        <v>13.83</v>
+        <v>6.35</v>
       </c>
       <c r="F8" t="n">
-        <v>3.91</v>
+        <v>2.79</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Después</t>
         </is>
       </c>
     </row>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="C9" t="n">
-        <v>11.83</v>
+        <v>11.9</v>
       </c>
       <c r="D9" t="n">
-        <v>9.970000000000001</v>
+        <v>9.92</v>
       </c>
       <c r="E9" t="n">
-        <v>13.74</v>
+        <v>13.83</v>
       </c>
       <c r="F9" t="n">
-        <v>3.77</v>
+        <v>3.91</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -676,19 +676,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C10" t="n">
-        <v>11.75</v>
+        <v>11.83</v>
       </c>
       <c r="D10" t="n">
-        <v>9.83</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>13.58</v>
+        <v>13.74</v>
       </c>
       <c r="F10" t="n">
-        <v>3.74</v>
+        <v>3.77</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -703,19 +703,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C11" t="n">
-        <v>11.18</v>
+        <v>11.75</v>
       </c>
       <c r="D11" t="n">
-        <v>9.49</v>
+        <v>9.83</v>
       </c>
       <c r="E11" t="n">
-        <v>12.92</v>
+        <v>13.58</v>
       </c>
       <c r="F11" t="n">
-        <v>3.42</v>
+        <v>3.74</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C12" t="n">
-        <v>11.02</v>
+        <v>11.18</v>
       </c>
       <c r="D12" t="n">
-        <v>9.41</v>
+        <v>9.49</v>
       </c>
       <c r="E12" t="n">
-        <v>12.68</v>
+        <v>12.92</v>
       </c>
       <c r="F12" t="n">
-        <v>3.26</v>
+        <v>3.42</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
@@ -757,100 +757,100 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C13" t="n">
-        <v>11.06</v>
+        <v>11.02</v>
       </c>
       <c r="D13" t="n">
-        <v>9.369999999999999</v>
+        <v>9.41</v>
       </c>
       <c r="E13" t="n">
-        <v>12.77</v>
+        <v>12.68</v>
       </c>
       <c r="F13" t="n">
-        <v>3.41</v>
+        <v>3.26</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>Durante</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Andorra</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="C14" t="n">
-        <v>11.7</v>
+        <v>11.06</v>
       </c>
       <c r="D14" t="n">
-        <v>9.890000000000001</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>13.71</v>
+        <v>12.77</v>
       </c>
       <c r="F14" t="n">
-        <v>3.82</v>
+        <v>3.41</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Andorra</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="C15" t="n">
-        <v>11.77</v>
+        <v>11.06</v>
       </c>
       <c r="D15" t="n">
-        <v>9.859999999999999</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>13.84</v>
+        <v>12.77</v>
       </c>
       <c r="F15" t="n">
-        <v>3.98</v>
+        <v>3.41</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Después</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C16" t="n">
-        <v>11.83</v>
+        <v>5.01</v>
       </c>
       <c r="D16" t="n">
-        <v>10.05</v>
+        <v>3.84</v>
       </c>
       <c r="E16" t="n">
-        <v>13.97</v>
+        <v>6.3</v>
       </c>
       <c r="F16" t="n">
-        <v>3.93</v>
+        <v>2.46</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -861,23 +861,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="C17" t="n">
-        <v>11.85</v>
+        <v>5.02</v>
       </c>
       <c r="D17" t="n">
-        <v>10.06</v>
+        <v>3.84</v>
       </c>
       <c r="E17" t="n">
-        <v>14.02</v>
+        <v>6.35</v>
       </c>
       <c r="F17" t="n">
-        <v>3.97</v>
+        <v>2.51</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -888,158 +888,158 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C18" t="n">
-        <v>11.88</v>
+        <v>5.17</v>
       </c>
       <c r="D18" t="n">
-        <v>10.21</v>
+        <v>3.97</v>
       </c>
       <c r="E18" t="n">
-        <v>13.72</v>
+        <v>6.48</v>
       </c>
       <c r="F18" t="n">
-        <v>3.51</v>
+        <v>2.51</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C19" t="n">
-        <v>11.85</v>
+        <v>4.97</v>
       </c>
       <c r="D19" t="n">
-        <v>10.17</v>
+        <v>3.81</v>
       </c>
       <c r="E19" t="n">
-        <v>13.65</v>
+        <v>6.29</v>
       </c>
       <c r="F19" t="n">
-        <v>3.49</v>
+        <v>2.48</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Belarus</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="C20" t="n">
-        <v>10.14</v>
+        <v>4.7</v>
       </c>
       <c r="D20" t="n">
-        <v>8.52</v>
+        <v>3.52</v>
       </c>
       <c r="E20" t="n">
-        <v>11.85</v>
+        <v>5.95</v>
       </c>
       <c r="F20" t="n">
-        <v>3.33</v>
+        <v>2.43</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Durante</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Belarus</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="C21" t="n">
-        <v>10.19</v>
+        <v>4.3</v>
       </c>
       <c r="D21" t="n">
-        <v>8.57</v>
+        <v>3.2</v>
       </c>
       <c r="E21" t="n">
-        <v>11.85</v>
+        <v>5.51</v>
       </c>
       <c r="F21" t="n">
-        <v>3.29</v>
+        <v>2.31</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Belarus</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="C22" t="n">
-        <v>10.45</v>
+        <v>4.3</v>
       </c>
       <c r="D22" t="n">
-        <v>8.69</v>
+        <v>3.2</v>
       </c>
       <c r="E22" t="n">
-        <v>12.07</v>
+        <v>5.51</v>
       </c>
       <c r="F22" t="n">
-        <v>3.38</v>
+        <v>2.31</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Después</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Belarus</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C23" t="n">
-        <v>10.82</v>
+        <v>11.7</v>
       </c>
       <c r="D23" t="n">
-        <v>9.119999999999999</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>12.55</v>
+        <v>13.71</v>
       </c>
       <c r="F23" t="n">
-        <v>3.43</v>
+        <v>3.82</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1050,77 +1050,77 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Belarus</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="C24" t="n">
-        <v>11.2</v>
+        <v>11.77</v>
       </c>
       <c r="D24" t="n">
-        <v>9.44</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>13.1</v>
+        <v>13.84</v>
       </c>
       <c r="F24" t="n">
-        <v>3.66</v>
+        <v>3.98</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Belarus</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C25" t="n">
-        <v>11.4</v>
+        <v>11.83</v>
       </c>
       <c r="D25" t="n">
-        <v>9.76</v>
+        <v>10.05</v>
       </c>
       <c r="E25" t="n">
-        <v>13.17</v>
+        <v>13.97</v>
       </c>
       <c r="F25" t="n">
-        <v>3.42</v>
+        <v>3.93</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="C26" t="n">
-        <v>10.39</v>
+        <v>11.85</v>
       </c>
       <c r="D26" t="n">
-        <v>8.82</v>
+        <v>10.06</v>
       </c>
       <c r="E26" t="n">
-        <v>12.02</v>
+        <v>14.02</v>
       </c>
       <c r="F26" t="n">
-        <v>3.2</v>
+        <v>3.97</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1131,158 +1131,158 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="C27" t="n">
-        <v>10.02</v>
+        <v>11.88</v>
       </c>
       <c r="D27" t="n">
-        <v>8.460000000000001</v>
+        <v>10.21</v>
       </c>
       <c r="E27" t="n">
-        <v>11.56</v>
+        <v>13.72</v>
       </c>
       <c r="F27" t="n">
-        <v>3.1</v>
+        <v>3.51</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Durante</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="C28" t="n">
-        <v>9.91</v>
+        <v>11.85</v>
       </c>
       <c r="D28" t="n">
-        <v>8.289999999999999</v>
+        <v>10.17</v>
       </c>
       <c r="E28" t="n">
-        <v>11.5</v>
+        <v>13.65</v>
       </c>
       <c r="F28" t="n">
-        <v>3.21</v>
+        <v>3.49</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C29" t="n">
-        <v>9.609999999999999</v>
+        <v>11.85</v>
       </c>
       <c r="D29" t="n">
-        <v>8.06</v>
+        <v>10.17</v>
       </c>
       <c r="E29" t="n">
-        <v>11.4</v>
+        <v>13.65</v>
       </c>
       <c r="F29" t="n">
-        <v>3.34</v>
+        <v>3.49</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Después</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C30" t="n">
-        <v>9.220000000000001</v>
+        <v>1.57</v>
       </c>
       <c r="D30" t="n">
-        <v>7.53</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>10.82</v>
+        <v>2.5</v>
       </c>
       <c r="F30" t="n">
-        <v>3.3</v>
+        <v>1.69</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C31" t="n">
-        <v>8.74</v>
+        <v>1.69</v>
       </c>
       <c r="D31" t="n">
-        <v>7.2</v>
+        <v>0.9</v>
       </c>
       <c r="E31" t="n">
-        <v>10.27</v>
+        <v>2.63</v>
       </c>
       <c r="F31" t="n">
-        <v>3.07</v>
+        <v>1.74</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="C32" t="n">
-        <v>6.34</v>
+        <v>2.02</v>
       </c>
       <c r="D32" t="n">
-        <v>4.95</v>
+        <v>1.17</v>
       </c>
       <c r="E32" t="n">
-        <v>7.86</v>
+        <v>2.93</v>
       </c>
       <c r="F32" t="n">
-        <v>2.91</v>
+        <v>1.75</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1293,23 +1293,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="C33" t="n">
-        <v>6.52</v>
+        <v>2.3</v>
       </c>
       <c r="D33" t="n">
-        <v>5.16</v>
+        <v>1.39</v>
       </c>
       <c r="E33" t="n">
-        <v>8.01</v>
+        <v>3.26</v>
       </c>
       <c r="F33" t="n">
-        <v>2.85</v>
+        <v>1.87</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1320,131 +1320,131 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="C34" t="n">
-        <v>6.49</v>
+        <v>2.44</v>
       </c>
       <c r="D34" t="n">
-        <v>5.18</v>
+        <v>1.56</v>
       </c>
       <c r="E34" t="n">
-        <v>7.82</v>
+        <v>3.48</v>
       </c>
       <c r="F34" t="n">
-        <v>2.64</v>
+        <v>1.92</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Durante</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="C35" t="n">
-        <v>6.27</v>
+        <v>2.32</v>
       </c>
       <c r="D35" t="n">
-        <v>4.93</v>
+        <v>1.46</v>
       </c>
       <c r="E35" t="n">
-        <v>7.61</v>
+        <v>3.28</v>
       </c>
       <c r="F35" t="n">
-        <v>2.68</v>
+        <v>1.82</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="C36" t="n">
-        <v>6.2</v>
+        <v>2.32</v>
       </c>
       <c r="D36" t="n">
-        <v>4.76</v>
+        <v>1.46</v>
       </c>
       <c r="E36" t="n">
-        <v>7.53</v>
+        <v>3.28</v>
       </c>
       <c r="F36" t="n">
-        <v>2.77</v>
+        <v>1.82</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>Después</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Belarus</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C37" t="n">
-        <v>6.33</v>
+        <v>10.14</v>
       </c>
       <c r="D37" t="n">
-        <v>4.91</v>
+        <v>8.52</v>
       </c>
       <c r="E37" t="n">
-        <v>7.82</v>
+        <v>11.85</v>
       </c>
       <c r="F37" t="n">
-        <v>2.91</v>
+        <v>3.33</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Belarus</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="C38" t="n">
-        <v>11.4</v>
+        <v>10.19</v>
       </c>
       <c r="D38" t="n">
-        <v>9.6</v>
+        <v>8.57</v>
       </c>
       <c r="E38" t="n">
-        <v>13.19</v>
+        <v>11.85</v>
       </c>
       <c r="F38" t="n">
-        <v>3.59</v>
+        <v>3.29</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1455,23 +1455,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Belarus</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C39" t="n">
-        <v>11.62</v>
+        <v>10.45</v>
       </c>
       <c r="D39" t="n">
-        <v>9.91</v>
+        <v>8.69</v>
       </c>
       <c r="E39" t="n">
-        <v>13.52</v>
+        <v>12.07</v>
       </c>
       <c r="F39" t="n">
-        <v>3.61</v>
+        <v>3.38</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1482,23 +1482,23 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Belarus</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="C40" t="n">
-        <v>11.6</v>
+        <v>10.82</v>
       </c>
       <c r="D40" t="n">
-        <v>9.84</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>13.4</v>
+        <v>12.55</v>
       </c>
       <c r="F40" t="n">
-        <v>3.55</v>
+        <v>3.43</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1509,77 +1509,77 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Belarus</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C41" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="D41" t="n">
-        <v>9.68</v>
+        <v>9.44</v>
       </c>
       <c r="E41" t="n">
-        <v>13.27</v>
+        <v>13.1</v>
       </c>
       <c r="F41" t="n">
-        <v>3.59</v>
+        <v>3.66</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Durante</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Belarus</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C42" t="n">
-        <v>11.44</v>
+        <v>11.4</v>
       </c>
       <c r="D42" t="n">
-        <v>9.56</v>
+        <v>9.76</v>
       </c>
       <c r="E42" t="n">
-        <v>13.37</v>
+        <v>13.17</v>
       </c>
       <c r="F42" t="n">
-        <v>3.81</v>
+        <v>3.42</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Belarus</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>2022</v>
       </c>
       <c r="C43" t="n">
-        <v>11.54</v>
+        <v>11.4</v>
       </c>
       <c r="D43" t="n">
-        <v>9.69</v>
+        <v>9.76</v>
       </c>
       <c r="E43" t="n">
-        <v>13.31</v>
+        <v>13.17</v>
       </c>
       <c r="F43" t="n">
-        <v>3.62</v>
+        <v>3.42</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1590,23 +1590,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>2016</v>
       </c>
       <c r="C44" t="n">
-        <v>10.62</v>
+        <v>10.39</v>
       </c>
       <c r="D44" t="n">
-        <v>8.779999999999999</v>
+        <v>8.82</v>
       </c>
       <c r="E44" t="n">
-        <v>12.6</v>
+        <v>12.02</v>
       </c>
       <c r="F44" t="n">
-        <v>3.82</v>
+        <v>3.2</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1617,23 +1617,23 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>2017</v>
       </c>
       <c r="C45" t="n">
-        <v>10.59</v>
+        <v>10.02</v>
       </c>
       <c r="D45" t="n">
-        <v>8.83</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="E45" t="n">
-        <v>12.41</v>
+        <v>11.56</v>
       </c>
       <c r="F45" t="n">
-        <v>3.59</v>
+        <v>3.1</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1644,23 +1644,23 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>2018</v>
       </c>
       <c r="C46" t="n">
-        <v>10.71</v>
+        <v>9.91</v>
       </c>
       <c r="D46" t="n">
-        <v>8.9</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>12.51</v>
+        <v>11.5</v>
       </c>
       <c r="F46" t="n">
-        <v>3.61</v>
+        <v>3.21</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1671,23 +1671,23 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>2019</v>
       </c>
       <c r="C47" t="n">
-        <v>10.75</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>8.91</v>
+        <v>8.06</v>
       </c>
       <c r="E47" t="n">
-        <v>12.6</v>
+        <v>11.4</v>
       </c>
       <c r="F47" t="n">
-        <v>3.69</v>
+        <v>3.34</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1698,23 +1698,23 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>2020</v>
       </c>
       <c r="C48" t="n">
-        <v>10.81</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>9.07</v>
+        <v>7.53</v>
       </c>
       <c r="E48" t="n">
-        <v>12.74</v>
+        <v>10.82</v>
       </c>
       <c r="F48" t="n">
-        <v>3.67</v>
+        <v>3.3</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1725,77 +1725,77 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C49" t="n">
-        <v>10.85</v>
+        <v>8.74</v>
       </c>
       <c r="D49" t="n">
-        <v>9.140000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="E49" t="n">
-        <v>12.78</v>
+        <v>10.27</v>
       </c>
       <c r="F49" t="n">
-        <v>3.65</v>
+        <v>3.07</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="C50" t="n">
-        <v>5.98</v>
+        <v>8.74</v>
       </c>
       <c r="D50" t="n">
-        <v>4.55</v>
+        <v>7.2</v>
       </c>
       <c r="E50" t="n">
-        <v>7.44</v>
+        <v>10.27</v>
       </c>
       <c r="F50" t="n">
-        <v>2.89</v>
+        <v>3.07</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Después</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="C51" t="n">
-        <v>6.12</v>
+        <v>6.34</v>
       </c>
       <c r="D51" t="n">
-        <v>4.63</v>
+        <v>4.95</v>
       </c>
       <c r="E51" t="n">
-        <v>7.8</v>
+        <v>7.86</v>
       </c>
       <c r="F51" t="n">
-        <v>3.17</v>
+        <v>2.91</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -1806,23 +1806,23 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C52" t="n">
-        <v>6.13</v>
+        <v>6.52</v>
       </c>
       <c r="D52" t="n">
-        <v>4.65</v>
+        <v>5.16</v>
       </c>
       <c r="E52" t="n">
-        <v>7.67</v>
+        <v>8.01</v>
       </c>
       <c r="F52" t="n">
-        <v>3.02</v>
+        <v>2.85</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -1833,23 +1833,23 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C53" t="n">
-        <v>5.79</v>
+        <v>6.49</v>
       </c>
       <c r="D53" t="n">
-        <v>4.41</v>
+        <v>5.18</v>
       </c>
       <c r="E53" t="n">
-        <v>7.31</v>
+        <v>7.82</v>
       </c>
       <c r="F53" t="n">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -1860,131 +1860,131 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C54" t="n">
-        <v>5.39</v>
+        <v>6.27</v>
       </c>
       <c r="D54" t="n">
-        <v>4.07</v>
+        <v>4.93</v>
       </c>
       <c r="E54" t="n">
-        <v>6.76</v>
+        <v>7.61</v>
       </c>
       <c r="F54" t="n">
         <v>2.68</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C55" t="n">
-        <v>5.21</v>
+        <v>6.2</v>
       </c>
       <c r="D55" t="n">
-        <v>3.98</v>
+        <v>4.76</v>
       </c>
       <c r="E55" t="n">
-        <v>6.53</v>
+        <v>7.53</v>
       </c>
       <c r="F55" t="n">
-        <v>2.55</v>
+        <v>2.77</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>Durante</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="C56" t="n">
-        <v>13.66</v>
+        <v>6.33</v>
       </c>
       <c r="D56" t="n">
-        <v>11.86</v>
+        <v>4.91</v>
       </c>
       <c r="E56" t="n">
-        <v>15.7</v>
+        <v>7.82</v>
       </c>
       <c r="F56" t="n">
-        <v>3.85</v>
+        <v>2.91</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="C57" t="n">
-        <v>13.73</v>
+        <v>6.33</v>
       </c>
       <c r="D57" t="n">
-        <v>11.96</v>
+        <v>4.91</v>
       </c>
       <c r="E57" t="n">
-        <v>15.74</v>
+        <v>7.82</v>
       </c>
       <c r="F57" t="n">
-        <v>3.78</v>
+        <v>2.91</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Después</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C58" t="n">
-        <v>13.77</v>
+        <v>11.4</v>
       </c>
       <c r="D58" t="n">
-        <v>11.95</v>
+        <v>9.6</v>
       </c>
       <c r="E58" t="n">
-        <v>15.67</v>
+        <v>13.19</v>
       </c>
       <c r="F58" t="n">
-        <v>3.72</v>
+        <v>3.59</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -1995,23 +1995,23 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="C59" t="n">
-        <v>13.75</v>
+        <v>11.62</v>
       </c>
       <c r="D59" t="n">
-        <v>11.92</v>
+        <v>9.91</v>
       </c>
       <c r="E59" t="n">
-        <v>15.81</v>
+        <v>13.52</v>
       </c>
       <c r="F59" t="n">
-        <v>3.89</v>
+        <v>3.61</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2022,158 +2022,158 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C60" t="n">
-        <v>13.64</v>
+        <v>11.6</v>
       </c>
       <c r="D60" t="n">
-        <v>11.92</v>
+        <v>9.84</v>
       </c>
       <c r="E60" t="n">
-        <v>15.52</v>
+        <v>13.4</v>
       </c>
       <c r="F60" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C61" t="n">
-        <v>13.68</v>
+        <v>11.5</v>
       </c>
       <c r="D61" t="n">
-        <v>11.81</v>
+        <v>9.68</v>
       </c>
       <c r="E61" t="n">
-        <v>15.58</v>
+        <v>13.27</v>
       </c>
       <c r="F61" t="n">
-        <v>3.77</v>
+        <v>3.59</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="C62" t="n">
-        <v>9.859999999999999</v>
+        <v>11.44</v>
       </c>
       <c r="D62" t="n">
-        <v>8.25</v>
+        <v>9.56</v>
       </c>
       <c r="E62" t="n">
-        <v>11.79</v>
+        <v>13.37</v>
       </c>
       <c r="F62" t="n">
-        <v>3.53</v>
+        <v>3.81</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Durante</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="C63" t="n">
-        <v>9.82</v>
+        <v>11.54</v>
       </c>
       <c r="D63" t="n">
-        <v>8.09</v>
+        <v>9.69</v>
       </c>
       <c r="E63" t="n">
-        <v>11.68</v>
+        <v>13.31</v>
       </c>
       <c r="F63" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="C64" t="n">
-        <v>9.67</v>
+        <v>11.54</v>
       </c>
       <c r="D64" t="n">
-        <v>7.99</v>
+        <v>9.69</v>
       </c>
       <c r="E64" t="n">
-        <v>11.44</v>
+        <v>13.31</v>
       </c>
       <c r="F64" t="n">
-        <v>3.45</v>
+        <v>3.62</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Después</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C65" t="n">
-        <v>9.710000000000001</v>
+        <v>10.62</v>
       </c>
       <c r="D65" t="n">
-        <v>8.109999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="E65" t="n">
-        <v>11.43</v>
+        <v>12.6</v>
       </c>
       <c r="F65" t="n">
-        <v>3.32</v>
+        <v>3.82</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2184,77 +2184,77 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="C66" t="n">
-        <v>9.93</v>
+        <v>10.59</v>
       </c>
       <c r="D66" t="n">
-        <v>8.279999999999999</v>
+        <v>8.83</v>
       </c>
       <c r="E66" t="n">
-        <v>11.64</v>
+        <v>12.41</v>
       </c>
       <c r="F66" t="n">
-        <v>3.35</v>
+        <v>3.59</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C67" t="n">
-        <v>9.970000000000001</v>
+        <v>10.71</v>
       </c>
       <c r="D67" t="n">
-        <v>8.359999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="E67" t="n">
-        <v>11.77</v>
+        <v>12.51</v>
       </c>
       <c r="F67" t="n">
-        <v>3.4</v>
+        <v>3.61</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="C68" t="n">
-        <v>10.18</v>
+        <v>10.75</v>
       </c>
       <c r="D68" t="n">
-        <v>7.2</v>
+        <v>8.91</v>
       </c>
       <c r="E68" t="n">
-        <v>13.14</v>
+        <v>12.6</v>
       </c>
       <c r="F68" t="n">
-        <v>5.94</v>
+        <v>3.69</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2265,158 +2265,158 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="C69" t="n">
-        <v>8.98</v>
+        <v>10.81</v>
       </c>
       <c r="D69" t="n">
-        <v>6.29</v>
+        <v>9.07</v>
       </c>
       <c r="E69" t="n">
-        <v>11.73</v>
+        <v>12.74</v>
       </c>
       <c r="F69" t="n">
-        <v>5.44</v>
+        <v>3.67</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Durante</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="C70" t="n">
-        <v>8.17</v>
+        <v>10.85</v>
       </c>
       <c r="D70" t="n">
-        <v>5.67</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E70" t="n">
-        <v>10.77</v>
+        <v>12.78</v>
       </c>
       <c r="F70" t="n">
-        <v>5.1</v>
+        <v>3.65</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C71" t="n">
-        <v>8.5</v>
+        <v>10.85</v>
       </c>
       <c r="D71" t="n">
-        <v>6.19</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E71" t="n">
-        <v>10.83</v>
+        <v>12.78</v>
       </c>
       <c r="F71" t="n">
-        <v>4.64</v>
+        <v>3.65</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Después</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C72" t="n">
-        <v>9.68</v>
+        <v>5.98</v>
       </c>
       <c r="D72" t="n">
-        <v>7.32</v>
+        <v>4.55</v>
       </c>
       <c r="E72" t="n">
-        <v>12.13</v>
+        <v>7.44</v>
       </c>
       <c r="F72" t="n">
-        <v>4.82</v>
+        <v>2.89</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C73" t="n">
-        <v>10.49</v>
+        <v>6.12</v>
       </c>
       <c r="D73" t="n">
-        <v>8.17</v>
+        <v>4.63</v>
       </c>
       <c r="E73" t="n">
-        <v>12.89</v>
+        <v>7.8</v>
       </c>
       <c r="F73" t="n">
-        <v>4.72</v>
+        <v>3.17</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="C74" t="n">
-        <v>11.22</v>
+        <v>6.13</v>
       </c>
       <c r="D74" t="n">
-        <v>9.33</v>
+        <v>4.65</v>
       </c>
       <c r="E74" t="n">
-        <v>13.14</v>
+        <v>7.67</v>
       </c>
       <c r="F74" t="n">
-        <v>3.81</v>
+        <v>3.02</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -2427,23 +2427,23 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="C75" t="n">
-        <v>11.07</v>
+        <v>5.79</v>
       </c>
       <c r="D75" t="n">
-        <v>9.210000000000001</v>
+        <v>4.41</v>
       </c>
       <c r="E75" t="n">
-        <v>13.11</v>
+        <v>7.31</v>
       </c>
       <c r="F75" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -2454,131 +2454,131 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="C76" t="n">
-        <v>10.81</v>
+        <v>5.39</v>
       </c>
       <c r="D76" t="n">
-        <v>8.99</v>
+        <v>4.07</v>
       </c>
       <c r="E76" t="n">
-        <v>12.78</v>
+        <v>6.76</v>
       </c>
       <c r="F76" t="n">
-        <v>3.79</v>
+        <v>2.68</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Durante</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="C77" t="n">
-        <v>10.38</v>
+        <v>5.21</v>
       </c>
       <c r="D77" t="n">
-        <v>8.52</v>
+        <v>3.98</v>
       </c>
       <c r="E77" t="n">
-        <v>12.38</v>
+        <v>6.53</v>
       </c>
       <c r="F77" t="n">
-        <v>3.86</v>
+        <v>2.55</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="C78" t="n">
-        <v>9.84</v>
+        <v>5.21</v>
       </c>
       <c r="D78" t="n">
-        <v>8.19</v>
+        <v>3.98</v>
       </c>
       <c r="E78" t="n">
-        <v>11.79</v>
+        <v>6.53</v>
       </c>
       <c r="F78" t="n">
-        <v>3.6</v>
+        <v>2.55</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>Después</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C79" t="n">
-        <v>9.51</v>
+        <v>13.66</v>
       </c>
       <c r="D79" t="n">
-        <v>7.78</v>
+        <v>11.86</v>
       </c>
       <c r="E79" t="n">
-        <v>11.19</v>
+        <v>15.7</v>
       </c>
       <c r="F79" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="C80" t="n">
-        <v>12.41</v>
+        <v>13.73</v>
       </c>
       <c r="D80" t="n">
-        <v>10.65</v>
+        <v>11.96</v>
       </c>
       <c r="E80" t="n">
-        <v>14.24</v>
+        <v>15.74</v>
       </c>
       <c r="F80" t="n">
-        <v>3.59</v>
+        <v>3.78</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -2589,23 +2589,23 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C81" t="n">
-        <v>12.3</v>
+        <v>13.77</v>
       </c>
       <c r="D81" t="n">
-        <v>10.35</v>
+        <v>11.95</v>
       </c>
       <c r="E81" t="n">
-        <v>14.12</v>
+        <v>15.67</v>
       </c>
       <c r="F81" t="n">
-        <v>3.77</v>
+        <v>3.72</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -2616,23 +2616,23 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="C82" t="n">
-        <v>12.19</v>
+        <v>13.75</v>
       </c>
       <c r="D82" t="n">
-        <v>10.28</v>
+        <v>11.92</v>
       </c>
       <c r="E82" t="n">
-        <v>14.04</v>
+        <v>15.81</v>
       </c>
       <c r="F82" t="n">
-        <v>3.77</v>
+        <v>3.89</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -2643,77 +2643,77 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C83" t="n">
-        <v>11.76</v>
+        <v>13.64</v>
       </c>
       <c r="D83" t="n">
-        <v>9.99</v>
+        <v>11.92</v>
       </c>
       <c r="E83" t="n">
-        <v>13.59</v>
+        <v>15.52</v>
       </c>
       <c r="F83" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Durante</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C84" t="n">
-        <v>11.43</v>
+        <v>13.68</v>
       </c>
       <c r="D84" t="n">
-        <v>9.6</v>
+        <v>11.81</v>
       </c>
       <c r="E84" t="n">
-        <v>13.24</v>
+        <v>15.58</v>
       </c>
       <c r="F84" t="n">
-        <v>3.64</v>
+        <v>3.77</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>2022</v>
       </c>
       <c r="C85" t="n">
-        <v>11.2</v>
+        <v>13.68</v>
       </c>
       <c r="D85" t="n">
-        <v>9.460000000000001</v>
+        <v>11.81</v>
       </c>
       <c r="E85" t="n">
-        <v>13.05</v>
+        <v>15.58</v>
       </c>
       <c r="F85" t="n">
-        <v>3.59</v>
+        <v>3.77</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -2724,23 +2724,23 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>2016</v>
       </c>
       <c r="C86" t="n">
-        <v>11.93</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="D86" t="n">
-        <v>10.15</v>
+        <v>8.25</v>
       </c>
       <c r="E86" t="n">
-        <v>13.7</v>
+        <v>11.79</v>
       </c>
       <c r="F86" t="n">
-        <v>3.56</v>
+        <v>3.53</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -2751,23 +2751,23 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>2017</v>
       </c>
       <c r="C87" t="n">
-        <v>11.92</v>
+        <v>9.82</v>
       </c>
       <c r="D87" t="n">
-        <v>10.25</v>
+        <v>8.09</v>
       </c>
       <c r="E87" t="n">
-        <v>13.64</v>
+        <v>11.68</v>
       </c>
       <c r="F87" t="n">
-        <v>3.39</v>
+        <v>3.6</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -2778,23 +2778,23 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>2018</v>
       </c>
       <c r="C88" t="n">
-        <v>11.76</v>
+        <v>9.67</v>
       </c>
       <c r="D88" t="n">
-        <v>10.1</v>
+        <v>7.99</v>
       </c>
       <c r="E88" t="n">
-        <v>13.47</v>
+        <v>11.44</v>
       </c>
       <c r="F88" t="n">
-        <v>3.37</v>
+        <v>3.45</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -2805,23 +2805,23 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>2019</v>
       </c>
       <c r="C89" t="n">
-        <v>11.57</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="D89" t="n">
-        <v>9.869999999999999</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="E89" t="n">
-        <v>13.42</v>
+        <v>11.43</v>
       </c>
       <c r="F89" t="n">
-        <v>3.55</v>
+        <v>3.32</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -2832,23 +2832,23 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>2020</v>
       </c>
       <c r="C90" t="n">
-        <v>11.31</v>
+        <v>9.93</v>
       </c>
       <c r="D90" t="n">
-        <v>9.609999999999999</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="E90" t="n">
-        <v>13.21</v>
+        <v>11.64</v>
       </c>
       <c r="F90" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -2859,77 +2859,77 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C91" t="n">
-        <v>11.24</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="D91" t="n">
-        <v>9.449999999999999</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="E91" t="n">
-        <v>12.92</v>
+        <v>11.77</v>
       </c>
       <c r="F91" t="n">
-        <v>3.47</v>
+        <v>3.4</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="C92" t="n">
-        <v>7.44</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="D92" t="n">
-        <v>5.94</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="E92" t="n">
-        <v>9</v>
+        <v>11.77</v>
       </c>
       <c r="F92" t="n">
-        <v>3.06</v>
+        <v>3.4</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Después</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="C93" t="n">
-        <v>7.37</v>
+        <v>10.18</v>
       </c>
       <c r="D93" t="n">
-        <v>5.82</v>
+        <v>7.2</v>
       </c>
       <c r="E93" t="n">
-        <v>8.859999999999999</v>
+        <v>13.14</v>
       </c>
       <c r="F93" t="n">
-        <v>3.04</v>
+        <v>5.94</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -2940,23 +2940,23 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C94" t="n">
-        <v>7.29</v>
+        <v>8.98</v>
       </c>
       <c r="D94" t="n">
-        <v>5.82</v>
+        <v>6.29</v>
       </c>
       <c r="E94" t="n">
-        <v>8.74</v>
+        <v>11.73</v>
       </c>
       <c r="F94" t="n">
-        <v>2.92</v>
+        <v>5.44</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -2967,23 +2967,23 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C95" t="n">
-        <v>7.01</v>
+        <v>8.17</v>
       </c>
       <c r="D95" t="n">
-        <v>5.54</v>
+        <v>5.67</v>
       </c>
       <c r="E95" t="n">
-        <v>8.57</v>
+        <v>10.77</v>
       </c>
       <c r="F95" t="n">
-        <v>3.04</v>
+        <v>5.1</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -2994,131 +2994,131 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C96" t="n">
-        <v>6.96</v>
+        <v>8.5</v>
       </c>
       <c r="D96" t="n">
-        <v>5.53</v>
+        <v>6.19</v>
       </c>
       <c r="E96" t="n">
-        <v>8.41</v>
+        <v>10.83</v>
       </c>
       <c r="F96" t="n">
-        <v>2.88</v>
+        <v>4.64</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C97" t="n">
-        <v>6.98</v>
+        <v>9.68</v>
       </c>
       <c r="D97" t="n">
-        <v>5.54</v>
+        <v>7.32</v>
       </c>
       <c r="E97" t="n">
-        <v>8.44</v>
+        <v>12.13</v>
       </c>
       <c r="F97" t="n">
-        <v>2.9</v>
+        <v>4.82</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>Durante</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="C98" t="n">
-        <v>11.76</v>
+        <v>10.49</v>
       </c>
       <c r="D98" t="n">
-        <v>9.960000000000001</v>
+        <v>8.17</v>
       </c>
       <c r="E98" t="n">
-        <v>13.46</v>
+        <v>12.89</v>
       </c>
       <c r="F98" t="n">
-        <v>3.5</v>
+        <v>4.72</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="C99" t="n">
-        <v>11.87</v>
+        <v>10.49</v>
       </c>
       <c r="D99" t="n">
-        <v>10.05</v>
+        <v>8.17</v>
       </c>
       <c r="E99" t="n">
-        <v>13.72</v>
+        <v>12.89</v>
       </c>
       <c r="F99" t="n">
-        <v>3.67</v>
+        <v>4.72</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Después</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C100" t="n">
-        <v>11.67</v>
+        <v>11.22</v>
       </c>
       <c r="D100" t="n">
-        <v>9.93</v>
+        <v>9.33</v>
       </c>
       <c r="E100" t="n">
-        <v>13.51</v>
+        <v>13.14</v>
       </c>
       <c r="F100" t="n">
-        <v>3.58</v>
+        <v>3.81</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -3129,23 +3129,23 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="C101" t="n">
-        <v>11.55</v>
+        <v>11.07</v>
       </c>
       <c r="D101" t="n">
-        <v>9.69</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="E101" t="n">
-        <v>13.33</v>
+        <v>13.11</v>
       </c>
       <c r="F101" t="n">
-        <v>3.64</v>
+        <v>3.9</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -3156,158 +3156,158 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C102" t="n">
-        <v>11.26</v>
+        <v>10.81</v>
       </c>
       <c r="D102" t="n">
-        <v>9.449999999999999</v>
+        <v>8.99</v>
       </c>
       <c r="E102" t="n">
-        <v>13.03</v>
+        <v>12.78</v>
       </c>
       <c r="F102" t="n">
-        <v>3.58</v>
+        <v>3.79</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C103" t="n">
-        <v>11.25</v>
+        <v>10.38</v>
       </c>
       <c r="D103" t="n">
-        <v>9.6</v>
+        <v>8.52</v>
       </c>
       <c r="E103" t="n">
-        <v>13.01</v>
+        <v>12.38</v>
       </c>
       <c r="F103" t="n">
-        <v>3.41</v>
+        <v>3.86</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="C104" t="n">
-        <v>7.6</v>
+        <v>9.84</v>
       </c>
       <c r="D104" t="n">
-        <v>5.96</v>
+        <v>8.19</v>
       </c>
       <c r="E104" t="n">
-        <v>9.34</v>
+        <v>11.79</v>
       </c>
       <c r="F104" t="n">
-        <v>3.39</v>
+        <v>3.6</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Durante</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="C105" t="n">
-        <v>7.5</v>
+        <v>9.51</v>
       </c>
       <c r="D105" t="n">
-        <v>5.98</v>
+        <v>7.78</v>
       </c>
       <c r="E105" t="n">
-        <v>9.300000000000001</v>
+        <v>11.19</v>
       </c>
       <c r="F105" t="n">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="C106" t="n">
-        <v>7.49</v>
+        <v>9.51</v>
       </c>
       <c r="D106" t="n">
-        <v>5.88</v>
+        <v>7.78</v>
       </c>
       <c r="E106" t="n">
-        <v>9.33</v>
+        <v>11.19</v>
       </c>
       <c r="F106" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Después</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C107" t="n">
-        <v>7.63</v>
+        <v>12.41</v>
       </c>
       <c r="D107" t="n">
-        <v>6.07</v>
+        <v>10.65</v>
       </c>
       <c r="E107" t="n">
-        <v>9.359999999999999</v>
+        <v>14.24</v>
       </c>
       <c r="F107" t="n">
-        <v>3.29</v>
+        <v>3.59</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -3318,77 +3318,77 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="C108" t="n">
-        <v>8</v>
+        <v>12.3</v>
       </c>
       <c r="D108" t="n">
-        <v>6.47</v>
+        <v>10.35</v>
       </c>
       <c r="E108" t="n">
-        <v>9.65</v>
+        <v>14.12</v>
       </c>
       <c r="F108" t="n">
-        <v>3.17</v>
+        <v>3.77</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C109" t="n">
-        <v>8.210000000000001</v>
+        <v>12.19</v>
       </c>
       <c r="D109" t="n">
-        <v>6.77</v>
+        <v>10.28</v>
       </c>
       <c r="E109" t="n">
-        <v>9.800000000000001</v>
+        <v>14.04</v>
       </c>
       <c r="F109" t="n">
-        <v>3.03</v>
+        <v>3.77</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="C110" t="n">
-        <v>11.38</v>
+        <v>11.76</v>
       </c>
       <c r="D110" t="n">
-        <v>9.69</v>
+        <v>9.99</v>
       </c>
       <c r="E110" t="n">
-        <v>13.17</v>
+        <v>13.59</v>
       </c>
       <c r="F110" t="n">
-        <v>3.47</v>
+        <v>3.61</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -3399,158 +3399,158 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="C111" t="n">
-        <v>11.47</v>
+        <v>11.43</v>
       </c>
       <c r="D111" t="n">
-        <v>9.640000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="E111" t="n">
         <v>13.24</v>
       </c>
       <c r="F111" t="n">
-        <v>3.61</v>
+        <v>3.64</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Durante</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="C112" t="n">
-        <v>11.31</v>
+        <v>11.2</v>
       </c>
       <c r="D112" t="n">
-        <v>9.619999999999999</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="E112" t="n">
-        <v>13.1</v>
+        <v>13.05</v>
       </c>
       <c r="F112" t="n">
-        <v>3.47</v>
+        <v>3.59</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C113" t="n">
-        <v>11.02</v>
+        <v>11.2</v>
       </c>
       <c r="D113" t="n">
-        <v>9.220000000000001</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="E113" t="n">
-        <v>12.86</v>
+        <v>13.05</v>
       </c>
       <c r="F113" t="n">
-        <v>3.64</v>
+        <v>3.59</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Después</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C114" t="n">
-        <v>10.63</v>
+        <v>14.65</v>
       </c>
       <c r="D114" t="n">
-        <v>8.84</v>
+        <v>12.16</v>
       </c>
       <c r="E114" t="n">
-        <v>12.33</v>
+        <v>17.21</v>
       </c>
       <c r="F114" t="n">
-        <v>3.49</v>
+        <v>5.05</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C115" t="n">
-        <v>10.55</v>
+        <v>14.63</v>
       </c>
       <c r="D115" t="n">
-        <v>8.73</v>
+        <v>12.18</v>
       </c>
       <c r="E115" t="n">
-        <v>12.2</v>
+        <v>17.15</v>
       </c>
       <c r="F115" t="n">
-        <v>3.47</v>
+        <v>4.97</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="C116" t="n">
-        <v>7.74</v>
+        <v>15.02</v>
       </c>
       <c r="D116" t="n">
-        <v>6.52</v>
+        <v>12.28</v>
       </c>
       <c r="E116" t="n">
-        <v>9.220000000000001</v>
+        <v>17.43</v>
       </c>
       <c r="F116" t="n">
-        <v>2.7</v>
+        <v>5.15</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -3561,23 +3561,23 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="C117" t="n">
-        <v>8.01</v>
+        <v>15.57</v>
       </c>
       <c r="D117" t="n">
-        <v>6.74</v>
+        <v>12.91</v>
       </c>
       <c r="E117" t="n">
-        <v>9.42</v>
+        <v>18.39</v>
       </c>
       <c r="F117" t="n">
-        <v>2.68</v>
+        <v>5.48</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -3588,131 +3588,131 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="C118" t="n">
-        <v>8.26</v>
+        <v>15.88</v>
       </c>
       <c r="D118" t="n">
-        <v>6.94</v>
+        <v>13.26</v>
       </c>
       <c r="E118" t="n">
-        <v>9.710000000000001</v>
+        <v>18.42</v>
       </c>
       <c r="F118" t="n">
-        <v>2.77</v>
+        <v>5.16</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Durante</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="C119" t="n">
-        <v>8.26</v>
+        <v>15.54</v>
       </c>
       <c r="D119" t="n">
-        <v>6.84</v>
+        <v>12.89</v>
       </c>
       <c r="E119" t="n">
-        <v>9.800000000000001</v>
+        <v>17.89</v>
       </c>
       <c r="F119" t="n">
-        <v>2.96</v>
+        <v>5</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="C120" t="n">
-        <v>8.300000000000001</v>
+        <v>15.54</v>
       </c>
       <c r="D120" t="n">
-        <v>6.82</v>
+        <v>12.89</v>
       </c>
       <c r="E120" t="n">
-        <v>9.859999999999999</v>
+        <v>17.89</v>
       </c>
       <c r="F120" t="n">
-        <v>3.04</v>
+        <v>5</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>Después</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C121" t="n">
-        <v>8.33</v>
+        <v>11.93</v>
       </c>
       <c r="D121" t="n">
-        <v>6.91</v>
+        <v>10.15</v>
       </c>
       <c r="E121" t="n">
-        <v>9.93</v>
+        <v>13.7</v>
       </c>
       <c r="F121" t="n">
-        <v>3.03</v>
+        <v>3.56</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="C122" t="n">
-        <v>12.91</v>
+        <v>11.92</v>
       </c>
       <c r="D122" t="n">
-        <v>10.51</v>
+        <v>10.25</v>
       </c>
       <c r="E122" t="n">
-        <v>15.6</v>
+        <v>13.64</v>
       </c>
       <c r="F122" t="n">
-        <v>5.09</v>
+        <v>3.39</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -3723,23 +3723,23 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C123" t="n">
-        <v>13.23</v>
+        <v>11.76</v>
       </c>
       <c r="D123" t="n">
-        <v>10.87</v>
+        <v>10.1</v>
       </c>
       <c r="E123" t="n">
-        <v>15.97</v>
+        <v>13.47</v>
       </c>
       <c r="F123" t="n">
-        <v>5.1</v>
+        <v>3.37</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -3750,23 +3750,23 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="C124" t="n">
-        <v>13.64</v>
+        <v>11.57</v>
       </c>
       <c r="D124" t="n">
-        <v>10.98</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="E124" t="n">
-        <v>16.18</v>
+        <v>13.42</v>
       </c>
       <c r="F124" t="n">
-        <v>5.2</v>
+        <v>3.55</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -3777,77 +3777,77 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C125" t="n">
-        <v>14.1</v>
+        <v>11.31</v>
       </c>
       <c r="D125" t="n">
-        <v>11.68</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="E125" t="n">
-        <v>16.56</v>
+        <v>13.21</v>
       </c>
       <c r="F125" t="n">
-        <v>4.88</v>
+        <v>3.6</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Durante</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C126" t="n">
-        <v>14.66</v>
+        <v>11.24</v>
       </c>
       <c r="D126" t="n">
-        <v>12.39</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="E126" t="n">
-        <v>17.24</v>
+        <v>12.92</v>
       </c>
       <c r="F126" t="n">
-        <v>4.85</v>
+        <v>3.47</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B127" t="n">
         <v>2022</v>
       </c>
       <c r="C127" t="n">
-        <v>14.73</v>
+        <v>11.24</v>
       </c>
       <c r="D127" t="n">
-        <v>12.63</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="E127" t="n">
-        <v>17.3</v>
+        <v>12.92</v>
       </c>
       <c r="F127" t="n">
-        <v>4.67</v>
+        <v>3.47</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -3858,23 +3858,23 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="B128" t="n">
         <v>2016</v>
       </c>
       <c r="C128" t="n">
-        <v>12.48</v>
+        <v>7.44</v>
       </c>
       <c r="D128" t="n">
-        <v>10.42</v>
+        <v>5.94</v>
       </c>
       <c r="E128" t="n">
-        <v>14.45</v>
+        <v>9</v>
       </c>
       <c r="F128" t="n">
-        <v>4.02</v>
+        <v>3.06</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -3885,23 +3885,23 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="B129" t="n">
         <v>2017</v>
       </c>
       <c r="C129" t="n">
-        <v>11.83</v>
+        <v>7.37</v>
       </c>
       <c r="D129" t="n">
-        <v>9.960000000000001</v>
+        <v>5.82</v>
       </c>
       <c r="E129" t="n">
-        <v>13.76</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="F129" t="n">
-        <v>3.79</v>
+        <v>3.04</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -3912,23 +3912,23 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="B130" t="n">
         <v>2018</v>
       </c>
       <c r="C130" t="n">
-        <v>11.4</v>
+        <v>7.29</v>
       </c>
       <c r="D130" t="n">
-        <v>9.65</v>
+        <v>5.82</v>
       </c>
       <c r="E130" t="n">
-        <v>13.29</v>
+        <v>8.74</v>
       </c>
       <c r="F130" t="n">
-        <v>3.64</v>
+        <v>2.92</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -3939,23 +3939,23 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="B131" t="n">
         <v>2019</v>
       </c>
       <c r="C131" t="n">
-        <v>11.43</v>
+        <v>7.01</v>
       </c>
       <c r="D131" t="n">
-        <v>9.76</v>
+        <v>5.54</v>
       </c>
       <c r="E131" t="n">
-        <v>13.35</v>
+        <v>8.57</v>
       </c>
       <c r="F131" t="n">
-        <v>3.59</v>
+        <v>3.04</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -3966,23 +3966,23 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="B132" t="n">
         <v>2020</v>
       </c>
       <c r="C132" t="n">
-        <v>11.98</v>
+        <v>6.96</v>
       </c>
       <c r="D132" t="n">
-        <v>10.18</v>
+        <v>5.53</v>
       </c>
       <c r="E132" t="n">
-        <v>13.83</v>
+        <v>8.41</v>
       </c>
       <c r="F132" t="n">
-        <v>3.65</v>
+        <v>2.88</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -3993,77 +3993,77 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C133" t="n">
-        <v>12.18</v>
+        <v>6.98</v>
       </c>
       <c r="D133" t="n">
-        <v>10.5</v>
+        <v>5.54</v>
       </c>
       <c r="E133" t="n">
-        <v>14.02</v>
+        <v>8.44</v>
       </c>
       <c r="F133" t="n">
-        <v>3.51</v>
+        <v>2.9</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="C134" t="n">
-        <v>11.68</v>
+        <v>6.98</v>
       </c>
       <c r="D134" t="n">
-        <v>9.82</v>
+        <v>5.54</v>
       </c>
       <c r="E134" t="n">
-        <v>13.41</v>
+        <v>8.44</v>
       </c>
       <c r="F134" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Después</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="C135" t="n">
-        <v>11.64</v>
+        <v>11.76</v>
       </c>
       <c r="D135" t="n">
-        <v>9.890000000000001</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="E135" t="n">
-        <v>13.49</v>
+        <v>13.46</v>
       </c>
       <c r="F135" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -4074,23 +4074,23 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C136" t="n">
-        <v>11.53</v>
+        <v>11.87</v>
       </c>
       <c r="D136" t="n">
-        <v>9.84</v>
+        <v>10.05</v>
       </c>
       <c r="E136" t="n">
-        <v>13.54</v>
+        <v>13.72</v>
       </c>
       <c r="F136" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -4101,20 +4101,20 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C137" t="n">
-        <v>11.25</v>
+        <v>11.67</v>
       </c>
       <c r="D137" t="n">
-        <v>9.609999999999999</v>
+        <v>9.93</v>
       </c>
       <c r="E137" t="n">
-        <v>13.19</v>
+        <v>13.51</v>
       </c>
       <c r="F137" t="n">
         <v>3.58</v>
@@ -4128,131 +4128,131 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C138" t="n">
-        <v>10.96</v>
+        <v>11.55</v>
       </c>
       <c r="D138" t="n">
-        <v>9.15</v>
+        <v>9.69</v>
       </c>
       <c r="E138" t="n">
-        <v>12.76</v>
+        <v>13.33</v>
       </c>
       <c r="F138" t="n">
-        <v>3.61</v>
+        <v>3.64</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C139" t="n">
-        <v>10.8</v>
+        <v>11.26</v>
       </c>
       <c r="D139" t="n">
-        <v>9.08</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="E139" t="n">
-        <v>12.61</v>
+        <v>13.03</v>
       </c>
       <c r="F139" t="n">
-        <v>3.53</v>
+        <v>3.58</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>Durante</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="C140" t="n">
-        <v>7.91</v>
+        <v>11.25</v>
       </c>
       <c r="D140" t="n">
-        <v>6.34</v>
+        <v>9.6</v>
       </c>
       <c r="E140" t="n">
-        <v>9.59</v>
+        <v>13.01</v>
       </c>
       <c r="F140" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="C141" t="n">
-        <v>7.96</v>
+        <v>11.25</v>
       </c>
       <c r="D141" t="n">
-        <v>6.48</v>
+        <v>9.6</v>
       </c>
       <c r="E141" t="n">
-        <v>9.68</v>
+        <v>13.01</v>
       </c>
       <c r="F141" t="n">
-        <v>3.21</v>
+        <v>3.41</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Después</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C142" t="n">
-        <v>7.78</v>
+        <v>7.6</v>
       </c>
       <c r="D142" t="n">
-        <v>6.17</v>
+        <v>5.96</v>
       </c>
       <c r="E142" t="n">
-        <v>9.51</v>
+        <v>9.34</v>
       </c>
       <c r="F142" t="n">
-        <v>3.34</v>
+        <v>3.39</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -4263,23 +4263,23 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="C143" t="n">
-        <v>7.03</v>
+        <v>7.5</v>
       </c>
       <c r="D143" t="n">
-        <v>5.55</v>
+        <v>5.98</v>
       </c>
       <c r="E143" t="n">
-        <v>8.65</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F143" t="n">
-        <v>3.11</v>
+        <v>3.32</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -4290,158 +4290,158 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C144" t="n">
-        <v>6.47</v>
+        <v>7.49</v>
       </c>
       <c r="D144" t="n">
-        <v>5.02</v>
+        <v>5.88</v>
       </c>
       <c r="E144" t="n">
-        <v>7.95</v>
+        <v>9.33</v>
       </c>
       <c r="F144" t="n">
-        <v>2.93</v>
+        <v>3.45</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C145" t="n">
-        <v>6.2</v>
+        <v>7.63</v>
       </c>
       <c r="D145" t="n">
-        <v>4.86</v>
+        <v>6.07</v>
       </c>
       <c r="E145" t="n">
-        <v>7.64</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="F145" t="n">
-        <v>2.79</v>
+        <v>3.29</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Moldova, Republic of</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="C146" t="n">
-        <v>11.42</v>
+        <v>8</v>
       </c>
       <c r="D146" t="n">
-        <v>9.390000000000001</v>
+        <v>6.47</v>
       </c>
       <c r="E146" t="n">
-        <v>13.65</v>
+        <v>9.65</v>
       </c>
       <c r="F146" t="n">
-        <v>4.26</v>
+        <v>3.17</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Durante</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Moldova, Republic of</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="C147" t="n">
-        <v>11.7</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="D147" t="n">
-        <v>9.789999999999999</v>
+        <v>6.77</v>
       </c>
       <c r="E147" t="n">
-        <v>13.87</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F147" t="n">
-        <v>4.09</v>
+        <v>3.03</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Moldova, Republic of</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="C148" t="n">
-        <v>11.88</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="D148" t="n">
-        <v>9.859999999999999</v>
+        <v>6.77</v>
       </c>
       <c r="E148" t="n">
-        <v>14.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F148" t="n">
-        <v>4.15</v>
+        <v>3.03</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Después</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Moldova, Republic of</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C149" t="n">
-        <v>12.32</v>
+        <v>11.38</v>
       </c>
       <c r="D149" t="n">
-        <v>10.34</v>
+        <v>9.69</v>
       </c>
       <c r="E149" t="n">
-        <v>14.5</v>
+        <v>13.17</v>
       </c>
       <c r="F149" t="n">
-        <v>4.16</v>
+        <v>3.47</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -4452,77 +4452,77 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Moldova, Republic of</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="C150" t="n">
-        <v>13.38</v>
+        <v>11.47</v>
       </c>
       <c r="D150" t="n">
-        <v>11.34</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="E150" t="n">
-        <v>15.5</v>
+        <v>13.24</v>
       </c>
       <c r="F150" t="n">
-        <v>4.15</v>
+        <v>3.61</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Moldova, Republic of</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C151" t="n">
-        <v>14.13</v>
+        <v>11.31</v>
       </c>
       <c r="D151" t="n">
-        <v>12.09</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="E151" t="n">
-        <v>16.29</v>
+        <v>13.1</v>
       </c>
       <c r="F151" t="n">
-        <v>4.19</v>
+        <v>3.47</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="C152" t="n">
-        <v>8.91</v>
+        <v>11.02</v>
       </c>
       <c r="D152" t="n">
-        <v>7.29</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="E152" t="n">
-        <v>10.74</v>
+        <v>12.86</v>
       </c>
       <c r="F152" t="n">
-        <v>3.45</v>
+        <v>3.64</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -4533,158 +4533,158 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="C153" t="n">
-        <v>9.15</v>
+        <v>10.63</v>
       </c>
       <c r="D153" t="n">
-        <v>7.42</v>
+        <v>8.84</v>
       </c>
       <c r="E153" t="n">
-        <v>10.97</v>
+        <v>12.33</v>
       </c>
       <c r="F153" t="n">
-        <v>3.55</v>
+        <v>3.49</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Durante</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="C154" t="n">
-        <v>9.23</v>
+        <v>10.55</v>
       </c>
       <c r="D154" t="n">
-        <v>7.55</v>
+        <v>8.73</v>
       </c>
       <c r="E154" t="n">
-        <v>10.98</v>
+        <v>12.2</v>
       </c>
       <c r="F154" t="n">
-        <v>3.43</v>
+        <v>3.47</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C155" t="n">
-        <v>8.77</v>
+        <v>10.55</v>
       </c>
       <c r="D155" t="n">
-        <v>7.02</v>
+        <v>8.73</v>
       </c>
       <c r="E155" t="n">
-        <v>10.5</v>
+        <v>12.2</v>
       </c>
       <c r="F155" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Después</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C156" t="n">
-        <v>8.32</v>
+        <v>7.74</v>
       </c>
       <c r="D156" t="n">
-        <v>6.66</v>
+        <v>6.52</v>
       </c>
       <c r="E156" t="n">
-        <v>9.9</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="F156" t="n">
-        <v>3.24</v>
+        <v>2.7</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C157" t="n">
         <v>8.01</v>
       </c>
       <c r="D157" t="n">
-        <v>6.47</v>
+        <v>6.74</v>
       </c>
       <c r="E157" t="n">
-        <v>9.65</v>
+        <v>9.42</v>
       </c>
       <c r="F157" t="n">
-        <v>3.18</v>
+        <v>2.68</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="C158" t="n">
-        <v>8.970000000000001</v>
+        <v>8.26</v>
       </c>
       <c r="D158" t="n">
-        <v>7.52</v>
+        <v>6.94</v>
       </c>
       <c r="E158" t="n">
-        <v>10.65</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="F158" t="n">
-        <v>3.14</v>
+        <v>2.77</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -4695,23 +4695,23 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="C159" t="n">
-        <v>8.970000000000001</v>
+        <v>8.26</v>
       </c>
       <c r="D159" t="n">
-        <v>7.55</v>
+        <v>6.84</v>
       </c>
       <c r="E159" t="n">
-        <v>10.53</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F159" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -4722,131 +4722,131 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="C160" t="n">
-        <v>8.94</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D160" t="n">
-        <v>7.32</v>
+        <v>6.82</v>
       </c>
       <c r="E160" t="n">
-        <v>10.57</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="F160" t="n">
-        <v>3.24</v>
+        <v>3.04</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Durante</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="C161" t="n">
-        <v>8.77</v>
+        <v>8.33</v>
       </c>
       <c r="D161" t="n">
-        <v>7.25</v>
+        <v>6.91</v>
       </c>
       <c r="E161" t="n">
-        <v>10.38</v>
+        <v>9.93</v>
       </c>
       <c r="F161" t="n">
-        <v>3.13</v>
+        <v>3.03</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="C162" t="n">
-        <v>8.710000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="D162" t="n">
-        <v>7.28</v>
+        <v>6.91</v>
       </c>
       <c r="E162" t="n">
-        <v>10.27</v>
+        <v>9.93</v>
       </c>
       <c r="F162" t="n">
-        <v>2.99</v>
+        <v>3.03</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>Después</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C163" t="n">
-        <v>8.699999999999999</v>
+        <v>4.45</v>
       </c>
       <c r="D163" t="n">
-        <v>7.19</v>
+        <v>3.45</v>
       </c>
       <c r="E163" t="n">
-        <v>10.23</v>
+        <v>5.7</v>
       </c>
       <c r="F163" t="n">
-        <v>3.04</v>
+        <v>2.25</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>North Macedonia</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="C164" t="n">
-        <v>5.53</v>
+        <v>4.75</v>
       </c>
       <c r="D164" t="n">
-        <v>4.21</v>
+        <v>3.53</v>
       </c>
       <c r="E164" t="n">
-        <v>6.98</v>
+        <v>6.02</v>
       </c>
       <c r="F164" t="n">
-        <v>2.77</v>
+        <v>2.49</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -4857,23 +4857,23 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>North Macedonia</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C165" t="n">
-        <v>5.27</v>
+        <v>4.79</v>
       </c>
       <c r="D165" t="n">
-        <v>3.99</v>
+        <v>3.48</v>
       </c>
       <c r="E165" t="n">
-        <v>6.69</v>
+        <v>6.05</v>
       </c>
       <c r="F165" t="n">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -4884,23 +4884,23 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>North Macedonia</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="C166" t="n">
-        <v>5.08</v>
+        <v>4.84</v>
       </c>
       <c r="D166" t="n">
-        <v>3.91</v>
+        <v>3.63</v>
       </c>
       <c r="E166" t="n">
-        <v>6.43</v>
+        <v>6.04</v>
       </c>
       <c r="F166" t="n">
-        <v>2.52</v>
+        <v>2.41</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -4911,77 +4911,77 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>North Macedonia</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C167" t="n">
-        <v>5.43</v>
+        <v>4.73</v>
       </c>
       <c r="D167" t="n">
-        <v>4.2</v>
+        <v>3.58</v>
       </c>
       <c r="E167" t="n">
-        <v>6.77</v>
+        <v>5.92</v>
       </c>
       <c r="F167" t="n">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Durante</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>North Macedonia</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C168" t="n">
-        <v>5.79</v>
+        <v>5.37</v>
       </c>
       <c r="D168" t="n">
-        <v>4.56</v>
+        <v>4.19</v>
       </c>
       <c r="E168" t="n">
-        <v>7.18</v>
+        <v>6.55</v>
       </c>
       <c r="F168" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>North Macedonia</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="B169" t="n">
         <v>2022</v>
       </c>
       <c r="C169" t="n">
-        <v>5.76</v>
+        <v>5.37</v>
       </c>
       <c r="D169" t="n">
-        <v>4.39</v>
+        <v>4.19</v>
       </c>
       <c r="E169" t="n">
-        <v>7.06</v>
+        <v>6.55</v>
       </c>
       <c r="F169" t="n">
-        <v>2.67</v>
+        <v>2.36</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -4992,23 +4992,23 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="B170" t="n">
         <v>2016</v>
       </c>
       <c r="C170" t="n">
-        <v>6.67</v>
+        <v>12.91</v>
       </c>
       <c r="D170" t="n">
-        <v>5.33</v>
+        <v>10.51</v>
       </c>
       <c r="E170" t="n">
-        <v>8.06</v>
+        <v>15.6</v>
       </c>
       <c r="F170" t="n">
-        <v>2.73</v>
+        <v>5.09</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -5019,23 +5019,23 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="B171" t="n">
         <v>2017</v>
       </c>
       <c r="C171" t="n">
-        <v>6.67</v>
+        <v>13.23</v>
       </c>
       <c r="D171" t="n">
-        <v>5.39</v>
+        <v>10.87</v>
       </c>
       <c r="E171" t="n">
-        <v>8.09</v>
+        <v>15.97</v>
       </c>
       <c r="F171" t="n">
-        <v>2.7</v>
+        <v>5.1</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -5046,23 +5046,23 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="B172" t="n">
         <v>2018</v>
       </c>
       <c r="C172" t="n">
-        <v>6.67</v>
+        <v>13.64</v>
       </c>
       <c r="D172" t="n">
-        <v>5.26</v>
+        <v>10.98</v>
       </c>
       <c r="E172" t="n">
-        <v>8.109999999999999</v>
+        <v>16.18</v>
       </c>
       <c r="F172" t="n">
-        <v>2.85</v>
+        <v>5.2</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -5073,23 +5073,23 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="B173" t="n">
         <v>2019</v>
       </c>
       <c r="C173" t="n">
-        <v>6.9</v>
+        <v>14.1</v>
       </c>
       <c r="D173" t="n">
-        <v>5.57</v>
+        <v>11.68</v>
       </c>
       <c r="E173" t="n">
-        <v>8.27</v>
+        <v>16.56</v>
       </c>
       <c r="F173" t="n">
-        <v>2.71</v>
+        <v>4.88</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -5100,23 +5100,23 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="B174" t="n">
         <v>2020</v>
       </c>
       <c r="C174" t="n">
-        <v>7.35</v>
+        <v>14.66</v>
       </c>
       <c r="D174" t="n">
-        <v>5.99</v>
+        <v>12.39</v>
       </c>
       <c r="E174" t="n">
-        <v>8.75</v>
+        <v>17.24</v>
       </c>
       <c r="F174" t="n">
-        <v>2.76</v>
+        <v>4.85</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -5127,77 +5127,77 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C175" t="n">
-        <v>7.48</v>
+        <v>14.73</v>
       </c>
       <c r="D175" t="n">
-        <v>6.14</v>
+        <v>12.63</v>
       </c>
       <c r="E175" t="n">
-        <v>8.970000000000001</v>
+        <v>17.3</v>
       </c>
       <c r="F175" t="n">
-        <v>2.83</v>
+        <v>4.67</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="C176" t="n">
-        <v>11.81</v>
+        <v>14.73</v>
       </c>
       <c r="D176" t="n">
-        <v>9.93</v>
+        <v>12.63</v>
       </c>
       <c r="E176" t="n">
-        <v>13.57</v>
+        <v>17.3</v>
       </c>
       <c r="F176" t="n">
-        <v>3.64</v>
+        <v>4.67</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Después</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="C177" t="n">
-        <v>11.83</v>
+        <v>12.48</v>
       </c>
       <c r="D177" t="n">
-        <v>10.02</v>
+        <v>10.42</v>
       </c>
       <c r="E177" t="n">
-        <v>13.85</v>
+        <v>14.45</v>
       </c>
       <c r="F177" t="n">
-        <v>3.83</v>
+        <v>4.02</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
@@ -5208,23 +5208,23 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C178" t="n">
-        <v>11.97</v>
+        <v>11.83</v>
       </c>
       <c r="D178" t="n">
-        <v>10.1</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="E178" t="n">
-        <v>13.96</v>
+        <v>13.76</v>
       </c>
       <c r="F178" t="n">
-        <v>3.86</v>
+        <v>3.79</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -5235,23 +5235,23 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C179" t="n">
-        <v>12.04</v>
+        <v>11.4</v>
       </c>
       <c r="D179" t="n">
-        <v>10.26</v>
+        <v>9.65</v>
       </c>
       <c r="E179" t="n">
-        <v>14.12</v>
+        <v>13.29</v>
       </c>
       <c r="F179" t="n">
-        <v>3.86</v>
+        <v>3.64</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
@@ -5262,131 +5262,131 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C180" t="n">
-        <v>12.11</v>
+        <v>11.43</v>
       </c>
       <c r="D180" t="n">
-        <v>10.35</v>
+        <v>9.76</v>
       </c>
       <c r="E180" t="n">
-        <v>14.05</v>
+        <v>13.35</v>
       </c>
       <c r="F180" t="n">
-        <v>3.71</v>
+        <v>3.59</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C181" t="n">
-        <v>11.92</v>
+        <v>11.98</v>
       </c>
       <c r="D181" t="n">
-        <v>10.15</v>
+        <v>10.18</v>
       </c>
       <c r="E181" t="n">
-        <v>13.87</v>
+        <v>13.83</v>
       </c>
       <c r="F181" t="n">
-        <v>3.72</v>
+        <v>3.65</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>Durante</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="C182" t="n">
-        <v>11.04</v>
+        <v>12.18</v>
       </c>
       <c r="D182" t="n">
-        <v>9.359999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="E182" t="n">
-        <v>12.83</v>
+        <v>14.02</v>
       </c>
       <c r="F182" t="n">
-        <v>3.47</v>
+        <v>3.51</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="C183" t="n">
-        <v>11.01</v>
+        <v>12.18</v>
       </c>
       <c r="D183" t="n">
-        <v>9.27</v>
+        <v>10.5</v>
       </c>
       <c r="E183" t="n">
-        <v>12.91</v>
+        <v>14.02</v>
       </c>
       <c r="F183" t="n">
-        <v>3.64</v>
+        <v>3.51</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Después</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C184" t="n">
-        <v>11.36</v>
+        <v>11.68</v>
       </c>
       <c r="D184" t="n">
-        <v>9.6</v>
+        <v>9.82</v>
       </c>
       <c r="E184" t="n">
-        <v>13.18</v>
+        <v>13.41</v>
       </c>
       <c r="F184" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
@@ -5397,23 +5397,23 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="C185" t="n">
-        <v>10.8</v>
+        <v>11.64</v>
       </c>
       <c r="D185" t="n">
-        <v>9.130000000000001</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="E185" t="n">
-        <v>12.42</v>
+        <v>13.49</v>
       </c>
       <c r="F185" t="n">
-        <v>3.29</v>
+        <v>3.6</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
@@ -5424,158 +5424,158 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C186" t="n">
-        <v>10.88</v>
+        <v>11.53</v>
       </c>
       <c r="D186" t="n">
-        <v>9.17</v>
+        <v>9.84</v>
       </c>
       <c r="E186" t="n">
-        <v>12.59</v>
+        <v>13.54</v>
       </c>
       <c r="F186" t="n">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C187" t="n">
-        <v>11.22</v>
+        <v>11.25</v>
       </c>
       <c r="D187" t="n">
-        <v>9.460000000000001</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="E187" t="n">
-        <v>12.97</v>
+        <v>13.19</v>
       </c>
       <c r="F187" t="n">
-        <v>3.52</v>
+        <v>3.58</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="C188" t="n">
-        <v>16.89</v>
+        <v>10.96</v>
       </c>
       <c r="D188" t="n">
-        <v>14.33</v>
+        <v>9.15</v>
       </c>
       <c r="E188" t="n">
-        <v>19.51</v>
+        <v>12.76</v>
       </c>
       <c r="F188" t="n">
-        <v>5.18</v>
+        <v>3.61</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Durante</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="C189" t="n">
-        <v>17.1</v>
+        <v>10.8</v>
       </c>
       <c r="D189" t="n">
-        <v>14.62</v>
+        <v>9.08</v>
       </c>
       <c r="E189" t="n">
-        <v>19.98</v>
+        <v>12.61</v>
       </c>
       <c r="F189" t="n">
-        <v>5.36</v>
+        <v>3.53</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="C190" t="n">
-        <v>17.22</v>
+        <v>10.8</v>
       </c>
       <c r="D190" t="n">
-        <v>14.72</v>
+        <v>9.08</v>
       </c>
       <c r="E190" t="n">
-        <v>19.81</v>
+        <v>12.61</v>
       </c>
       <c r="F190" t="n">
-        <v>5.09</v>
+        <v>3.53</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Después</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C191" t="n">
-        <v>17.11</v>
+        <v>7.91</v>
       </c>
       <c r="D191" t="n">
-        <v>14.51</v>
+        <v>6.34</v>
       </c>
       <c r="E191" t="n">
-        <v>19.85</v>
+        <v>9.59</v>
       </c>
       <c r="F191" t="n">
-        <v>5.34</v>
+        <v>3.25</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
@@ -5586,77 +5586,77 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="C192" t="n">
-        <v>17.09</v>
+        <v>7.96</v>
       </c>
       <c r="D192" t="n">
-        <v>14.33</v>
+        <v>6.48</v>
       </c>
       <c r="E192" t="n">
-        <v>19.57</v>
+        <v>9.68</v>
       </c>
       <c r="F192" t="n">
-        <v>5.24</v>
+        <v>3.21</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C193" t="n">
-        <v>17.06</v>
+        <v>7.78</v>
       </c>
       <c r="D193" t="n">
-        <v>14.56</v>
+        <v>6.17</v>
       </c>
       <c r="E193" t="n">
-        <v>19.79</v>
+        <v>9.51</v>
       </c>
       <c r="F193" t="n">
-        <v>5.23</v>
+        <v>3.34</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Russian Federation</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="C194" t="n">
-        <v>11.21</v>
+        <v>7.03</v>
       </c>
       <c r="D194" t="n">
-        <v>9.119999999999999</v>
+        <v>5.55</v>
       </c>
       <c r="E194" t="n">
-        <v>13.15</v>
+        <v>8.65</v>
       </c>
       <c r="F194" t="n">
-        <v>4.04</v>
+        <v>3.11</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -5667,158 +5667,158 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Russian Federation</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="C195" t="n">
-        <v>10.92</v>
+        <v>6.47</v>
       </c>
       <c r="D195" t="n">
-        <v>8.92</v>
+        <v>5.02</v>
       </c>
       <c r="E195" t="n">
-        <v>12.87</v>
+        <v>7.95</v>
       </c>
       <c r="F195" t="n">
-        <v>3.95</v>
+        <v>2.93</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Durante</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Russian Federation</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="C196" t="n">
-        <v>10.72</v>
+        <v>6.2</v>
       </c>
       <c r="D196" t="n">
-        <v>8.800000000000001</v>
+        <v>4.86</v>
       </c>
       <c r="E196" t="n">
-        <v>12.72</v>
+        <v>7.64</v>
       </c>
       <c r="F196" t="n">
-        <v>3.93</v>
+        <v>2.79</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Russian Federation</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C197" t="n">
-        <v>10.67</v>
+        <v>6.2</v>
       </c>
       <c r="D197" t="n">
-        <v>8.779999999999999</v>
+        <v>4.86</v>
       </c>
       <c r="E197" t="n">
-        <v>12.71</v>
+        <v>7.64</v>
       </c>
       <c r="F197" t="n">
-        <v>3.93</v>
+        <v>2.79</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Después</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Russian Federation</t>
+          <t>Montenegro</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C198" t="n">
-        <v>10.56</v>
+        <v>8.91</v>
       </c>
       <c r="D198" t="n">
-        <v>8.65</v>
+        <v>7.29</v>
       </c>
       <c r="E198" t="n">
-        <v>12.61</v>
+        <v>10.74</v>
       </c>
       <c r="F198" t="n">
-        <v>3.96</v>
+        <v>3.45</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Russian Federation</t>
+          <t>Montenegro</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C199" t="n">
-        <v>10.51</v>
+        <v>9.15</v>
       </c>
       <c r="D199" t="n">
-        <v>8.550000000000001</v>
+        <v>7.42</v>
       </c>
       <c r="E199" t="n">
-        <v>12.52</v>
+        <v>10.97</v>
       </c>
       <c r="F199" t="n">
-        <v>3.97</v>
+        <v>3.55</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Montenegro</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="C200" t="n">
-        <v>9.289999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="D200" t="n">
-        <v>7.65</v>
+        <v>7.55</v>
       </c>
       <c r="E200" t="n">
-        <v>11.04</v>
+        <v>10.98</v>
       </c>
       <c r="F200" t="n">
-        <v>3.38</v>
+        <v>3.43</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
@@ -5829,23 +5829,23 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Montenegro</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="C201" t="n">
-        <v>9.369999999999999</v>
+        <v>8.77</v>
       </c>
       <c r="D201" t="n">
-        <v>7.81</v>
+        <v>7.02</v>
       </c>
       <c r="E201" t="n">
-        <v>11.11</v>
+        <v>10.5</v>
       </c>
       <c r="F201" t="n">
-        <v>3.29</v>
+        <v>3.48</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
@@ -5856,131 +5856,131 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Montenegro</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="C202" t="n">
-        <v>9.43</v>
+        <v>8.32</v>
       </c>
       <c r="D202" t="n">
-        <v>7.86</v>
+        <v>6.66</v>
       </c>
       <c r="E202" t="n">
-        <v>11.08</v>
+        <v>9.9</v>
       </c>
       <c r="F202" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Durante</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Montenegro</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="C203" t="n">
-        <v>9.27</v>
+        <v>8.01</v>
       </c>
       <c r="D203" t="n">
-        <v>7.69</v>
+        <v>6.47</v>
       </c>
       <c r="E203" t="n">
-        <v>10.93</v>
+        <v>9.65</v>
       </c>
       <c r="F203" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Montenegro</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="C204" t="n">
-        <v>9.09</v>
+        <v>8.01</v>
       </c>
       <c r="D204" t="n">
-        <v>7.33</v>
+        <v>6.47</v>
       </c>
       <c r="E204" t="n">
-        <v>10.71</v>
+        <v>9.65</v>
       </c>
       <c r="F204" t="n">
-        <v>3.37</v>
+        <v>3.18</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>Después</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C205" t="n">
-        <v>9.029999999999999</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="D205" t="n">
-        <v>7.39</v>
+        <v>7.52</v>
       </c>
       <c r="E205" t="n">
-        <v>10.75</v>
+        <v>10.65</v>
       </c>
       <c r="F205" t="n">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="C206" t="n">
-        <v>11.09</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="D206" t="n">
-        <v>9.41</v>
+        <v>7.55</v>
       </c>
       <c r="E206" t="n">
-        <v>12.81</v>
+        <v>10.53</v>
       </c>
       <c r="F206" t="n">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
@@ -5991,23 +5991,23 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C207" t="n">
-        <v>11.03</v>
+        <v>8.94</v>
       </c>
       <c r="D207" t="n">
-        <v>9.23</v>
+        <v>7.32</v>
       </c>
       <c r="E207" t="n">
-        <v>12.82</v>
+        <v>10.57</v>
       </c>
       <c r="F207" t="n">
-        <v>3.59</v>
+        <v>3.24</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
@@ -6018,23 +6018,23 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="C208" t="n">
-        <v>11.19</v>
+        <v>8.77</v>
       </c>
       <c r="D208" t="n">
-        <v>9.48</v>
+        <v>7.25</v>
       </c>
       <c r="E208" t="n">
-        <v>12.91</v>
+        <v>10.38</v>
       </c>
       <c r="F208" t="n">
-        <v>3.42</v>
+        <v>3.13</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
@@ -6045,77 +6045,77 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C209" t="n">
-        <v>11.25</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="D209" t="n">
-        <v>9.49</v>
+        <v>7.28</v>
       </c>
       <c r="E209" t="n">
-        <v>12.93</v>
+        <v>10.27</v>
       </c>
       <c r="F209" t="n">
-        <v>3.43</v>
+        <v>2.99</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Durante</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C210" t="n">
-        <v>11.11</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D210" t="n">
-        <v>9.359999999999999</v>
+        <v>7.19</v>
       </c>
       <c r="E210" t="n">
-        <v>12.8</v>
+        <v>10.23</v>
       </c>
       <c r="F210" t="n">
-        <v>3.45</v>
+        <v>3.04</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B211" t="n">
         <v>2022</v>
       </c>
       <c r="C211" t="n">
-        <v>10.97</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D211" t="n">
-        <v>9.25</v>
+        <v>7.19</v>
       </c>
       <c r="E211" t="n">
-        <v>12.78</v>
+        <v>10.23</v>
       </c>
       <c r="F211" t="n">
-        <v>3.53</v>
+        <v>3.04</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
@@ -6126,23 +6126,23 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>North Macedonia</t>
         </is>
       </c>
       <c r="B212" t="n">
         <v>2016</v>
       </c>
       <c r="C212" t="n">
-        <v>11.53</v>
+        <v>5.53</v>
       </c>
       <c r="D212" t="n">
-        <v>9.75</v>
+        <v>4.21</v>
       </c>
       <c r="E212" t="n">
-        <v>13.36</v>
+        <v>6.98</v>
       </c>
       <c r="F212" t="n">
-        <v>3.6</v>
+        <v>2.77</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
@@ -6153,23 +6153,23 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>North Macedonia</t>
         </is>
       </c>
       <c r="B213" t="n">
         <v>2017</v>
       </c>
       <c r="C213" t="n">
-        <v>11</v>
+        <v>5.27</v>
       </c>
       <c r="D213" t="n">
-        <v>9.34</v>
+        <v>3.99</v>
       </c>
       <c r="E213" t="n">
-        <v>12.82</v>
+        <v>6.69</v>
       </c>
       <c r="F213" t="n">
-        <v>3.48</v>
+        <v>2.7</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
@@ -6180,23 +6180,23 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>North Macedonia</t>
         </is>
       </c>
       <c r="B214" t="n">
         <v>2018</v>
       </c>
       <c r="C214" t="n">
-        <v>11.15</v>
+        <v>5.08</v>
       </c>
       <c r="D214" t="n">
-        <v>9.4</v>
+        <v>3.91</v>
       </c>
       <c r="E214" t="n">
-        <v>13.02</v>
+        <v>6.43</v>
       </c>
       <c r="F214" t="n">
-        <v>3.62</v>
+        <v>2.52</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
@@ -6207,23 +6207,23 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>North Macedonia</t>
         </is>
       </c>
       <c r="B215" t="n">
         <v>2019</v>
       </c>
       <c r="C215" t="n">
-        <v>11.08</v>
+        <v>5.43</v>
       </c>
       <c r="D215" t="n">
-        <v>9.43</v>
+        <v>4.2</v>
       </c>
       <c r="E215" t="n">
-        <v>12.93</v>
+        <v>6.77</v>
       </c>
       <c r="F215" t="n">
-        <v>3.5</v>
+        <v>2.56</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
@@ -6234,23 +6234,23 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>North Macedonia</t>
         </is>
       </c>
       <c r="B216" t="n">
         <v>2020</v>
       </c>
       <c r="C216" t="n">
-        <v>11.29</v>
+        <v>5.79</v>
       </c>
       <c r="D216" t="n">
-        <v>9.56</v>
+        <v>4.56</v>
       </c>
       <c r="E216" t="n">
-        <v>13.24</v>
+        <v>7.18</v>
       </c>
       <c r="F216" t="n">
-        <v>3.67</v>
+        <v>2.62</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
@@ -6261,77 +6261,77 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>North Macedonia</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C217" t="n">
-        <v>10.9</v>
+        <v>5.76</v>
       </c>
       <c r="D217" t="n">
-        <v>9.119999999999999</v>
+        <v>4.39</v>
       </c>
       <c r="E217" t="n">
-        <v>12.63</v>
+        <v>7.06</v>
       </c>
       <c r="F217" t="n">
-        <v>3.51</v>
+        <v>2.67</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>North Macedonia</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="C218" t="n">
-        <v>11.36</v>
+        <v>5.76</v>
       </c>
       <c r="D218" t="n">
-        <v>9.69</v>
+        <v>4.39</v>
       </c>
       <c r="E218" t="n">
-        <v>13.16</v>
+        <v>7.06</v>
       </c>
       <c r="F218" t="n">
-        <v>3.47</v>
+        <v>2.67</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Después</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="C219" t="n">
-        <v>11.34</v>
+        <v>6.67</v>
       </c>
       <c r="D219" t="n">
-        <v>9.65</v>
+        <v>5.33</v>
       </c>
       <c r="E219" t="n">
-        <v>13.17</v>
+        <v>8.06</v>
       </c>
       <c r="F219" t="n">
-        <v>3.51</v>
+        <v>2.73</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
@@ -6342,23 +6342,23 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C220" t="n">
-        <v>11.27</v>
+        <v>6.67</v>
       </c>
       <c r="D220" t="n">
-        <v>9.56</v>
+        <v>5.39</v>
       </c>
       <c r="E220" t="n">
-        <v>13.27</v>
+        <v>8.09</v>
       </c>
       <c r="F220" t="n">
-        <v>3.71</v>
+        <v>2.7</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
@@ -6369,23 +6369,23 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C221" t="n">
-        <v>10.61</v>
+        <v>6.67</v>
       </c>
       <c r="D221" t="n">
-        <v>8.98</v>
+        <v>5.26</v>
       </c>
       <c r="E221" t="n">
-        <v>12.48</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="F221" t="n">
-        <v>3.5</v>
+        <v>2.85</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
@@ -6396,131 +6396,131 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C222" t="n">
-        <v>10.66</v>
+        <v>6.9</v>
       </c>
       <c r="D222" t="n">
-        <v>8.92</v>
+        <v>5.57</v>
       </c>
       <c r="E222" t="n">
-        <v>12.37</v>
+        <v>8.27</v>
       </c>
       <c r="F222" t="n">
-        <v>3.44</v>
+        <v>2.71</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C223" t="n">
-        <v>10.97</v>
+        <v>7.35</v>
       </c>
       <c r="D223" t="n">
-        <v>9.24</v>
+        <v>5.99</v>
       </c>
       <c r="E223" t="n">
-        <v>12.66</v>
+        <v>8.75</v>
       </c>
       <c r="F223" t="n">
-        <v>3.42</v>
+        <v>2.76</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>Durante</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="C224" t="n">
-        <v>9.449999999999999</v>
+        <v>7.48</v>
       </c>
       <c r="D224" t="n">
-        <v>7.59</v>
+        <v>6.14</v>
       </c>
       <c r="E224" t="n">
-        <v>11.35</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="F224" t="n">
-        <v>3.76</v>
+        <v>2.83</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="C225" t="n">
-        <v>9.44</v>
+        <v>7.48</v>
       </c>
       <c r="D225" t="n">
-        <v>7.59</v>
+        <v>6.14</v>
       </c>
       <c r="E225" t="n">
-        <v>11.34</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="F225" t="n">
-        <v>3.75</v>
+        <v>2.83</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Después</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C226" t="n">
-        <v>9.390000000000001</v>
+        <v>11.81</v>
       </c>
       <c r="D226" t="n">
-        <v>7.67</v>
+        <v>9.93</v>
       </c>
       <c r="E226" t="n">
-        <v>11.25</v>
+        <v>13.57</v>
       </c>
       <c r="F226" t="n">
-        <v>3.58</v>
+        <v>3.64</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
@@ -6531,23 +6531,23 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="C227" t="n">
-        <v>9.48</v>
+        <v>11.83</v>
       </c>
       <c r="D227" t="n">
-        <v>7.79</v>
+        <v>10.02</v>
       </c>
       <c r="E227" t="n">
-        <v>11.23</v>
+        <v>13.85</v>
       </c>
       <c r="F227" t="n">
-        <v>3.44</v>
+        <v>3.83</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
@@ -6558,158 +6558,158 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C228" t="n">
-        <v>9.539999999999999</v>
+        <v>11.97</v>
       </c>
       <c r="D228" t="n">
-        <v>7.88</v>
+        <v>10.1</v>
       </c>
       <c r="E228" t="n">
-        <v>11.34</v>
+        <v>13.96</v>
       </c>
       <c r="F228" t="n">
-        <v>3.46</v>
+        <v>3.86</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C229" t="n">
-        <v>9.609999999999999</v>
+        <v>12.04</v>
       </c>
       <c r="D229" t="n">
-        <v>7.78</v>
+        <v>10.26</v>
       </c>
       <c r="E229" t="n">
-        <v>11.39</v>
+        <v>14.12</v>
       </c>
       <c r="F229" t="n">
-        <v>3.61</v>
+        <v>3.86</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="C230" t="n">
-        <v>9.529999999999999</v>
+        <v>12.11</v>
       </c>
       <c r="D230" t="n">
-        <v>7.81</v>
+        <v>10.35</v>
       </c>
       <c r="E230" t="n">
-        <v>11.19</v>
+        <v>14.05</v>
       </c>
       <c r="F230" t="n">
-        <v>3.38</v>
+        <v>3.71</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Durante</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="C231" t="n">
-        <v>9.34</v>
+        <v>11.92</v>
       </c>
       <c r="D231" t="n">
-        <v>7.71</v>
+        <v>10.15</v>
       </c>
       <c r="E231" t="n">
-        <v>10.96</v>
+        <v>13.87</v>
       </c>
       <c r="F231" t="n">
-        <v>3.25</v>
+        <v>3.72</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="C232" t="n">
-        <v>9.289999999999999</v>
+        <v>11.92</v>
       </c>
       <c r="D232" t="n">
-        <v>7.7</v>
+        <v>10.15</v>
       </c>
       <c r="E232" t="n">
-        <v>11.03</v>
+        <v>13.87</v>
       </c>
       <c r="F232" t="n">
-        <v>3.32</v>
+        <v>3.72</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Después</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C233" t="n">
-        <v>9.24</v>
+        <v>11.04</v>
       </c>
       <c r="D233" t="n">
-        <v>7.58</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="E233" t="n">
-        <v>10.76</v>
+        <v>12.83</v>
       </c>
       <c r="F233" t="n">
-        <v>3.18</v>
+        <v>3.47</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
@@ -6720,77 +6720,77 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="C234" t="n">
-        <v>9.26</v>
+        <v>11.01</v>
       </c>
       <c r="D234" t="n">
-        <v>7.8</v>
+        <v>9.27</v>
       </c>
       <c r="E234" t="n">
-        <v>10.91</v>
+        <v>12.91</v>
       </c>
       <c r="F234" t="n">
-        <v>3.11</v>
+        <v>3.64</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C235" t="n">
-        <v>9.16</v>
+        <v>11.36</v>
       </c>
       <c r="D235" t="n">
-        <v>7.68</v>
+        <v>9.6</v>
       </c>
       <c r="E235" t="n">
-        <v>10.87</v>
+        <v>13.18</v>
       </c>
       <c r="F235" t="n">
-        <v>3.19</v>
+        <v>3.58</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="C236" t="n">
-        <v>8.99</v>
+        <v>10.8</v>
       </c>
       <c r="D236" t="n">
-        <v>7.3</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="E236" t="n">
-        <v>10.89</v>
+        <v>12.42</v>
       </c>
       <c r="F236" t="n">
-        <v>3.59</v>
+        <v>3.29</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
@@ -6801,158 +6801,158 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="C237" t="n">
-        <v>8.76</v>
+        <v>10.88</v>
       </c>
       <c r="D237" t="n">
-        <v>6.96</v>
+        <v>9.17</v>
       </c>
       <c r="E237" t="n">
-        <v>10.58</v>
+        <v>12.59</v>
       </c>
       <c r="F237" t="n">
-        <v>3.62</v>
+        <v>3.42</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Durante</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="C238" t="n">
-        <v>8.74</v>
+        <v>11.22</v>
       </c>
       <c r="D238" t="n">
-        <v>6.77</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="E238" t="n">
-        <v>10.53</v>
+        <v>12.97</v>
       </c>
       <c r="F238" t="n">
-        <v>3.76</v>
+        <v>3.52</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C239" t="n">
-        <v>8.99</v>
+        <v>11.22</v>
       </c>
       <c r="D239" t="n">
-        <v>7.21</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="E239" t="n">
-        <v>10.83</v>
+        <v>12.97</v>
       </c>
       <c r="F239" t="n">
-        <v>3.62</v>
+        <v>3.52</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Después</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C240" t="n">
-        <v>8.44</v>
+        <v>16.89</v>
       </c>
       <c r="D240" t="n">
-        <v>6.63</v>
+        <v>14.33</v>
       </c>
       <c r="E240" t="n">
-        <v>10.18</v>
+        <v>19.51</v>
       </c>
       <c r="F240" t="n">
-        <v>3.54</v>
+        <v>5.18</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C241" t="n">
-        <v>7.43</v>
+        <v>17.1</v>
       </c>
       <c r="D241" t="n">
-        <v>5.69</v>
+        <v>14.62</v>
       </c>
       <c r="E241" t="n">
-        <v>9.109999999999999</v>
+        <v>19.98</v>
       </c>
       <c r="F241" t="n">
-        <v>3.42</v>
+        <v>5.36</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Después</t>
+          <t>Antes</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="C242" t="n">
-        <v>10.59</v>
+        <v>17.22</v>
       </c>
       <c r="D242" t="n">
-        <v>8.92</v>
+        <v>14.72</v>
       </c>
       <c r="E242" t="n">
-        <v>12.53</v>
+        <v>19.81</v>
       </c>
       <c r="F242" t="n">
-        <v>3.61</v>
+        <v>5.09</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
@@ -6963,23 +6963,23 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="C243" t="n">
-        <v>10.71</v>
+        <v>17.11</v>
       </c>
       <c r="D243" t="n">
-        <v>9.050000000000001</v>
+        <v>14.51</v>
       </c>
       <c r="E243" t="n">
-        <v>12.42</v>
+        <v>19.85</v>
       </c>
       <c r="F243" t="n">
-        <v>3.37</v>
+        <v>5.34</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
@@ -6990,106 +6990,1969 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="C244" t="n">
-        <v>10.77</v>
+        <v>17.09</v>
       </c>
       <c r="D244" t="n">
-        <v>9.09</v>
+        <v>14.33</v>
       </c>
       <c r="E244" t="n">
-        <v>12.51</v>
+        <v>19.57</v>
       </c>
       <c r="F244" t="n">
-        <v>3.41</v>
+        <v>5.24</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>Durante</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="C245" t="n">
-        <v>10.74</v>
+        <v>17.06</v>
       </c>
       <c r="D245" t="n">
-        <v>9.119999999999999</v>
+        <v>14.56</v>
       </c>
       <c r="E245" t="n">
-        <v>12.45</v>
+        <v>19.79</v>
       </c>
       <c r="F245" t="n">
-        <v>3.33</v>
+        <v>5.23</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Antes</t>
+          <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="C246" t="n">
-        <v>10.79</v>
+        <v>17.06</v>
       </c>
       <c r="D246" t="n">
-        <v>9.029999999999999</v>
+        <v>14.56</v>
       </c>
       <c r="E246" t="n">
-        <v>12.59</v>
+        <v>19.79</v>
       </c>
       <c r="F246" t="n">
-        <v>3.56</v>
+        <v>5.23</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Durante</t>
+          <t>Después</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
+          <t>Russian Federation</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C247" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="D247" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="E247" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="F247" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Russian Federation</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C248" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="D248" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="E248" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="F248" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Russian Federation</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C249" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="D249" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="E249" t="n">
+        <v>12.72</v>
+      </c>
+      <c r="F249" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Russian Federation</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C250" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="D250" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="E250" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="F250" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Russian Federation</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C251" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="D251" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="E251" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="F251" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Russian Federation</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C252" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="D252" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="E252" t="n">
+        <v>12.52</v>
+      </c>
+      <c r="F252" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Russian Federation</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C253" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="D253" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="E253" t="n">
+        <v>12.52</v>
+      </c>
+      <c r="F253" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C254" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="D254" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="E254" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="F254" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C255" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="D255" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="E255" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="F255" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C256" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="D256" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="E256" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="F256" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C257" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="D257" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="E257" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="F257" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C258" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="D258" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="E258" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="F258" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C259" t="n">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="D259" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="E259" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="F259" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C260" t="n">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="D260" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="E260" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="F260" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C261" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="D261" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="E261" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="F261" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C262" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="D262" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="E262" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="F262" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C263" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="D263" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="E263" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="F263" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C264" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="D264" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="E264" t="n">
+        <v>12.93</v>
+      </c>
+      <c r="F264" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C265" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="D265" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="E265" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="F265" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C266" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="D266" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="E266" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="F266" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C267" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="D267" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="E267" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="F267" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C268" t="n">
+        <v>11.53</v>
+      </c>
+      <c r="D268" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="E268" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="F268" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C269" t="n">
+        <v>11</v>
+      </c>
+      <c r="D269" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="E269" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="F269" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C270" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="D270" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="E270" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="F270" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C271" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="D271" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="E271" t="n">
+        <v>12.93</v>
+      </c>
+      <c r="F271" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C272" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="D272" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="E272" t="n">
+        <v>13.24</v>
+      </c>
+      <c r="F272" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C273" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="D273" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="E273" t="n">
+        <v>12.63</v>
+      </c>
+      <c r="F273" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C274" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="D274" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="E274" t="n">
+        <v>12.63</v>
+      </c>
+      <c r="F274" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C275" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="D275" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="E275" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="F275" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C276" t="n">
+        <v>11.34</v>
+      </c>
+      <c r="D276" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="E276" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="F276" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C277" t="n">
+        <v>11.27</v>
+      </c>
+      <c r="D277" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="E277" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="F277" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C278" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="D278" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="E278" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="F278" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C279" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="D279" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="E279" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="F279" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C280" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="D280" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="E280" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="F280" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C281" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="D281" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="E281" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="F281" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C282" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="D282" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="E282" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="F282" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C283" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="D283" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="E283" t="n">
+        <v>11.34</v>
+      </c>
+      <c r="F283" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C284" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="D284" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="E284" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="F284" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C285" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="D285" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="E285" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="F285" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C286" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="D286" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="E286" t="n">
+        <v>11.34</v>
+      </c>
+      <c r="F286" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C287" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="D287" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="E287" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="F287" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C288" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="D288" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="E288" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="F288" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C289" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="D289" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="E289" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="F289" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C290" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="D290" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="E290" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="F290" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C291" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="D291" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E291" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="F291" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C292" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="D292" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="E292" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="F292" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C293" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="D293" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="E293" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="F293" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C294" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="D294" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="E294" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="F294" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C295" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="D295" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="E295" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="F295" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C296" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="D296" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="E296" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="F296" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C297" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="D297" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="E297" t="n">
+        <v>3</v>
+      </c>
+      <c r="F297" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C298" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="D298" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="E298" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="F298" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C299" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="D299" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="E299" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="F299" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C300" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="D300" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E300" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="F300" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C301" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D301" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E301" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="F301" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C302" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D302" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E302" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="F302" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C303" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="D303" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E303" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="F303" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C304" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="D304" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="E304" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="F304" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C305" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="D305" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="E305" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="F305" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C306" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="D306" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="E306" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="F306" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C307" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="D307" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="E307" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="F307" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C308" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="D308" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="E308" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="F308" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C309" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="D309" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="E309" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="F309" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B247" t="n">
+      <c r="B310" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C310" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="D310" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="E310" t="n">
+        <v>12.53</v>
+      </c>
+      <c r="F310" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C311" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="D311" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="E311" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="F311" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C312" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="D312" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="E312" t="n">
+        <v>12.51</v>
+      </c>
+      <c r="F312" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C313" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="D313" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="E313" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="F313" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C314" t="n">
+        <v>10.79</v>
+      </c>
+      <c r="D314" t="n">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="E314" t="n">
+        <v>12.59</v>
+      </c>
+      <c r="F314" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>Durante</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C315" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="D315" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E315" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="F315" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
         <v>2022</v>
       </c>
-      <c r="C247" t="n">
+      <c r="C316" t="n">
         <v>10.86</v>
       </c>
-      <c r="D247" t="n">
+      <c r="D316" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="E247" t="n">
+      <c r="E316" t="n">
         <v>12.56</v>
       </c>
-      <c r="F247" t="n">
+      <c r="F316" t="n">
         <v>3.36</v>
       </c>
-      <c r="G247" t="inlineStr">
+      <c r="G316" t="inlineStr">
         <is>
           <t>Después</t>
         </is>

--- a/alcohol_filtrado.xlsx
+++ b/alcohol_filtrado.xlsx
@@ -645,23 +645,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Andorra</t>
+          <t>Alemania</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2016</v>
       </c>
       <c r="C9" t="n">
-        <v>11.9</v>
+        <v>11.93</v>
       </c>
       <c r="D9" t="n">
-        <v>9.92</v>
+        <v>10.15</v>
       </c>
       <c r="E9" t="n">
-        <v>13.83</v>
+        <v>13.7</v>
       </c>
       <c r="F9" t="n">
-        <v>3.91</v>
+        <v>3.56</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -672,23 +672,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Andorra</t>
+          <t>Alemania</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2017</v>
       </c>
       <c r="C10" t="n">
-        <v>11.83</v>
+        <v>11.92</v>
       </c>
       <c r="D10" t="n">
-        <v>9.970000000000001</v>
+        <v>10.25</v>
       </c>
       <c r="E10" t="n">
-        <v>13.74</v>
+        <v>13.64</v>
       </c>
       <c r="F10" t="n">
-        <v>3.77</v>
+        <v>3.39</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -699,23 +699,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Andorra</t>
+          <t>Alemania</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2018</v>
       </c>
       <c r="C11" t="n">
-        <v>11.75</v>
+        <v>11.76</v>
       </c>
       <c r="D11" t="n">
-        <v>9.83</v>
+        <v>10.1</v>
       </c>
       <c r="E11" t="n">
-        <v>13.58</v>
+        <v>13.47</v>
       </c>
       <c r="F11" t="n">
-        <v>3.74</v>
+        <v>3.37</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -726,23 +726,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Andorra</t>
+          <t>Alemania</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2019</v>
       </c>
       <c r="C12" t="n">
-        <v>11.18</v>
+        <v>11.57</v>
       </c>
       <c r="D12" t="n">
-        <v>9.49</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>12.92</v>
+        <v>13.42</v>
       </c>
       <c r="F12" t="n">
-        <v>3.42</v>
+        <v>3.55</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -753,23 +753,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Andorra</t>
+          <t>Alemania</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2020</v>
       </c>
       <c r="C13" t="n">
-        <v>11.02</v>
+        <v>11.31</v>
       </c>
       <c r="D13" t="n">
-        <v>9.41</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>12.68</v>
+        <v>13.21</v>
       </c>
       <c r="F13" t="n">
-        <v>3.26</v>
+        <v>3.6</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -780,23 +780,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Andorra</t>
+          <t>Alemania</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2021</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06</v>
+        <v>11.24</v>
       </c>
       <c r="D14" t="n">
-        <v>9.369999999999999</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>12.77</v>
+        <v>12.92</v>
       </c>
       <c r="F14" t="n">
-        <v>3.41</v>
+        <v>3.47</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -807,23 +807,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Andorra</t>
+          <t>Alemania</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>2022</v>
       </c>
       <c r="C15" t="n">
-        <v>11.06</v>
+        <v>11.24</v>
       </c>
       <c r="D15" t="n">
-        <v>9.369999999999999</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>12.77</v>
+        <v>12.92</v>
       </c>
       <c r="F15" t="n">
-        <v>3.41</v>
+        <v>3.47</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -834,23 +834,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Andorra</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2016</v>
       </c>
       <c r="C16" t="n">
-        <v>5.01</v>
+        <v>11.9</v>
       </c>
       <c r="D16" t="n">
-        <v>3.84</v>
+        <v>9.92</v>
       </c>
       <c r="E16" t="n">
-        <v>6.3</v>
+        <v>13.83</v>
       </c>
       <c r="F16" t="n">
-        <v>2.46</v>
+        <v>3.91</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -861,23 +861,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Andorra</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2017</v>
       </c>
       <c r="C17" t="n">
-        <v>5.02</v>
+        <v>11.83</v>
       </c>
       <c r="D17" t="n">
-        <v>3.84</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>6.35</v>
+        <v>13.74</v>
       </c>
       <c r="F17" t="n">
-        <v>2.51</v>
+        <v>3.77</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -888,23 +888,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Andorra</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2018</v>
       </c>
       <c r="C18" t="n">
-        <v>5.17</v>
+        <v>11.75</v>
       </c>
       <c r="D18" t="n">
-        <v>3.97</v>
+        <v>9.83</v>
       </c>
       <c r="E18" t="n">
-        <v>6.48</v>
+        <v>13.58</v>
       </c>
       <c r="F18" t="n">
-        <v>2.51</v>
+        <v>3.74</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Andorra</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2019</v>
       </c>
       <c r="C19" t="n">
-        <v>4.97</v>
+        <v>11.18</v>
       </c>
       <c r="D19" t="n">
-        <v>3.81</v>
+        <v>9.49</v>
       </c>
       <c r="E19" t="n">
-        <v>6.29</v>
+        <v>12.92</v>
       </c>
       <c r="F19" t="n">
-        <v>2.48</v>
+        <v>3.42</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -942,23 +942,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Andorra</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>2020</v>
       </c>
       <c r="C20" t="n">
-        <v>4.7</v>
+        <v>11.02</v>
       </c>
       <c r="D20" t="n">
-        <v>3.52</v>
+        <v>9.41</v>
       </c>
       <c r="E20" t="n">
-        <v>5.95</v>
+        <v>12.68</v>
       </c>
       <c r="F20" t="n">
-        <v>2.43</v>
+        <v>3.26</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -969,23 +969,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Andorra</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2021</v>
       </c>
       <c r="C21" t="n">
-        <v>4.3</v>
+        <v>11.06</v>
       </c>
       <c r="D21" t="n">
-        <v>3.2</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>5.51</v>
+        <v>12.77</v>
       </c>
       <c r="F21" t="n">
-        <v>2.31</v>
+        <v>3.41</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -996,23 +996,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Andorra</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>2022</v>
       </c>
       <c r="C22" t="n">
-        <v>4.3</v>
+        <v>11.06</v>
       </c>
       <c r="D22" t="n">
-        <v>3.2</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>5.51</v>
+        <v>12.77</v>
       </c>
       <c r="F22" t="n">
-        <v>2.31</v>
+        <v>3.41</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1023,23 +1023,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>2016</v>
       </c>
       <c r="C23" t="n">
-        <v>11.7</v>
+        <v>5.01</v>
       </c>
       <c r="D23" t="n">
-        <v>9.890000000000001</v>
+        <v>3.84</v>
       </c>
       <c r="E23" t="n">
-        <v>13.71</v>
+        <v>6.3</v>
       </c>
       <c r="F23" t="n">
-        <v>3.82</v>
+        <v>2.46</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1050,23 +1050,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>2017</v>
       </c>
       <c r="C24" t="n">
-        <v>11.77</v>
+        <v>5.02</v>
       </c>
       <c r="D24" t="n">
-        <v>9.859999999999999</v>
+        <v>3.84</v>
       </c>
       <c r="E24" t="n">
-        <v>13.84</v>
+        <v>6.35</v>
       </c>
       <c r="F24" t="n">
-        <v>3.98</v>
+        <v>2.51</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1077,23 +1077,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>2018</v>
       </c>
       <c r="C25" t="n">
-        <v>11.83</v>
+        <v>5.17</v>
       </c>
       <c r="D25" t="n">
-        <v>10.05</v>
+        <v>3.97</v>
       </c>
       <c r="E25" t="n">
-        <v>13.97</v>
+        <v>6.48</v>
       </c>
       <c r="F25" t="n">
-        <v>3.93</v>
+        <v>2.51</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1104,23 +1104,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>2019</v>
       </c>
       <c r="C26" t="n">
-        <v>11.85</v>
+        <v>4.97</v>
       </c>
       <c r="D26" t="n">
-        <v>10.06</v>
+        <v>3.81</v>
       </c>
       <c r="E26" t="n">
-        <v>14.02</v>
+        <v>6.29</v>
       </c>
       <c r="F26" t="n">
-        <v>3.97</v>
+        <v>2.48</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1131,23 +1131,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>2020</v>
       </c>
       <c r="C27" t="n">
-        <v>11.88</v>
+        <v>4.7</v>
       </c>
       <c r="D27" t="n">
-        <v>10.21</v>
+        <v>3.52</v>
       </c>
       <c r="E27" t="n">
-        <v>13.72</v>
+        <v>5.95</v>
       </c>
       <c r="F27" t="n">
-        <v>3.51</v>
+        <v>2.43</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1158,23 +1158,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>2021</v>
       </c>
       <c r="C28" t="n">
-        <v>11.85</v>
+        <v>4.3</v>
       </c>
       <c r="D28" t="n">
-        <v>10.17</v>
+        <v>3.2</v>
       </c>
       <c r="E28" t="n">
-        <v>13.65</v>
+        <v>5.51</v>
       </c>
       <c r="F28" t="n">
-        <v>3.49</v>
+        <v>2.31</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1185,23 +1185,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>2022</v>
       </c>
       <c r="C29" t="n">
-        <v>11.85</v>
+        <v>4.3</v>
       </c>
       <c r="D29" t="n">
-        <v>10.17</v>
+        <v>3.2</v>
       </c>
       <c r="E29" t="n">
-        <v>13.65</v>
+        <v>5.51</v>
       </c>
       <c r="F29" t="n">
-        <v>3.49</v>
+        <v>2.31</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1212,23 +1212,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>2016</v>
       </c>
       <c r="C30" t="n">
-        <v>1.57</v>
+        <v>11.7</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8100000000000001</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>2.5</v>
+        <v>13.71</v>
       </c>
       <c r="F30" t="n">
-        <v>1.69</v>
+        <v>3.82</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1239,23 +1239,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>2017</v>
       </c>
       <c r="C31" t="n">
-        <v>1.69</v>
+        <v>11.77</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>2.63</v>
+        <v>13.84</v>
       </c>
       <c r="F31" t="n">
-        <v>1.74</v>
+        <v>3.98</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1266,23 +1266,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>2018</v>
       </c>
       <c r="C32" t="n">
-        <v>2.02</v>
+        <v>11.83</v>
       </c>
       <c r="D32" t="n">
-        <v>1.17</v>
+        <v>10.05</v>
       </c>
       <c r="E32" t="n">
-        <v>2.93</v>
+        <v>13.97</v>
       </c>
       <c r="F32" t="n">
-        <v>1.75</v>
+        <v>3.93</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1293,23 +1293,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>2019</v>
       </c>
       <c r="C33" t="n">
-        <v>2.3</v>
+        <v>11.85</v>
       </c>
       <c r="D33" t="n">
-        <v>1.39</v>
+        <v>10.06</v>
       </c>
       <c r="E33" t="n">
-        <v>3.26</v>
+        <v>14.02</v>
       </c>
       <c r="F33" t="n">
-        <v>1.87</v>
+        <v>3.97</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1320,23 +1320,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>2020</v>
       </c>
       <c r="C34" t="n">
-        <v>2.44</v>
+        <v>11.88</v>
       </c>
       <c r="D34" t="n">
-        <v>1.56</v>
+        <v>10.21</v>
       </c>
       <c r="E34" t="n">
-        <v>3.48</v>
+        <v>13.72</v>
       </c>
       <c r="F34" t="n">
-        <v>1.92</v>
+        <v>3.51</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1347,23 +1347,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>2021</v>
       </c>
       <c r="C35" t="n">
-        <v>2.32</v>
+        <v>11.85</v>
       </c>
       <c r="D35" t="n">
-        <v>1.46</v>
+        <v>10.17</v>
       </c>
       <c r="E35" t="n">
-        <v>3.28</v>
+        <v>13.65</v>
       </c>
       <c r="F35" t="n">
-        <v>1.82</v>
+        <v>3.49</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1374,23 +1374,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>2022</v>
       </c>
       <c r="C36" t="n">
-        <v>2.32</v>
+        <v>11.85</v>
       </c>
       <c r="D36" t="n">
-        <v>1.46</v>
+        <v>10.17</v>
       </c>
       <c r="E36" t="n">
-        <v>3.28</v>
+        <v>13.65</v>
       </c>
       <c r="F36" t="n">
-        <v>1.82</v>
+        <v>3.49</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1401,23 +1401,23 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Belarus</t>
+          <t>Azerbaiyán</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>2016</v>
       </c>
       <c r="C37" t="n">
-        <v>10.14</v>
+        <v>1.57</v>
       </c>
       <c r="D37" t="n">
-        <v>8.52</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>11.85</v>
+        <v>2.5</v>
       </c>
       <c r="F37" t="n">
-        <v>3.33</v>
+        <v>1.69</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1428,23 +1428,23 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Belarus</t>
+          <t>Azerbaiyán</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>2017</v>
       </c>
       <c r="C38" t="n">
-        <v>10.19</v>
+        <v>1.69</v>
       </c>
       <c r="D38" t="n">
-        <v>8.57</v>
+        <v>0.9</v>
       </c>
       <c r="E38" t="n">
-        <v>11.85</v>
+        <v>2.63</v>
       </c>
       <c r="F38" t="n">
-        <v>3.29</v>
+        <v>1.74</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1455,23 +1455,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Belarus</t>
+          <t>Azerbaiyán</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>2018</v>
       </c>
       <c r="C39" t="n">
-        <v>10.45</v>
+        <v>2.02</v>
       </c>
       <c r="D39" t="n">
-        <v>8.69</v>
+        <v>1.17</v>
       </c>
       <c r="E39" t="n">
-        <v>12.07</v>
+        <v>2.93</v>
       </c>
       <c r="F39" t="n">
-        <v>3.38</v>
+        <v>1.75</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1482,23 +1482,23 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Belarus</t>
+          <t>Azerbaiyán</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>2019</v>
       </c>
       <c r="C40" t="n">
-        <v>10.82</v>
+        <v>2.3</v>
       </c>
       <c r="D40" t="n">
-        <v>9.119999999999999</v>
+        <v>1.39</v>
       </c>
       <c r="E40" t="n">
-        <v>12.55</v>
+        <v>3.26</v>
       </c>
       <c r="F40" t="n">
-        <v>3.43</v>
+        <v>1.87</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1509,23 +1509,23 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Belarus</t>
+          <t>Azerbaiyán</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>2020</v>
       </c>
       <c r="C41" t="n">
-        <v>11.2</v>
+        <v>2.44</v>
       </c>
       <c r="D41" t="n">
-        <v>9.44</v>
+        <v>1.56</v>
       </c>
       <c r="E41" t="n">
-        <v>13.1</v>
+        <v>3.48</v>
       </c>
       <c r="F41" t="n">
-        <v>3.66</v>
+        <v>1.92</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1536,23 +1536,23 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Belarus</t>
+          <t>Azerbaiyán</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>2021</v>
       </c>
       <c r="C42" t="n">
-        <v>11.4</v>
+        <v>2.32</v>
       </c>
       <c r="D42" t="n">
-        <v>9.76</v>
+        <v>1.46</v>
       </c>
       <c r="E42" t="n">
-        <v>13.17</v>
+        <v>3.28</v>
       </c>
       <c r="F42" t="n">
-        <v>3.42</v>
+        <v>1.82</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1563,23 +1563,23 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Belarus</t>
+          <t>Azerbaiyán</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>2022</v>
       </c>
       <c r="C43" t="n">
-        <v>11.4</v>
+        <v>2.32</v>
       </c>
       <c r="D43" t="n">
-        <v>9.76</v>
+        <v>1.46</v>
       </c>
       <c r="E43" t="n">
-        <v>13.17</v>
+        <v>3.28</v>
       </c>
       <c r="F43" t="n">
-        <v>3.42</v>
+        <v>1.82</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1590,23 +1590,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Bielorrusia</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>2016</v>
       </c>
       <c r="C44" t="n">
-        <v>10.39</v>
+        <v>10.14</v>
       </c>
       <c r="D44" t="n">
-        <v>8.82</v>
+        <v>8.52</v>
       </c>
       <c r="E44" t="n">
-        <v>12.02</v>
+        <v>11.85</v>
       </c>
       <c r="F44" t="n">
-        <v>3.2</v>
+        <v>3.33</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1617,23 +1617,23 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Bielorrusia</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>2017</v>
       </c>
       <c r="C45" t="n">
-        <v>10.02</v>
+        <v>10.19</v>
       </c>
       <c r="D45" t="n">
-        <v>8.460000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="E45" t="n">
-        <v>11.56</v>
+        <v>11.85</v>
       </c>
       <c r="F45" t="n">
-        <v>3.1</v>
+        <v>3.29</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1644,23 +1644,23 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Bielorrusia</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>2018</v>
       </c>
       <c r="C46" t="n">
-        <v>9.91</v>
+        <v>10.45</v>
       </c>
       <c r="D46" t="n">
-        <v>8.289999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="E46" t="n">
-        <v>11.5</v>
+        <v>12.07</v>
       </c>
       <c r="F46" t="n">
-        <v>3.21</v>
+        <v>3.38</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1671,23 +1671,23 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Bielorrusia</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>2019</v>
       </c>
       <c r="C47" t="n">
-        <v>9.609999999999999</v>
+        <v>10.82</v>
       </c>
       <c r="D47" t="n">
-        <v>8.06</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>11.4</v>
+        <v>12.55</v>
       </c>
       <c r="F47" t="n">
-        <v>3.34</v>
+        <v>3.43</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1698,23 +1698,23 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Bielorrusia</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>2020</v>
       </c>
       <c r="C48" t="n">
-        <v>9.220000000000001</v>
+        <v>11.2</v>
       </c>
       <c r="D48" t="n">
-        <v>7.53</v>
+        <v>9.44</v>
       </c>
       <c r="E48" t="n">
-        <v>10.82</v>
+        <v>13.1</v>
       </c>
       <c r="F48" t="n">
-        <v>3.3</v>
+        <v>3.66</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1725,23 +1725,23 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Bielorrusia</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>2021</v>
       </c>
       <c r="C49" t="n">
-        <v>8.74</v>
+        <v>11.4</v>
       </c>
       <c r="D49" t="n">
-        <v>7.2</v>
+        <v>9.76</v>
       </c>
       <c r="E49" t="n">
-        <v>10.27</v>
+        <v>13.17</v>
       </c>
       <c r="F49" t="n">
-        <v>3.07</v>
+        <v>3.42</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -1752,23 +1752,23 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Bielorrusia</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>2022</v>
       </c>
       <c r="C50" t="n">
-        <v>8.74</v>
+        <v>11.4</v>
       </c>
       <c r="D50" t="n">
-        <v>7.2</v>
+        <v>9.76</v>
       </c>
       <c r="E50" t="n">
-        <v>10.27</v>
+        <v>13.17</v>
       </c>
       <c r="F50" t="n">
-        <v>3.07</v>
+        <v>3.42</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Bosnia y Herzegovina</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -1806,7 +1806,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Bosnia y Herzegovina</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -1833,7 +1833,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Bosnia y Herzegovina</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -1860,7 +1860,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Bosnia y Herzegovina</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -1887,7 +1887,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Bosnia y Herzegovina</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -1914,7 +1914,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Bosnia y Herzegovina</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -1941,7 +1941,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Bosnia y Herzegovina</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2157,23 +2157,23 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Bélgica</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>2016</v>
       </c>
       <c r="C65" t="n">
-        <v>10.62</v>
+        <v>10.39</v>
       </c>
       <c r="D65" t="n">
-        <v>8.779999999999999</v>
+        <v>8.82</v>
       </c>
       <c r="E65" t="n">
-        <v>12.6</v>
+        <v>12.02</v>
       </c>
       <c r="F65" t="n">
-        <v>3.82</v>
+        <v>3.2</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2184,23 +2184,23 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Bélgica</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>2017</v>
       </c>
       <c r="C66" t="n">
-        <v>10.59</v>
+        <v>10.02</v>
       </c>
       <c r="D66" t="n">
-        <v>8.83</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="E66" t="n">
-        <v>12.41</v>
+        <v>11.56</v>
       </c>
       <c r="F66" t="n">
-        <v>3.59</v>
+        <v>3.1</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2211,23 +2211,23 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Bélgica</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>2018</v>
       </c>
       <c r="C67" t="n">
-        <v>10.71</v>
+        <v>9.91</v>
       </c>
       <c r="D67" t="n">
-        <v>8.9</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="E67" t="n">
-        <v>12.51</v>
+        <v>11.5</v>
       </c>
       <c r="F67" t="n">
-        <v>3.61</v>
+        <v>3.21</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2238,23 +2238,23 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Bélgica</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>2019</v>
       </c>
       <c r="C68" t="n">
-        <v>10.75</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="D68" t="n">
-        <v>8.91</v>
+        <v>8.06</v>
       </c>
       <c r="E68" t="n">
-        <v>12.6</v>
+        <v>11.4</v>
       </c>
       <c r="F68" t="n">
-        <v>3.69</v>
+        <v>3.34</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2265,23 +2265,23 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Bélgica</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>2020</v>
       </c>
       <c r="C69" t="n">
-        <v>10.81</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="D69" t="n">
-        <v>9.07</v>
+        <v>7.53</v>
       </c>
       <c r="E69" t="n">
-        <v>12.74</v>
+        <v>10.82</v>
       </c>
       <c r="F69" t="n">
-        <v>3.67</v>
+        <v>3.3</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2292,23 +2292,23 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Bélgica</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>2021</v>
       </c>
       <c r="C70" t="n">
-        <v>10.85</v>
+        <v>8.74</v>
       </c>
       <c r="D70" t="n">
-        <v>9.140000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="E70" t="n">
-        <v>12.78</v>
+        <v>10.27</v>
       </c>
       <c r="F70" t="n">
-        <v>3.65</v>
+        <v>3.07</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2319,23 +2319,23 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Bélgica</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>2022</v>
       </c>
       <c r="C71" t="n">
-        <v>10.85</v>
+        <v>8.74</v>
       </c>
       <c r="D71" t="n">
-        <v>9.140000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="E71" t="n">
-        <v>12.78</v>
+        <v>10.27</v>
       </c>
       <c r="F71" t="n">
-        <v>3.65</v>
+        <v>3.07</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2346,23 +2346,23 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Chequia</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>2016</v>
       </c>
       <c r="C72" t="n">
-        <v>5.98</v>
+        <v>13.66</v>
       </c>
       <c r="D72" t="n">
-        <v>4.55</v>
+        <v>11.86</v>
       </c>
       <c r="E72" t="n">
-        <v>7.44</v>
+        <v>15.7</v>
       </c>
       <c r="F72" t="n">
-        <v>2.89</v>
+        <v>3.85</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2373,23 +2373,23 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Chequia</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>2017</v>
       </c>
       <c r="C73" t="n">
-        <v>6.12</v>
+        <v>13.73</v>
       </c>
       <c r="D73" t="n">
-        <v>4.63</v>
+        <v>11.96</v>
       </c>
       <c r="E73" t="n">
-        <v>7.8</v>
+        <v>15.74</v>
       </c>
       <c r="F73" t="n">
-        <v>3.17</v>
+        <v>3.78</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -2400,23 +2400,23 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Chequia</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>2018</v>
       </c>
       <c r="C74" t="n">
-        <v>6.13</v>
+        <v>13.77</v>
       </c>
       <c r="D74" t="n">
-        <v>4.65</v>
+        <v>11.95</v>
       </c>
       <c r="E74" t="n">
-        <v>7.67</v>
+        <v>15.67</v>
       </c>
       <c r="F74" t="n">
-        <v>3.02</v>
+        <v>3.72</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -2427,23 +2427,23 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Chequia</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>2019</v>
       </c>
       <c r="C75" t="n">
-        <v>5.79</v>
+        <v>13.75</v>
       </c>
       <c r="D75" t="n">
-        <v>4.41</v>
+        <v>11.92</v>
       </c>
       <c r="E75" t="n">
-        <v>7.31</v>
+        <v>15.81</v>
       </c>
       <c r="F75" t="n">
-        <v>2.9</v>
+        <v>3.89</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -2454,23 +2454,23 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Chequia</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>2020</v>
       </c>
       <c r="C76" t="n">
-        <v>5.39</v>
+        <v>13.64</v>
       </c>
       <c r="D76" t="n">
-        <v>4.07</v>
+        <v>11.92</v>
       </c>
       <c r="E76" t="n">
-        <v>6.76</v>
+        <v>15.52</v>
       </c>
       <c r="F76" t="n">
-        <v>2.68</v>
+        <v>3.6</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2481,23 +2481,23 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Chequia</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>2021</v>
       </c>
       <c r="C77" t="n">
-        <v>5.21</v>
+        <v>13.68</v>
       </c>
       <c r="D77" t="n">
-        <v>3.98</v>
+        <v>11.81</v>
       </c>
       <c r="E77" t="n">
-        <v>6.53</v>
+        <v>15.58</v>
       </c>
       <c r="F77" t="n">
-        <v>2.55</v>
+        <v>3.77</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -2508,23 +2508,23 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Chequia</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>2022</v>
       </c>
       <c r="C78" t="n">
-        <v>5.21</v>
+        <v>13.68</v>
       </c>
       <c r="D78" t="n">
-        <v>3.98</v>
+        <v>11.81</v>
       </c>
       <c r="E78" t="n">
-        <v>6.53</v>
+        <v>15.58</v>
       </c>
       <c r="F78" t="n">
-        <v>2.55</v>
+        <v>3.77</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -2535,23 +2535,23 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Chipre</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>2016</v>
       </c>
       <c r="C79" t="n">
-        <v>13.66</v>
+        <v>5.98</v>
       </c>
       <c r="D79" t="n">
-        <v>11.86</v>
+        <v>4.55</v>
       </c>
       <c r="E79" t="n">
-        <v>15.7</v>
+        <v>7.44</v>
       </c>
       <c r="F79" t="n">
-        <v>3.85</v>
+        <v>2.89</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -2562,23 +2562,23 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Chipre</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>2017</v>
       </c>
       <c r="C80" t="n">
-        <v>13.73</v>
+        <v>6.12</v>
       </c>
       <c r="D80" t="n">
-        <v>11.96</v>
+        <v>4.63</v>
       </c>
       <c r="E80" t="n">
-        <v>15.74</v>
+        <v>7.8</v>
       </c>
       <c r="F80" t="n">
-        <v>3.78</v>
+        <v>3.17</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -2589,23 +2589,23 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Chipre</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>2018</v>
       </c>
       <c r="C81" t="n">
-        <v>13.77</v>
+        <v>6.13</v>
       </c>
       <c r="D81" t="n">
-        <v>11.95</v>
+        <v>4.65</v>
       </c>
       <c r="E81" t="n">
-        <v>15.67</v>
+        <v>7.67</v>
       </c>
       <c r="F81" t="n">
-        <v>3.72</v>
+        <v>3.02</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -2616,23 +2616,23 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Chipre</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>2019</v>
       </c>
       <c r="C82" t="n">
-        <v>13.75</v>
+        <v>5.79</v>
       </c>
       <c r="D82" t="n">
-        <v>11.92</v>
+        <v>4.41</v>
       </c>
       <c r="E82" t="n">
-        <v>15.81</v>
+        <v>7.31</v>
       </c>
       <c r="F82" t="n">
-        <v>3.89</v>
+        <v>2.9</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -2643,23 +2643,23 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Chipre</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>2020</v>
       </c>
       <c r="C83" t="n">
-        <v>13.64</v>
+        <v>5.39</v>
       </c>
       <c r="D83" t="n">
-        <v>11.92</v>
+        <v>4.07</v>
       </c>
       <c r="E83" t="n">
-        <v>15.52</v>
+        <v>6.76</v>
       </c>
       <c r="F83" t="n">
-        <v>3.6</v>
+        <v>2.68</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -2670,23 +2670,23 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Chipre</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>2021</v>
       </c>
       <c r="C84" t="n">
-        <v>13.68</v>
+        <v>5.21</v>
       </c>
       <c r="D84" t="n">
-        <v>11.81</v>
+        <v>3.98</v>
       </c>
       <c r="E84" t="n">
-        <v>15.58</v>
+        <v>6.53</v>
       </c>
       <c r="F84" t="n">
-        <v>3.77</v>
+        <v>2.55</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -2697,23 +2697,23 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Chipre</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>2022</v>
       </c>
       <c r="C85" t="n">
-        <v>13.68</v>
+        <v>5.21</v>
       </c>
       <c r="D85" t="n">
-        <v>11.81</v>
+        <v>3.98</v>
       </c>
       <c r="E85" t="n">
-        <v>15.58</v>
+        <v>6.53</v>
       </c>
       <c r="F85" t="n">
-        <v>3.77</v>
+        <v>2.55</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -2724,23 +2724,23 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Croacia</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>2016</v>
       </c>
       <c r="C86" t="n">
-        <v>9.859999999999999</v>
+        <v>10.62</v>
       </c>
       <c r="D86" t="n">
-        <v>8.25</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="E86" t="n">
-        <v>11.79</v>
+        <v>12.6</v>
       </c>
       <c r="F86" t="n">
-        <v>3.53</v>
+        <v>3.82</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -2751,23 +2751,23 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Croacia</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>2017</v>
       </c>
       <c r="C87" t="n">
-        <v>9.82</v>
+        <v>10.59</v>
       </c>
       <c r="D87" t="n">
-        <v>8.09</v>
+        <v>8.83</v>
       </c>
       <c r="E87" t="n">
-        <v>11.68</v>
+        <v>12.41</v>
       </c>
       <c r="F87" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -2778,23 +2778,23 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Croacia</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>2018</v>
       </c>
       <c r="C88" t="n">
-        <v>9.67</v>
+        <v>10.71</v>
       </c>
       <c r="D88" t="n">
-        <v>7.99</v>
+        <v>8.9</v>
       </c>
       <c r="E88" t="n">
-        <v>11.44</v>
+        <v>12.51</v>
       </c>
       <c r="F88" t="n">
-        <v>3.45</v>
+        <v>3.61</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -2805,23 +2805,23 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Croacia</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>2019</v>
       </c>
       <c r="C89" t="n">
-        <v>9.710000000000001</v>
+        <v>10.75</v>
       </c>
       <c r="D89" t="n">
-        <v>8.109999999999999</v>
+        <v>8.91</v>
       </c>
       <c r="E89" t="n">
-        <v>11.43</v>
+        <v>12.6</v>
       </c>
       <c r="F89" t="n">
-        <v>3.32</v>
+        <v>3.69</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -2832,23 +2832,23 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Croacia</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>2020</v>
       </c>
       <c r="C90" t="n">
-        <v>9.93</v>
+        <v>10.81</v>
       </c>
       <c r="D90" t="n">
-        <v>8.279999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="E90" t="n">
-        <v>11.64</v>
+        <v>12.74</v>
       </c>
       <c r="F90" t="n">
-        <v>3.35</v>
+        <v>3.67</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -2859,23 +2859,23 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Croacia</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>2021</v>
       </c>
       <c r="C91" t="n">
-        <v>9.970000000000001</v>
+        <v>10.85</v>
       </c>
       <c r="D91" t="n">
-        <v>8.359999999999999</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E91" t="n">
-        <v>11.77</v>
+        <v>12.78</v>
       </c>
       <c r="F91" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -2886,23 +2886,23 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Croacia</t>
         </is>
       </c>
       <c r="B92" t="n">
         <v>2022</v>
       </c>
       <c r="C92" t="n">
-        <v>9.970000000000001</v>
+        <v>10.85</v>
       </c>
       <c r="D92" t="n">
-        <v>8.359999999999999</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E92" t="n">
-        <v>11.77</v>
+        <v>12.78</v>
       </c>
       <c r="F92" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -2913,23 +2913,23 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Dinamarca</t>
         </is>
       </c>
       <c r="B93" t="n">
         <v>2016</v>
       </c>
       <c r="C93" t="n">
-        <v>10.18</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="D93" t="n">
-        <v>7.2</v>
+        <v>8.25</v>
       </c>
       <c r="E93" t="n">
-        <v>13.14</v>
+        <v>11.79</v>
       </c>
       <c r="F93" t="n">
-        <v>5.94</v>
+        <v>3.53</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -2940,23 +2940,23 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Dinamarca</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>2017</v>
       </c>
       <c r="C94" t="n">
-        <v>8.98</v>
+        <v>9.82</v>
       </c>
       <c r="D94" t="n">
-        <v>6.29</v>
+        <v>8.09</v>
       </c>
       <c r="E94" t="n">
-        <v>11.73</v>
+        <v>11.68</v>
       </c>
       <c r="F94" t="n">
-        <v>5.44</v>
+        <v>3.6</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -2967,23 +2967,23 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Dinamarca</t>
         </is>
       </c>
       <c r="B95" t="n">
         <v>2018</v>
       </c>
       <c r="C95" t="n">
-        <v>8.17</v>
+        <v>9.67</v>
       </c>
       <c r="D95" t="n">
-        <v>5.67</v>
+        <v>7.99</v>
       </c>
       <c r="E95" t="n">
-        <v>10.77</v>
+        <v>11.44</v>
       </c>
       <c r="F95" t="n">
-        <v>5.1</v>
+        <v>3.45</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -2994,23 +2994,23 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Dinamarca</t>
         </is>
       </c>
       <c r="B96" t="n">
         <v>2019</v>
       </c>
       <c r="C96" t="n">
-        <v>8.5</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="D96" t="n">
-        <v>6.19</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="E96" t="n">
-        <v>10.83</v>
+        <v>11.43</v>
       </c>
       <c r="F96" t="n">
-        <v>4.64</v>
+        <v>3.32</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -3021,23 +3021,23 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Dinamarca</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>2020</v>
       </c>
       <c r="C97" t="n">
-        <v>9.68</v>
+        <v>9.93</v>
       </c>
       <c r="D97" t="n">
-        <v>7.32</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="E97" t="n">
-        <v>12.13</v>
+        <v>11.64</v>
       </c>
       <c r="F97" t="n">
-        <v>4.82</v>
+        <v>3.35</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -3048,23 +3048,23 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Dinamarca</t>
         </is>
       </c>
       <c r="B98" t="n">
         <v>2021</v>
       </c>
       <c r="C98" t="n">
-        <v>10.49</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="D98" t="n">
-        <v>8.17</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="E98" t="n">
-        <v>12.89</v>
+        <v>11.77</v>
       </c>
       <c r="F98" t="n">
-        <v>4.72</v>
+        <v>3.4</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -3075,23 +3075,23 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Dinamarca</t>
         </is>
       </c>
       <c r="B99" t="n">
         <v>2022</v>
       </c>
       <c r="C99" t="n">
-        <v>10.49</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="D99" t="n">
-        <v>8.17</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="E99" t="n">
-        <v>12.89</v>
+        <v>11.77</v>
       </c>
       <c r="F99" t="n">
-        <v>4.72</v>
+        <v>3.4</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -3102,23 +3102,23 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Eslovaquia</t>
         </is>
       </c>
       <c r="B100" t="n">
         <v>2016</v>
       </c>
       <c r="C100" t="n">
-        <v>11.22</v>
+        <v>11.09</v>
       </c>
       <c r="D100" t="n">
-        <v>9.33</v>
+        <v>9.41</v>
       </c>
       <c r="E100" t="n">
-        <v>13.14</v>
+        <v>12.81</v>
       </c>
       <c r="F100" t="n">
-        <v>3.81</v>
+        <v>3.4</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -3129,23 +3129,23 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Eslovaquia</t>
         </is>
       </c>
       <c r="B101" t="n">
         <v>2017</v>
       </c>
       <c r="C101" t="n">
-        <v>11.07</v>
+        <v>11.03</v>
       </c>
       <c r="D101" t="n">
-        <v>9.210000000000001</v>
+        <v>9.23</v>
       </c>
       <c r="E101" t="n">
-        <v>13.11</v>
+        <v>12.82</v>
       </c>
       <c r="F101" t="n">
-        <v>3.9</v>
+        <v>3.59</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -3156,23 +3156,23 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Eslovaquia</t>
         </is>
       </c>
       <c r="B102" t="n">
         <v>2018</v>
       </c>
       <c r="C102" t="n">
-        <v>10.81</v>
+        <v>11.19</v>
       </c>
       <c r="D102" t="n">
-        <v>8.99</v>
+        <v>9.48</v>
       </c>
       <c r="E102" t="n">
-        <v>12.78</v>
+        <v>12.91</v>
       </c>
       <c r="F102" t="n">
-        <v>3.79</v>
+        <v>3.42</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -3183,23 +3183,23 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Eslovaquia</t>
         </is>
       </c>
       <c r="B103" t="n">
         <v>2019</v>
       </c>
       <c r="C103" t="n">
-        <v>10.38</v>
+        <v>11.25</v>
       </c>
       <c r="D103" t="n">
-        <v>8.52</v>
+        <v>9.49</v>
       </c>
       <c r="E103" t="n">
-        <v>12.38</v>
+        <v>12.93</v>
       </c>
       <c r="F103" t="n">
-        <v>3.86</v>
+        <v>3.43</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -3210,23 +3210,23 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Eslovaquia</t>
         </is>
       </c>
       <c r="B104" t="n">
         <v>2020</v>
       </c>
       <c r="C104" t="n">
-        <v>9.84</v>
+        <v>11.11</v>
       </c>
       <c r="D104" t="n">
-        <v>8.19</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="E104" t="n">
-        <v>11.79</v>
+        <v>12.8</v>
       </c>
       <c r="F104" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -3237,23 +3237,23 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Eslovaquia</t>
         </is>
       </c>
       <c r="B105" t="n">
         <v>2021</v>
       </c>
       <c r="C105" t="n">
-        <v>9.51</v>
+        <v>10.97</v>
       </c>
       <c r="D105" t="n">
-        <v>7.78</v>
+        <v>9.25</v>
       </c>
       <c r="E105" t="n">
-        <v>11.19</v>
+        <v>12.78</v>
       </c>
       <c r="F105" t="n">
-        <v>3.4</v>
+        <v>3.53</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -3264,23 +3264,23 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Eslovaquia</t>
         </is>
       </c>
       <c r="B106" t="n">
         <v>2022</v>
       </c>
       <c r="C106" t="n">
-        <v>9.51</v>
+        <v>10.97</v>
       </c>
       <c r="D106" t="n">
-        <v>7.78</v>
+        <v>9.25</v>
       </c>
       <c r="E106" t="n">
-        <v>11.19</v>
+        <v>12.78</v>
       </c>
       <c r="F106" t="n">
-        <v>3.4</v>
+        <v>3.53</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -3291,23 +3291,23 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Eslovenia</t>
         </is>
       </c>
       <c r="B107" t="n">
         <v>2016</v>
       </c>
       <c r="C107" t="n">
-        <v>12.41</v>
+        <v>11.53</v>
       </c>
       <c r="D107" t="n">
-        <v>10.65</v>
+        <v>9.75</v>
       </c>
       <c r="E107" t="n">
-        <v>14.24</v>
+        <v>13.36</v>
       </c>
       <c r="F107" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -3318,23 +3318,23 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Eslovenia</t>
         </is>
       </c>
       <c r="B108" t="n">
         <v>2017</v>
       </c>
       <c r="C108" t="n">
-        <v>12.3</v>
+        <v>11</v>
       </c>
       <c r="D108" t="n">
-        <v>10.35</v>
+        <v>9.34</v>
       </c>
       <c r="E108" t="n">
-        <v>14.12</v>
+        <v>12.82</v>
       </c>
       <c r="F108" t="n">
-        <v>3.77</v>
+        <v>3.48</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -3345,23 +3345,23 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Eslovenia</t>
         </is>
       </c>
       <c r="B109" t="n">
         <v>2018</v>
       </c>
       <c r="C109" t="n">
-        <v>12.19</v>
+        <v>11.15</v>
       </c>
       <c r="D109" t="n">
-        <v>10.28</v>
+        <v>9.4</v>
       </c>
       <c r="E109" t="n">
-        <v>14.04</v>
+        <v>13.02</v>
       </c>
       <c r="F109" t="n">
-        <v>3.77</v>
+        <v>3.62</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -3372,23 +3372,23 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Eslovenia</t>
         </is>
       </c>
       <c r="B110" t="n">
         <v>2019</v>
       </c>
       <c r="C110" t="n">
-        <v>11.76</v>
+        <v>11.08</v>
       </c>
       <c r="D110" t="n">
-        <v>9.99</v>
+        <v>9.43</v>
       </c>
       <c r="E110" t="n">
-        <v>13.59</v>
+        <v>12.93</v>
       </c>
       <c r="F110" t="n">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -3399,23 +3399,23 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Eslovenia</t>
         </is>
       </c>
       <c r="B111" t="n">
         <v>2020</v>
       </c>
       <c r="C111" t="n">
-        <v>11.43</v>
+        <v>11.29</v>
       </c>
       <c r="D111" t="n">
-        <v>9.6</v>
+        <v>9.56</v>
       </c>
       <c r="E111" t="n">
         <v>13.24</v>
       </c>
       <c r="F111" t="n">
-        <v>3.64</v>
+        <v>3.67</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -3426,23 +3426,23 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Eslovenia</t>
         </is>
       </c>
       <c r="B112" t="n">
         <v>2021</v>
       </c>
       <c r="C112" t="n">
-        <v>11.2</v>
+        <v>10.9</v>
       </c>
       <c r="D112" t="n">
-        <v>9.460000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="E112" t="n">
-        <v>13.05</v>
+        <v>12.63</v>
       </c>
       <c r="F112" t="n">
-        <v>3.59</v>
+        <v>3.51</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -3453,23 +3453,23 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Eslovenia</t>
         </is>
       </c>
       <c r="B113" t="n">
         <v>2022</v>
       </c>
       <c r="C113" t="n">
-        <v>11.2</v>
+        <v>10.9</v>
       </c>
       <c r="D113" t="n">
-        <v>9.460000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="E113" t="n">
-        <v>13.05</v>
+        <v>12.63</v>
       </c>
       <c r="F113" t="n">
-        <v>3.59</v>
+        <v>3.51</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -3480,23 +3480,23 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>España</t>
         </is>
       </c>
       <c r="B114" t="n">
         <v>2016</v>
       </c>
       <c r="C114" t="n">
-        <v>14.65</v>
+        <v>11.36</v>
       </c>
       <c r="D114" t="n">
-        <v>12.16</v>
+        <v>9.69</v>
       </c>
       <c r="E114" t="n">
-        <v>17.21</v>
+        <v>13.16</v>
       </c>
       <c r="F114" t="n">
-        <v>5.05</v>
+        <v>3.47</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -3507,23 +3507,23 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>España</t>
         </is>
       </c>
       <c r="B115" t="n">
         <v>2017</v>
       </c>
       <c r="C115" t="n">
-        <v>14.63</v>
+        <v>11.34</v>
       </c>
       <c r="D115" t="n">
-        <v>12.18</v>
+        <v>9.65</v>
       </c>
       <c r="E115" t="n">
-        <v>17.15</v>
+        <v>13.17</v>
       </c>
       <c r="F115" t="n">
-        <v>4.97</v>
+        <v>3.51</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -3534,23 +3534,23 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>España</t>
         </is>
       </c>
       <c r="B116" t="n">
         <v>2018</v>
       </c>
       <c r="C116" t="n">
-        <v>15.02</v>
+        <v>11.27</v>
       </c>
       <c r="D116" t="n">
-        <v>12.28</v>
+        <v>9.56</v>
       </c>
       <c r="E116" t="n">
-        <v>17.43</v>
+        <v>13.27</v>
       </c>
       <c r="F116" t="n">
-        <v>5.15</v>
+        <v>3.71</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -3561,23 +3561,23 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>España</t>
         </is>
       </c>
       <c r="B117" t="n">
         <v>2019</v>
       </c>
       <c r="C117" t="n">
-        <v>15.57</v>
+        <v>10.61</v>
       </c>
       <c r="D117" t="n">
-        <v>12.91</v>
+        <v>8.98</v>
       </c>
       <c r="E117" t="n">
-        <v>18.39</v>
+        <v>12.48</v>
       </c>
       <c r="F117" t="n">
-        <v>5.48</v>
+        <v>3.5</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -3588,23 +3588,23 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>España</t>
         </is>
       </c>
       <c r="B118" t="n">
         <v>2020</v>
       </c>
       <c r="C118" t="n">
-        <v>15.88</v>
+        <v>10.66</v>
       </c>
       <c r="D118" t="n">
-        <v>13.26</v>
+        <v>8.92</v>
       </c>
       <c r="E118" t="n">
-        <v>18.42</v>
+        <v>12.37</v>
       </c>
       <c r="F118" t="n">
-        <v>5.16</v>
+        <v>3.44</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -3615,23 +3615,23 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>España</t>
         </is>
       </c>
       <c r="B119" t="n">
         <v>2021</v>
       </c>
       <c r="C119" t="n">
-        <v>15.54</v>
+        <v>10.97</v>
       </c>
       <c r="D119" t="n">
-        <v>12.89</v>
+        <v>9.24</v>
       </c>
       <c r="E119" t="n">
-        <v>17.89</v>
+        <v>12.66</v>
       </c>
       <c r="F119" t="n">
-        <v>5</v>
+        <v>3.42</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -3642,23 +3642,23 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>España</t>
         </is>
       </c>
       <c r="B120" t="n">
         <v>2022</v>
       </c>
       <c r="C120" t="n">
-        <v>15.54</v>
+        <v>10.97</v>
       </c>
       <c r="D120" t="n">
-        <v>12.89</v>
+        <v>9.24</v>
       </c>
       <c r="E120" t="n">
-        <v>17.89</v>
+        <v>12.66</v>
       </c>
       <c r="F120" t="n">
-        <v>5</v>
+        <v>3.42</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -3669,23 +3669,23 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="B121" t="n">
         <v>2016</v>
       </c>
       <c r="C121" t="n">
-        <v>11.93</v>
+        <v>10.18</v>
       </c>
       <c r="D121" t="n">
-        <v>10.15</v>
+        <v>7.2</v>
       </c>
       <c r="E121" t="n">
-        <v>13.7</v>
+        <v>13.14</v>
       </c>
       <c r="F121" t="n">
-        <v>3.56</v>
+        <v>5.94</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -3696,23 +3696,23 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="B122" t="n">
         <v>2017</v>
       </c>
       <c r="C122" t="n">
-        <v>11.92</v>
+        <v>8.98</v>
       </c>
       <c r="D122" t="n">
-        <v>10.25</v>
+        <v>6.29</v>
       </c>
       <c r="E122" t="n">
-        <v>13.64</v>
+        <v>11.73</v>
       </c>
       <c r="F122" t="n">
-        <v>3.39</v>
+        <v>5.44</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -3723,23 +3723,23 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="B123" t="n">
         <v>2018</v>
       </c>
       <c r="C123" t="n">
-        <v>11.76</v>
+        <v>8.17</v>
       </c>
       <c r="D123" t="n">
-        <v>10.1</v>
+        <v>5.67</v>
       </c>
       <c r="E123" t="n">
-        <v>13.47</v>
+        <v>10.77</v>
       </c>
       <c r="F123" t="n">
-        <v>3.37</v>
+        <v>5.1</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -3750,23 +3750,23 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="B124" t="n">
         <v>2019</v>
       </c>
       <c r="C124" t="n">
-        <v>11.57</v>
+        <v>8.5</v>
       </c>
       <c r="D124" t="n">
-        <v>9.869999999999999</v>
+        <v>6.19</v>
       </c>
       <c r="E124" t="n">
-        <v>13.42</v>
+        <v>10.83</v>
       </c>
       <c r="F124" t="n">
-        <v>3.55</v>
+        <v>4.64</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -3777,23 +3777,23 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="B125" t="n">
         <v>2020</v>
       </c>
       <c r="C125" t="n">
-        <v>11.31</v>
+        <v>9.68</v>
       </c>
       <c r="D125" t="n">
-        <v>9.609999999999999</v>
+        <v>7.32</v>
       </c>
       <c r="E125" t="n">
-        <v>13.21</v>
+        <v>12.13</v>
       </c>
       <c r="F125" t="n">
-        <v>3.6</v>
+        <v>4.82</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -3804,23 +3804,23 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="B126" t="n">
         <v>2021</v>
       </c>
       <c r="C126" t="n">
-        <v>11.24</v>
+        <v>10.49</v>
       </c>
       <c r="D126" t="n">
-        <v>9.449999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="E126" t="n">
-        <v>12.92</v>
+        <v>12.89</v>
       </c>
       <c r="F126" t="n">
-        <v>3.47</v>
+        <v>4.72</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -3831,23 +3831,23 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="B127" t="n">
         <v>2022</v>
       </c>
       <c r="C127" t="n">
-        <v>11.24</v>
+        <v>10.49</v>
       </c>
       <c r="D127" t="n">
-        <v>9.449999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="E127" t="n">
-        <v>12.92</v>
+        <v>12.89</v>
       </c>
       <c r="F127" t="n">
-        <v>3.47</v>
+        <v>4.72</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -3858,23 +3858,23 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Federación de Rusia</t>
         </is>
       </c>
       <c r="B128" t="n">
         <v>2016</v>
       </c>
       <c r="C128" t="n">
-        <v>7.44</v>
+        <v>11.21</v>
       </c>
       <c r="D128" t="n">
-        <v>5.94</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="E128" t="n">
-        <v>9</v>
+        <v>13.15</v>
       </c>
       <c r="F128" t="n">
-        <v>3.06</v>
+        <v>4.04</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -3885,23 +3885,23 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Federación de Rusia</t>
         </is>
       </c>
       <c r="B129" t="n">
         <v>2017</v>
       </c>
       <c r="C129" t="n">
-        <v>7.37</v>
+        <v>10.92</v>
       </c>
       <c r="D129" t="n">
-        <v>5.82</v>
+        <v>8.92</v>
       </c>
       <c r="E129" t="n">
-        <v>8.859999999999999</v>
+        <v>12.87</v>
       </c>
       <c r="F129" t="n">
-        <v>3.04</v>
+        <v>3.95</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -3912,23 +3912,23 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Federación de Rusia</t>
         </is>
       </c>
       <c r="B130" t="n">
         <v>2018</v>
       </c>
       <c r="C130" t="n">
-        <v>7.29</v>
+        <v>10.72</v>
       </c>
       <c r="D130" t="n">
-        <v>5.82</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E130" t="n">
-        <v>8.74</v>
+        <v>12.72</v>
       </c>
       <c r="F130" t="n">
-        <v>2.92</v>
+        <v>3.93</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -3939,23 +3939,23 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Federación de Rusia</t>
         </is>
       </c>
       <c r="B131" t="n">
         <v>2019</v>
       </c>
       <c r="C131" t="n">
-        <v>7.01</v>
+        <v>10.67</v>
       </c>
       <c r="D131" t="n">
-        <v>5.54</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="E131" t="n">
-        <v>8.57</v>
+        <v>12.71</v>
       </c>
       <c r="F131" t="n">
-        <v>3.04</v>
+        <v>3.93</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -3966,23 +3966,23 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Federación de Rusia</t>
         </is>
       </c>
       <c r="B132" t="n">
         <v>2020</v>
       </c>
       <c r="C132" t="n">
-        <v>6.96</v>
+        <v>10.56</v>
       </c>
       <c r="D132" t="n">
-        <v>5.53</v>
+        <v>8.65</v>
       </c>
       <c r="E132" t="n">
-        <v>8.41</v>
+        <v>12.61</v>
       </c>
       <c r="F132" t="n">
-        <v>2.88</v>
+        <v>3.96</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -3993,23 +3993,23 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Federación de Rusia</t>
         </is>
       </c>
       <c r="B133" t="n">
         <v>2021</v>
       </c>
       <c r="C133" t="n">
-        <v>6.98</v>
+        <v>10.51</v>
       </c>
       <c r="D133" t="n">
-        <v>5.54</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="E133" t="n">
-        <v>8.44</v>
+        <v>12.52</v>
       </c>
       <c r="F133" t="n">
-        <v>2.9</v>
+        <v>3.97</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -4020,23 +4020,23 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Federación de Rusia</t>
         </is>
       </c>
       <c r="B134" t="n">
         <v>2022</v>
       </c>
       <c r="C134" t="n">
-        <v>6.98</v>
+        <v>10.51</v>
       </c>
       <c r="D134" t="n">
-        <v>5.54</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="E134" t="n">
-        <v>8.44</v>
+        <v>12.52</v>
       </c>
       <c r="F134" t="n">
-        <v>2.9</v>
+        <v>3.97</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -4047,23 +4047,23 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Finlandia</t>
         </is>
       </c>
       <c r="B135" t="n">
         <v>2016</v>
       </c>
       <c r="C135" t="n">
-        <v>11.76</v>
+        <v>11.22</v>
       </c>
       <c r="D135" t="n">
-        <v>9.960000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="E135" t="n">
-        <v>13.46</v>
+        <v>13.14</v>
       </c>
       <c r="F135" t="n">
-        <v>3.5</v>
+        <v>3.81</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -4074,23 +4074,23 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Finlandia</t>
         </is>
       </c>
       <c r="B136" t="n">
         <v>2017</v>
       </c>
       <c r="C136" t="n">
-        <v>11.87</v>
+        <v>11.07</v>
       </c>
       <c r="D136" t="n">
-        <v>10.05</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="E136" t="n">
-        <v>13.72</v>
+        <v>13.11</v>
       </c>
       <c r="F136" t="n">
-        <v>3.67</v>
+        <v>3.9</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -4101,23 +4101,23 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Finlandia</t>
         </is>
       </c>
       <c r="B137" t="n">
         <v>2018</v>
       </c>
       <c r="C137" t="n">
-        <v>11.67</v>
+        <v>10.81</v>
       </c>
       <c r="D137" t="n">
-        <v>9.93</v>
+        <v>8.99</v>
       </c>
       <c r="E137" t="n">
-        <v>13.51</v>
+        <v>12.78</v>
       </c>
       <c r="F137" t="n">
-        <v>3.58</v>
+        <v>3.79</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -4128,23 +4128,23 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Finlandia</t>
         </is>
       </c>
       <c r="B138" t="n">
         <v>2019</v>
       </c>
       <c r="C138" t="n">
-        <v>11.55</v>
+        <v>10.38</v>
       </c>
       <c r="D138" t="n">
-        <v>9.69</v>
+        <v>8.52</v>
       </c>
       <c r="E138" t="n">
-        <v>13.33</v>
+        <v>12.38</v>
       </c>
       <c r="F138" t="n">
-        <v>3.64</v>
+        <v>3.86</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -4155,23 +4155,23 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Finlandia</t>
         </is>
       </c>
       <c r="B139" t="n">
         <v>2020</v>
       </c>
       <c r="C139" t="n">
-        <v>11.26</v>
+        <v>9.84</v>
       </c>
       <c r="D139" t="n">
-        <v>9.449999999999999</v>
+        <v>8.19</v>
       </c>
       <c r="E139" t="n">
-        <v>13.03</v>
+        <v>11.79</v>
       </c>
       <c r="F139" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -4182,23 +4182,23 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Finlandia</t>
         </is>
       </c>
       <c r="B140" t="n">
         <v>2021</v>
       </c>
       <c r="C140" t="n">
-        <v>11.25</v>
+        <v>9.51</v>
       </c>
       <c r="D140" t="n">
-        <v>9.6</v>
+        <v>7.78</v>
       </c>
       <c r="E140" t="n">
-        <v>13.01</v>
+        <v>11.19</v>
       </c>
       <c r="F140" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -4209,23 +4209,23 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Finlandia</t>
         </is>
       </c>
       <c r="B141" t="n">
         <v>2022</v>
       </c>
       <c r="C141" t="n">
-        <v>11.25</v>
+        <v>9.51</v>
       </c>
       <c r="D141" t="n">
-        <v>9.6</v>
+        <v>7.78</v>
       </c>
       <c r="E141" t="n">
-        <v>13.01</v>
+        <v>11.19</v>
       </c>
       <c r="F141" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -4236,23 +4236,23 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="B142" t="n">
         <v>2016</v>
       </c>
       <c r="C142" t="n">
-        <v>7.6</v>
+        <v>12.41</v>
       </c>
       <c r="D142" t="n">
-        <v>5.96</v>
+        <v>10.65</v>
       </c>
       <c r="E142" t="n">
-        <v>9.34</v>
+        <v>14.24</v>
       </c>
       <c r="F142" t="n">
-        <v>3.39</v>
+        <v>3.59</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -4263,23 +4263,23 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="B143" t="n">
         <v>2017</v>
       </c>
       <c r="C143" t="n">
-        <v>7.5</v>
+        <v>12.3</v>
       </c>
       <c r="D143" t="n">
-        <v>5.98</v>
+        <v>10.35</v>
       </c>
       <c r="E143" t="n">
-        <v>9.300000000000001</v>
+        <v>14.12</v>
       </c>
       <c r="F143" t="n">
-        <v>3.32</v>
+        <v>3.77</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -4290,23 +4290,23 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="B144" t="n">
         <v>2018</v>
       </c>
       <c r="C144" t="n">
-        <v>7.49</v>
+        <v>12.19</v>
       </c>
       <c r="D144" t="n">
-        <v>5.88</v>
+        <v>10.28</v>
       </c>
       <c r="E144" t="n">
-        <v>9.33</v>
+        <v>14.04</v>
       </c>
       <c r="F144" t="n">
-        <v>3.45</v>
+        <v>3.77</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -4317,23 +4317,23 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="B145" t="n">
         <v>2019</v>
       </c>
       <c r="C145" t="n">
-        <v>7.63</v>
+        <v>11.76</v>
       </c>
       <c r="D145" t="n">
-        <v>6.07</v>
+        <v>9.99</v>
       </c>
       <c r="E145" t="n">
-        <v>9.359999999999999</v>
+        <v>13.59</v>
       </c>
       <c r="F145" t="n">
-        <v>3.29</v>
+        <v>3.61</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -4344,23 +4344,23 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="B146" t="n">
         <v>2020</v>
       </c>
       <c r="C146" t="n">
-        <v>8</v>
+        <v>11.43</v>
       </c>
       <c r="D146" t="n">
-        <v>6.47</v>
+        <v>9.6</v>
       </c>
       <c r="E146" t="n">
-        <v>9.65</v>
+        <v>13.24</v>
       </c>
       <c r="F146" t="n">
-        <v>3.17</v>
+        <v>3.64</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -4371,23 +4371,23 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="B147" t="n">
         <v>2021</v>
       </c>
       <c r="C147" t="n">
-        <v>8.210000000000001</v>
+        <v>11.2</v>
       </c>
       <c r="D147" t="n">
-        <v>6.77</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="E147" t="n">
-        <v>9.800000000000001</v>
+        <v>13.05</v>
       </c>
       <c r="F147" t="n">
-        <v>3.03</v>
+        <v>3.59</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -4398,23 +4398,23 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="B148" t="n">
         <v>2022</v>
       </c>
       <c r="C148" t="n">
-        <v>8.210000000000001</v>
+        <v>11.2</v>
       </c>
       <c r="D148" t="n">
-        <v>6.77</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="E148" t="n">
-        <v>9.800000000000001</v>
+        <v>13.05</v>
       </c>
       <c r="F148" t="n">
-        <v>3.03</v>
+        <v>3.59</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -4425,23 +4425,23 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="B149" t="n">
         <v>2016</v>
       </c>
       <c r="C149" t="n">
-        <v>11.38</v>
+        <v>14.65</v>
       </c>
       <c r="D149" t="n">
-        <v>9.69</v>
+        <v>12.16</v>
       </c>
       <c r="E149" t="n">
-        <v>13.17</v>
+        <v>17.21</v>
       </c>
       <c r="F149" t="n">
-        <v>3.47</v>
+        <v>5.05</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -4452,23 +4452,23 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="B150" t="n">
         <v>2017</v>
       </c>
       <c r="C150" t="n">
-        <v>11.47</v>
+        <v>14.63</v>
       </c>
       <c r="D150" t="n">
-        <v>9.640000000000001</v>
+        <v>12.18</v>
       </c>
       <c r="E150" t="n">
-        <v>13.24</v>
+        <v>17.15</v>
       </c>
       <c r="F150" t="n">
-        <v>3.61</v>
+        <v>4.97</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -4479,23 +4479,23 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="B151" t="n">
         <v>2018</v>
       </c>
       <c r="C151" t="n">
-        <v>11.31</v>
+        <v>15.02</v>
       </c>
       <c r="D151" t="n">
-        <v>9.619999999999999</v>
+        <v>12.28</v>
       </c>
       <c r="E151" t="n">
-        <v>13.1</v>
+        <v>17.43</v>
       </c>
       <c r="F151" t="n">
-        <v>3.47</v>
+        <v>5.15</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -4506,23 +4506,23 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="B152" t="n">
         <v>2019</v>
       </c>
       <c r="C152" t="n">
-        <v>11.02</v>
+        <v>15.57</v>
       </c>
       <c r="D152" t="n">
-        <v>9.220000000000001</v>
+        <v>12.91</v>
       </c>
       <c r="E152" t="n">
-        <v>12.86</v>
+        <v>18.39</v>
       </c>
       <c r="F152" t="n">
-        <v>3.64</v>
+        <v>5.48</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -4533,23 +4533,23 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="B153" t="n">
         <v>2020</v>
       </c>
       <c r="C153" t="n">
-        <v>10.63</v>
+        <v>15.88</v>
       </c>
       <c r="D153" t="n">
-        <v>8.84</v>
+        <v>13.26</v>
       </c>
       <c r="E153" t="n">
-        <v>12.33</v>
+        <v>18.42</v>
       </c>
       <c r="F153" t="n">
-        <v>3.49</v>
+        <v>5.16</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -4560,23 +4560,23 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="B154" t="n">
         <v>2021</v>
       </c>
       <c r="C154" t="n">
-        <v>10.55</v>
+        <v>15.54</v>
       </c>
       <c r="D154" t="n">
-        <v>8.73</v>
+        <v>12.89</v>
       </c>
       <c r="E154" t="n">
-        <v>12.2</v>
+        <v>17.89</v>
       </c>
       <c r="F154" t="n">
-        <v>3.47</v>
+        <v>5</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -4587,23 +4587,23 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="B155" t="n">
         <v>2022</v>
       </c>
       <c r="C155" t="n">
-        <v>10.55</v>
+        <v>15.54</v>
       </c>
       <c r="D155" t="n">
-        <v>8.73</v>
+        <v>12.89</v>
       </c>
       <c r="E155" t="n">
-        <v>12.2</v>
+        <v>17.89</v>
       </c>
       <c r="F155" t="n">
-        <v>3.47</v>
+        <v>5</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -4614,23 +4614,23 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Grecia</t>
         </is>
       </c>
       <c r="B156" t="n">
         <v>2016</v>
       </c>
       <c r="C156" t="n">
-        <v>7.74</v>
+        <v>7.44</v>
       </c>
       <c r="D156" t="n">
-        <v>6.52</v>
+        <v>5.94</v>
       </c>
       <c r="E156" t="n">
-        <v>9.220000000000001</v>
+        <v>9</v>
       </c>
       <c r="F156" t="n">
-        <v>2.7</v>
+        <v>3.06</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -4641,23 +4641,23 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Grecia</t>
         </is>
       </c>
       <c r="B157" t="n">
         <v>2017</v>
       </c>
       <c r="C157" t="n">
-        <v>8.01</v>
+        <v>7.37</v>
       </c>
       <c r="D157" t="n">
-        <v>6.74</v>
+        <v>5.82</v>
       </c>
       <c r="E157" t="n">
-        <v>9.42</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="F157" t="n">
-        <v>2.68</v>
+        <v>3.04</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -4668,23 +4668,23 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Grecia</t>
         </is>
       </c>
       <c r="B158" t="n">
         <v>2018</v>
       </c>
       <c r="C158" t="n">
-        <v>8.26</v>
+        <v>7.29</v>
       </c>
       <c r="D158" t="n">
-        <v>6.94</v>
+        <v>5.82</v>
       </c>
       <c r="E158" t="n">
-        <v>9.710000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="F158" t="n">
-        <v>2.77</v>
+        <v>2.92</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -4695,23 +4695,23 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Grecia</t>
         </is>
       </c>
       <c r="B159" t="n">
         <v>2019</v>
       </c>
       <c r="C159" t="n">
-        <v>8.26</v>
+        <v>7.01</v>
       </c>
       <c r="D159" t="n">
-        <v>6.84</v>
+        <v>5.54</v>
       </c>
       <c r="E159" t="n">
-        <v>9.800000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="F159" t="n">
-        <v>2.96</v>
+        <v>3.04</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -4722,23 +4722,23 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Grecia</t>
         </is>
       </c>
       <c r="B160" t="n">
         <v>2020</v>
       </c>
       <c r="C160" t="n">
-        <v>8.300000000000001</v>
+        <v>6.96</v>
       </c>
       <c r="D160" t="n">
-        <v>6.82</v>
+        <v>5.53</v>
       </c>
       <c r="E160" t="n">
-        <v>9.859999999999999</v>
+        <v>8.41</v>
       </c>
       <c r="F160" t="n">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -4749,23 +4749,23 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Grecia</t>
         </is>
       </c>
       <c r="B161" t="n">
         <v>2021</v>
       </c>
       <c r="C161" t="n">
-        <v>8.33</v>
+        <v>6.98</v>
       </c>
       <c r="D161" t="n">
-        <v>6.91</v>
+        <v>5.54</v>
       </c>
       <c r="E161" t="n">
-        <v>9.93</v>
+        <v>8.44</v>
       </c>
       <c r="F161" t="n">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -4776,23 +4776,23 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Grecia</t>
         </is>
       </c>
       <c r="B162" t="n">
         <v>2022</v>
       </c>
       <c r="C162" t="n">
-        <v>8.33</v>
+        <v>6.98</v>
       </c>
       <c r="D162" t="n">
-        <v>6.91</v>
+        <v>5.54</v>
       </c>
       <c r="E162" t="n">
-        <v>9.93</v>
+        <v>8.44</v>
       </c>
       <c r="F162" t="n">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -4803,23 +4803,23 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>Hungría</t>
         </is>
       </c>
       <c r="B163" t="n">
         <v>2016</v>
       </c>
       <c r="C163" t="n">
-        <v>4.45</v>
+        <v>11.76</v>
       </c>
       <c r="D163" t="n">
-        <v>3.45</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="E163" t="n">
-        <v>5.7</v>
+        <v>13.46</v>
       </c>
       <c r="F163" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -4830,23 +4830,23 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>Hungría</t>
         </is>
       </c>
       <c r="B164" t="n">
         <v>2017</v>
       </c>
       <c r="C164" t="n">
-        <v>4.75</v>
+        <v>11.87</v>
       </c>
       <c r="D164" t="n">
-        <v>3.53</v>
+        <v>10.05</v>
       </c>
       <c r="E164" t="n">
-        <v>6.02</v>
+        <v>13.72</v>
       </c>
       <c r="F164" t="n">
-        <v>2.49</v>
+        <v>3.67</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -4857,23 +4857,23 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>Hungría</t>
         </is>
       </c>
       <c r="B165" t="n">
         <v>2018</v>
       </c>
       <c r="C165" t="n">
-        <v>4.79</v>
+        <v>11.67</v>
       </c>
       <c r="D165" t="n">
-        <v>3.48</v>
+        <v>9.93</v>
       </c>
       <c r="E165" t="n">
-        <v>6.05</v>
+        <v>13.51</v>
       </c>
       <c r="F165" t="n">
-        <v>2.57</v>
+        <v>3.58</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -4884,23 +4884,23 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>Hungría</t>
         </is>
       </c>
       <c r="B166" t="n">
         <v>2019</v>
       </c>
       <c r="C166" t="n">
-        <v>4.84</v>
+        <v>11.55</v>
       </c>
       <c r="D166" t="n">
-        <v>3.63</v>
+        <v>9.69</v>
       </c>
       <c r="E166" t="n">
-        <v>6.04</v>
+        <v>13.33</v>
       </c>
       <c r="F166" t="n">
-        <v>2.41</v>
+        <v>3.64</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -4911,23 +4911,23 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>Hungría</t>
         </is>
       </c>
       <c r="B167" t="n">
         <v>2020</v>
       </c>
       <c r="C167" t="n">
-        <v>4.73</v>
+        <v>11.26</v>
       </c>
       <c r="D167" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="E167" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="F167" t="n">
         <v>3.58</v>
-      </c>
-      <c r="E167" t="n">
-        <v>5.92</v>
-      </c>
-      <c r="F167" t="n">
-        <v>2.34</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -4938,23 +4938,23 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>Hungría</t>
         </is>
       </c>
       <c r="B168" t="n">
         <v>2021</v>
       </c>
       <c r="C168" t="n">
-        <v>5.37</v>
+        <v>11.25</v>
       </c>
       <c r="D168" t="n">
-        <v>4.19</v>
+        <v>9.6</v>
       </c>
       <c r="E168" t="n">
-        <v>6.55</v>
+        <v>13.01</v>
       </c>
       <c r="F168" t="n">
-        <v>2.36</v>
+        <v>3.41</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -4965,23 +4965,23 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>Hungría</t>
         </is>
       </c>
       <c r="B169" t="n">
         <v>2022</v>
       </c>
       <c r="C169" t="n">
-        <v>5.37</v>
+        <v>11.25</v>
       </c>
       <c r="D169" t="n">
-        <v>4.19</v>
+        <v>9.6</v>
       </c>
       <c r="E169" t="n">
-        <v>6.55</v>
+        <v>13.01</v>
       </c>
       <c r="F169" t="n">
-        <v>2.36</v>
+        <v>3.41</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -4992,23 +4992,23 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Irlanda</t>
         </is>
       </c>
       <c r="B170" t="n">
         <v>2016</v>
       </c>
       <c r="C170" t="n">
-        <v>12.91</v>
+        <v>11.38</v>
       </c>
       <c r="D170" t="n">
-        <v>10.51</v>
+        <v>9.69</v>
       </c>
       <c r="E170" t="n">
-        <v>15.6</v>
+        <v>13.17</v>
       </c>
       <c r="F170" t="n">
-        <v>5.09</v>
+        <v>3.47</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -5019,23 +5019,23 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Irlanda</t>
         </is>
       </c>
       <c r="B171" t="n">
         <v>2017</v>
       </c>
       <c r="C171" t="n">
-        <v>13.23</v>
+        <v>11.47</v>
       </c>
       <c r="D171" t="n">
-        <v>10.87</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="E171" t="n">
-        <v>15.97</v>
+        <v>13.24</v>
       </c>
       <c r="F171" t="n">
-        <v>5.1</v>
+        <v>3.61</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -5046,23 +5046,23 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Irlanda</t>
         </is>
       </c>
       <c r="B172" t="n">
         <v>2018</v>
       </c>
       <c r="C172" t="n">
-        <v>13.64</v>
+        <v>11.31</v>
       </c>
       <c r="D172" t="n">
-        <v>10.98</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="E172" t="n">
-        <v>16.18</v>
+        <v>13.1</v>
       </c>
       <c r="F172" t="n">
-        <v>5.2</v>
+        <v>3.47</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -5073,23 +5073,23 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Irlanda</t>
         </is>
       </c>
       <c r="B173" t="n">
         <v>2019</v>
       </c>
       <c r="C173" t="n">
-        <v>14.1</v>
+        <v>11.02</v>
       </c>
       <c r="D173" t="n">
-        <v>11.68</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="E173" t="n">
-        <v>16.56</v>
+        <v>12.86</v>
       </c>
       <c r="F173" t="n">
-        <v>4.88</v>
+        <v>3.64</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -5100,23 +5100,23 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Irlanda</t>
         </is>
       </c>
       <c r="B174" t="n">
         <v>2020</v>
       </c>
       <c r="C174" t="n">
-        <v>14.66</v>
+        <v>10.63</v>
       </c>
       <c r="D174" t="n">
-        <v>12.39</v>
+        <v>8.84</v>
       </c>
       <c r="E174" t="n">
-        <v>17.24</v>
+        <v>12.33</v>
       </c>
       <c r="F174" t="n">
-        <v>4.85</v>
+        <v>3.49</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -5127,23 +5127,23 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Irlanda</t>
         </is>
       </c>
       <c r="B175" t="n">
         <v>2021</v>
       </c>
       <c r="C175" t="n">
-        <v>14.73</v>
+        <v>10.55</v>
       </c>
       <c r="D175" t="n">
-        <v>12.63</v>
+        <v>8.73</v>
       </c>
       <c r="E175" t="n">
-        <v>17.3</v>
+        <v>12.2</v>
       </c>
       <c r="F175" t="n">
-        <v>4.67</v>
+        <v>3.47</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -5154,23 +5154,23 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Irlanda</t>
         </is>
       </c>
       <c r="B176" t="n">
         <v>2022</v>
       </c>
       <c r="C176" t="n">
-        <v>14.73</v>
+        <v>10.55</v>
       </c>
       <c r="D176" t="n">
-        <v>12.63</v>
+        <v>8.73</v>
       </c>
       <c r="E176" t="n">
-        <v>17.3</v>
+        <v>12.2</v>
       </c>
       <c r="F176" t="n">
-        <v>4.67</v>
+        <v>3.47</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
@@ -5181,23 +5181,23 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Islandia</t>
         </is>
       </c>
       <c r="B177" t="n">
         <v>2016</v>
       </c>
       <c r="C177" t="n">
-        <v>12.48</v>
+        <v>7.6</v>
       </c>
       <c r="D177" t="n">
-        <v>10.42</v>
+        <v>5.96</v>
       </c>
       <c r="E177" t="n">
-        <v>14.45</v>
+        <v>9.34</v>
       </c>
       <c r="F177" t="n">
-        <v>4.02</v>
+        <v>3.39</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
@@ -5208,23 +5208,23 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Islandia</t>
         </is>
       </c>
       <c r="B178" t="n">
         <v>2017</v>
       </c>
       <c r="C178" t="n">
-        <v>11.83</v>
+        <v>7.5</v>
       </c>
       <c r="D178" t="n">
-        <v>9.960000000000001</v>
+        <v>5.98</v>
       </c>
       <c r="E178" t="n">
-        <v>13.76</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F178" t="n">
-        <v>3.79</v>
+        <v>3.32</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -5235,23 +5235,23 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Islandia</t>
         </is>
       </c>
       <c r="B179" t="n">
         <v>2018</v>
       </c>
       <c r="C179" t="n">
-        <v>11.4</v>
+        <v>7.49</v>
       </c>
       <c r="D179" t="n">
-        <v>9.65</v>
+        <v>5.88</v>
       </c>
       <c r="E179" t="n">
-        <v>13.29</v>
+        <v>9.33</v>
       </c>
       <c r="F179" t="n">
-        <v>3.64</v>
+        <v>3.45</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
@@ -5262,23 +5262,23 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Islandia</t>
         </is>
       </c>
       <c r="B180" t="n">
         <v>2019</v>
       </c>
       <c r="C180" t="n">
-        <v>11.43</v>
+        <v>7.63</v>
       </c>
       <c r="D180" t="n">
-        <v>9.76</v>
+        <v>6.07</v>
       </c>
       <c r="E180" t="n">
-        <v>13.35</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="F180" t="n">
-        <v>3.59</v>
+        <v>3.29</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -5289,23 +5289,23 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Islandia</t>
         </is>
       </c>
       <c r="B181" t="n">
         <v>2020</v>
       </c>
       <c r="C181" t="n">
-        <v>11.98</v>
+        <v>8</v>
       </c>
       <c r="D181" t="n">
-        <v>10.18</v>
+        <v>6.47</v>
       </c>
       <c r="E181" t="n">
-        <v>13.83</v>
+        <v>9.65</v>
       </c>
       <c r="F181" t="n">
-        <v>3.65</v>
+        <v>3.17</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -5316,23 +5316,23 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Islandia</t>
         </is>
       </c>
       <c r="B182" t="n">
         <v>2021</v>
       </c>
       <c r="C182" t="n">
-        <v>12.18</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="D182" t="n">
-        <v>10.5</v>
+        <v>6.77</v>
       </c>
       <c r="E182" t="n">
-        <v>14.02</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F182" t="n">
-        <v>3.51</v>
+        <v>3.03</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
@@ -5343,23 +5343,23 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Islandia</t>
         </is>
       </c>
       <c r="B183" t="n">
         <v>2022</v>
       </c>
       <c r="C183" t="n">
-        <v>12.18</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="D183" t="n">
-        <v>10.5</v>
+        <v>6.77</v>
       </c>
       <c r="E183" t="n">
-        <v>14.02</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F183" t="n">
-        <v>3.51</v>
+        <v>3.03</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
@@ -5370,23 +5370,23 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Italia</t>
         </is>
       </c>
       <c r="B184" t="n">
         <v>2016</v>
       </c>
       <c r="C184" t="n">
-        <v>11.68</v>
+        <v>7.74</v>
       </c>
       <c r="D184" t="n">
-        <v>9.82</v>
+        <v>6.52</v>
       </c>
       <c r="E184" t="n">
-        <v>13.41</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="F184" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
@@ -5397,23 +5397,23 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Italia</t>
         </is>
       </c>
       <c r="B185" t="n">
         <v>2017</v>
       </c>
       <c r="C185" t="n">
-        <v>11.64</v>
+        <v>8.01</v>
       </c>
       <c r="D185" t="n">
-        <v>9.890000000000001</v>
+        <v>6.74</v>
       </c>
       <c r="E185" t="n">
-        <v>13.49</v>
+        <v>9.42</v>
       </c>
       <c r="F185" t="n">
-        <v>3.6</v>
+        <v>2.68</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
@@ -5424,23 +5424,23 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Italia</t>
         </is>
       </c>
       <c r="B186" t="n">
         <v>2018</v>
       </c>
       <c r="C186" t="n">
-        <v>11.53</v>
+        <v>8.26</v>
       </c>
       <c r="D186" t="n">
-        <v>9.84</v>
+        <v>6.94</v>
       </c>
       <c r="E186" t="n">
-        <v>13.54</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="F186" t="n">
-        <v>3.7</v>
+        <v>2.77</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -5451,23 +5451,23 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Italia</t>
         </is>
       </c>
       <c r="B187" t="n">
         <v>2019</v>
       </c>
       <c r="C187" t="n">
-        <v>11.25</v>
+        <v>8.26</v>
       </c>
       <c r="D187" t="n">
-        <v>9.609999999999999</v>
+        <v>6.84</v>
       </c>
       <c r="E187" t="n">
-        <v>13.19</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F187" t="n">
-        <v>3.58</v>
+        <v>2.96</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
@@ -5478,23 +5478,23 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Italia</t>
         </is>
       </c>
       <c r="B188" t="n">
         <v>2020</v>
       </c>
       <c r="C188" t="n">
-        <v>10.96</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D188" t="n">
-        <v>9.15</v>
+        <v>6.82</v>
       </c>
       <c r="E188" t="n">
-        <v>12.76</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="F188" t="n">
-        <v>3.61</v>
+        <v>3.04</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
@@ -5505,23 +5505,23 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Italia</t>
         </is>
       </c>
       <c r="B189" t="n">
         <v>2021</v>
       </c>
       <c r="C189" t="n">
-        <v>10.8</v>
+        <v>8.33</v>
       </c>
       <c r="D189" t="n">
-        <v>9.08</v>
+        <v>6.91</v>
       </c>
       <c r="E189" t="n">
-        <v>12.61</v>
+        <v>9.93</v>
       </c>
       <c r="F189" t="n">
-        <v>3.53</v>
+        <v>3.03</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
@@ -5532,23 +5532,23 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Italia</t>
         </is>
       </c>
       <c r="B190" t="n">
         <v>2022</v>
       </c>
       <c r="C190" t="n">
-        <v>10.8</v>
+        <v>8.33</v>
       </c>
       <c r="D190" t="n">
-        <v>9.08</v>
+        <v>6.91</v>
       </c>
       <c r="E190" t="n">
-        <v>12.61</v>
+        <v>9.93</v>
       </c>
       <c r="F190" t="n">
-        <v>3.53</v>
+        <v>3.03</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
@@ -5559,23 +5559,23 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Kazajistán</t>
         </is>
       </c>
       <c r="B191" t="n">
         <v>2016</v>
       </c>
       <c r="C191" t="n">
-        <v>7.91</v>
+        <v>4.45</v>
       </c>
       <c r="D191" t="n">
-        <v>6.34</v>
+        <v>3.45</v>
       </c>
       <c r="E191" t="n">
-        <v>9.59</v>
+        <v>5.7</v>
       </c>
       <c r="F191" t="n">
-        <v>3.25</v>
+        <v>2.25</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
@@ -5586,23 +5586,23 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Kazajistán</t>
         </is>
       </c>
       <c r="B192" t="n">
         <v>2017</v>
       </c>
       <c r="C192" t="n">
-        <v>7.96</v>
+        <v>4.75</v>
       </c>
       <c r="D192" t="n">
-        <v>6.48</v>
+        <v>3.53</v>
       </c>
       <c r="E192" t="n">
-        <v>9.68</v>
+        <v>6.02</v>
       </c>
       <c r="F192" t="n">
-        <v>3.21</v>
+        <v>2.49</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
@@ -5613,23 +5613,23 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Kazajistán</t>
         </is>
       </c>
       <c r="B193" t="n">
         <v>2018</v>
       </c>
       <c r="C193" t="n">
-        <v>7.78</v>
+        <v>4.79</v>
       </c>
       <c r="D193" t="n">
-        <v>6.17</v>
+        <v>3.48</v>
       </c>
       <c r="E193" t="n">
-        <v>9.51</v>
+        <v>6.05</v>
       </c>
       <c r="F193" t="n">
-        <v>3.34</v>
+        <v>2.57</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
@@ -5640,23 +5640,23 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Kazajistán</t>
         </is>
       </c>
       <c r="B194" t="n">
         <v>2019</v>
       </c>
       <c r="C194" t="n">
-        <v>7.03</v>
+        <v>4.84</v>
       </c>
       <c r="D194" t="n">
-        <v>5.55</v>
+        <v>3.63</v>
       </c>
       <c r="E194" t="n">
-        <v>8.65</v>
+        <v>6.04</v>
       </c>
       <c r="F194" t="n">
-        <v>3.11</v>
+        <v>2.41</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -5667,23 +5667,23 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Kazajistán</t>
         </is>
       </c>
       <c r="B195" t="n">
         <v>2020</v>
       </c>
       <c r="C195" t="n">
-        <v>6.47</v>
+        <v>4.73</v>
       </c>
       <c r="D195" t="n">
-        <v>5.02</v>
+        <v>3.58</v>
       </c>
       <c r="E195" t="n">
-        <v>7.95</v>
+        <v>5.92</v>
       </c>
       <c r="F195" t="n">
-        <v>2.93</v>
+        <v>2.34</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -5694,23 +5694,23 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Kazajistán</t>
         </is>
       </c>
       <c r="B196" t="n">
         <v>2021</v>
       </c>
       <c r="C196" t="n">
-        <v>6.2</v>
+        <v>5.37</v>
       </c>
       <c r="D196" t="n">
-        <v>4.86</v>
+        <v>4.19</v>
       </c>
       <c r="E196" t="n">
-        <v>7.64</v>
+        <v>6.55</v>
       </c>
       <c r="F196" t="n">
-        <v>2.79</v>
+        <v>2.36</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -5721,23 +5721,23 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Kazajistán</t>
         </is>
       </c>
       <c r="B197" t="n">
         <v>2022</v>
       </c>
       <c r="C197" t="n">
-        <v>6.2</v>
+        <v>5.37</v>
       </c>
       <c r="D197" t="n">
-        <v>4.86</v>
+        <v>4.19</v>
       </c>
       <c r="E197" t="n">
-        <v>7.64</v>
+        <v>6.55</v>
       </c>
       <c r="F197" t="n">
-        <v>2.79</v>
+        <v>2.36</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -5748,23 +5748,23 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>Letonia</t>
         </is>
       </c>
       <c r="B198" t="n">
         <v>2016</v>
       </c>
       <c r="C198" t="n">
-        <v>8.91</v>
+        <v>12.91</v>
       </c>
       <c r="D198" t="n">
-        <v>7.29</v>
+        <v>10.51</v>
       </c>
       <c r="E198" t="n">
-        <v>10.74</v>
+        <v>15.6</v>
       </c>
       <c r="F198" t="n">
-        <v>3.45</v>
+        <v>5.09</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
@@ -5775,23 +5775,23 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>Letonia</t>
         </is>
       </c>
       <c r="B199" t="n">
         <v>2017</v>
       </c>
       <c r="C199" t="n">
-        <v>9.15</v>
+        <v>13.23</v>
       </c>
       <c r="D199" t="n">
-        <v>7.42</v>
+        <v>10.87</v>
       </c>
       <c r="E199" t="n">
-        <v>10.97</v>
+        <v>15.97</v>
       </c>
       <c r="F199" t="n">
-        <v>3.55</v>
+        <v>5.1</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
@@ -5802,23 +5802,23 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>Letonia</t>
         </is>
       </c>
       <c r="B200" t="n">
         <v>2018</v>
       </c>
       <c r="C200" t="n">
-        <v>9.23</v>
+        <v>13.64</v>
       </c>
       <c r="D200" t="n">
-        <v>7.55</v>
+        <v>10.98</v>
       </c>
       <c r="E200" t="n">
-        <v>10.98</v>
+        <v>16.18</v>
       </c>
       <c r="F200" t="n">
-        <v>3.43</v>
+        <v>5.2</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
@@ -5829,23 +5829,23 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>Letonia</t>
         </is>
       </c>
       <c r="B201" t="n">
         <v>2019</v>
       </c>
       <c r="C201" t="n">
-        <v>8.77</v>
+        <v>14.1</v>
       </c>
       <c r="D201" t="n">
-        <v>7.02</v>
+        <v>11.68</v>
       </c>
       <c r="E201" t="n">
-        <v>10.5</v>
+        <v>16.56</v>
       </c>
       <c r="F201" t="n">
-        <v>3.48</v>
+        <v>4.88</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
@@ -5856,23 +5856,23 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>Letonia</t>
         </is>
       </c>
       <c r="B202" t="n">
         <v>2020</v>
       </c>
       <c r="C202" t="n">
-        <v>8.32</v>
+        <v>14.66</v>
       </c>
       <c r="D202" t="n">
-        <v>6.66</v>
+        <v>12.39</v>
       </c>
       <c r="E202" t="n">
-        <v>9.9</v>
+        <v>17.24</v>
       </c>
       <c r="F202" t="n">
-        <v>3.24</v>
+        <v>4.85</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -5883,23 +5883,23 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>Letonia</t>
         </is>
       </c>
       <c r="B203" t="n">
         <v>2021</v>
       </c>
       <c r="C203" t="n">
-        <v>8.01</v>
+        <v>14.73</v>
       </c>
       <c r="D203" t="n">
-        <v>6.47</v>
+        <v>12.63</v>
       </c>
       <c r="E203" t="n">
-        <v>9.65</v>
+        <v>17.3</v>
       </c>
       <c r="F203" t="n">
-        <v>3.18</v>
+        <v>4.67</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
@@ -5910,23 +5910,23 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>Letonia</t>
         </is>
       </c>
       <c r="B204" t="n">
         <v>2022</v>
       </c>
       <c r="C204" t="n">
-        <v>8.01</v>
+        <v>14.73</v>
       </c>
       <c r="D204" t="n">
-        <v>6.47</v>
+        <v>12.63</v>
       </c>
       <c r="E204" t="n">
-        <v>9.65</v>
+        <v>17.3</v>
       </c>
       <c r="F204" t="n">
-        <v>3.18</v>
+        <v>4.67</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
@@ -5937,23 +5937,23 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Lituania</t>
         </is>
       </c>
       <c r="B205" t="n">
         <v>2016</v>
       </c>
       <c r="C205" t="n">
-        <v>8.970000000000001</v>
+        <v>12.48</v>
       </c>
       <c r="D205" t="n">
-        <v>7.52</v>
+        <v>10.42</v>
       </c>
       <c r="E205" t="n">
-        <v>10.65</v>
+        <v>14.45</v>
       </c>
       <c r="F205" t="n">
-        <v>3.14</v>
+        <v>4.02</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
@@ -5964,23 +5964,23 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Lituania</t>
         </is>
       </c>
       <c r="B206" t="n">
         <v>2017</v>
       </c>
       <c r="C206" t="n">
-        <v>8.970000000000001</v>
+        <v>11.83</v>
       </c>
       <c r="D206" t="n">
-        <v>7.55</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="E206" t="n">
-        <v>10.53</v>
+        <v>13.76</v>
       </c>
       <c r="F206" t="n">
-        <v>2.98</v>
+        <v>3.79</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
@@ -5991,23 +5991,23 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Lituania</t>
         </is>
       </c>
       <c r="B207" t="n">
         <v>2018</v>
       </c>
       <c r="C207" t="n">
-        <v>8.94</v>
+        <v>11.4</v>
       </c>
       <c r="D207" t="n">
-        <v>7.32</v>
+        <v>9.65</v>
       </c>
       <c r="E207" t="n">
-        <v>10.57</v>
+        <v>13.29</v>
       </c>
       <c r="F207" t="n">
-        <v>3.24</v>
+        <v>3.64</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
@@ -6018,23 +6018,23 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Lituania</t>
         </is>
       </c>
       <c r="B208" t="n">
         <v>2019</v>
       </c>
       <c r="C208" t="n">
-        <v>8.77</v>
+        <v>11.43</v>
       </c>
       <c r="D208" t="n">
-        <v>7.25</v>
+        <v>9.76</v>
       </c>
       <c r="E208" t="n">
-        <v>10.38</v>
+        <v>13.35</v>
       </c>
       <c r="F208" t="n">
-        <v>3.13</v>
+        <v>3.59</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
@@ -6045,23 +6045,23 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Lituania</t>
         </is>
       </c>
       <c r="B209" t="n">
         <v>2020</v>
       </c>
       <c r="C209" t="n">
-        <v>8.710000000000001</v>
+        <v>11.98</v>
       </c>
       <c r="D209" t="n">
-        <v>7.28</v>
+        <v>10.18</v>
       </c>
       <c r="E209" t="n">
-        <v>10.27</v>
+        <v>13.83</v>
       </c>
       <c r="F209" t="n">
-        <v>2.99</v>
+        <v>3.65</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
@@ -6072,23 +6072,23 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Lituania</t>
         </is>
       </c>
       <c r="B210" t="n">
         <v>2021</v>
       </c>
       <c r="C210" t="n">
-        <v>8.699999999999999</v>
+        <v>12.18</v>
       </c>
       <c r="D210" t="n">
-        <v>7.19</v>
+        <v>10.5</v>
       </c>
       <c r="E210" t="n">
-        <v>10.23</v>
+        <v>14.02</v>
       </c>
       <c r="F210" t="n">
-        <v>3.04</v>
+        <v>3.51</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
@@ -6099,23 +6099,23 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Lituania</t>
         </is>
       </c>
       <c r="B211" t="n">
         <v>2022</v>
       </c>
       <c r="C211" t="n">
-        <v>8.699999999999999</v>
+        <v>12.18</v>
       </c>
       <c r="D211" t="n">
-        <v>7.19</v>
+        <v>10.5</v>
       </c>
       <c r="E211" t="n">
-        <v>10.23</v>
+        <v>14.02</v>
       </c>
       <c r="F211" t="n">
-        <v>3.04</v>
+        <v>3.51</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
@@ -6126,23 +6126,23 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>North Macedonia</t>
+          <t>Luxemburgo</t>
         </is>
       </c>
       <c r="B212" t="n">
         <v>2016</v>
       </c>
       <c r="C212" t="n">
-        <v>5.53</v>
+        <v>11.68</v>
       </c>
       <c r="D212" t="n">
-        <v>4.21</v>
+        <v>9.82</v>
       </c>
       <c r="E212" t="n">
-        <v>6.98</v>
+        <v>13.41</v>
       </c>
       <c r="F212" t="n">
-        <v>2.77</v>
+        <v>3.6</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
@@ -6153,23 +6153,23 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>North Macedonia</t>
+          <t>Luxemburgo</t>
         </is>
       </c>
       <c r="B213" t="n">
         <v>2017</v>
       </c>
       <c r="C213" t="n">
-        <v>5.27</v>
+        <v>11.64</v>
       </c>
       <c r="D213" t="n">
-        <v>3.99</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="E213" t="n">
-        <v>6.69</v>
+        <v>13.49</v>
       </c>
       <c r="F213" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
@@ -6180,23 +6180,23 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>North Macedonia</t>
+          <t>Luxemburgo</t>
         </is>
       </c>
       <c r="B214" t="n">
         <v>2018</v>
       </c>
       <c r="C214" t="n">
-        <v>5.08</v>
+        <v>11.53</v>
       </c>
       <c r="D214" t="n">
-        <v>3.91</v>
+        <v>9.84</v>
       </c>
       <c r="E214" t="n">
-        <v>6.43</v>
+        <v>13.54</v>
       </c>
       <c r="F214" t="n">
-        <v>2.52</v>
+        <v>3.7</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
@@ -6207,23 +6207,23 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>North Macedonia</t>
+          <t>Luxemburgo</t>
         </is>
       </c>
       <c r="B215" t="n">
         <v>2019</v>
       </c>
       <c r="C215" t="n">
-        <v>5.43</v>
+        <v>11.25</v>
       </c>
       <c r="D215" t="n">
-        <v>4.2</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="E215" t="n">
-        <v>6.77</v>
+        <v>13.19</v>
       </c>
       <c r="F215" t="n">
-        <v>2.56</v>
+        <v>3.58</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
@@ -6234,23 +6234,23 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>North Macedonia</t>
+          <t>Luxemburgo</t>
         </is>
       </c>
       <c r="B216" t="n">
         <v>2020</v>
       </c>
       <c r="C216" t="n">
-        <v>5.79</v>
+        <v>10.96</v>
       </c>
       <c r="D216" t="n">
-        <v>4.56</v>
+        <v>9.15</v>
       </c>
       <c r="E216" t="n">
-        <v>7.18</v>
+        <v>12.76</v>
       </c>
       <c r="F216" t="n">
-        <v>2.62</v>
+        <v>3.61</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
@@ -6261,23 +6261,23 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>North Macedonia</t>
+          <t>Luxemburgo</t>
         </is>
       </c>
       <c r="B217" t="n">
         <v>2021</v>
       </c>
       <c r="C217" t="n">
-        <v>5.76</v>
+        <v>10.8</v>
       </c>
       <c r="D217" t="n">
-        <v>4.39</v>
+        <v>9.08</v>
       </c>
       <c r="E217" t="n">
-        <v>7.06</v>
+        <v>12.61</v>
       </c>
       <c r="F217" t="n">
-        <v>2.67</v>
+        <v>3.53</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
@@ -6288,23 +6288,23 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>North Macedonia</t>
+          <t>Luxemburgo</t>
         </is>
       </c>
       <c r="B218" t="n">
         <v>2022</v>
       </c>
       <c r="C218" t="n">
-        <v>5.76</v>
+        <v>10.8</v>
       </c>
       <c r="D218" t="n">
-        <v>4.39</v>
+        <v>9.08</v>
       </c>
       <c r="E218" t="n">
-        <v>7.06</v>
+        <v>12.61</v>
       </c>
       <c r="F218" t="n">
-        <v>2.67</v>
+        <v>3.53</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
@@ -6315,23 +6315,23 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Macedonia del Norte</t>
         </is>
       </c>
       <c r="B219" t="n">
         <v>2016</v>
       </c>
       <c r="C219" t="n">
-        <v>6.67</v>
+        <v>5.53</v>
       </c>
       <c r="D219" t="n">
-        <v>5.33</v>
+        <v>4.21</v>
       </c>
       <c r="E219" t="n">
-        <v>8.06</v>
+        <v>6.98</v>
       </c>
       <c r="F219" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
@@ -6342,20 +6342,20 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Macedonia del Norte</t>
         </is>
       </c>
       <c r="B220" t="n">
         <v>2017</v>
       </c>
       <c r="C220" t="n">
-        <v>6.67</v>
+        <v>5.27</v>
       </c>
       <c r="D220" t="n">
-        <v>5.39</v>
+        <v>3.99</v>
       </c>
       <c r="E220" t="n">
-        <v>8.09</v>
+        <v>6.69</v>
       </c>
       <c r="F220" t="n">
         <v>2.7</v>
@@ -6369,23 +6369,23 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Macedonia del Norte</t>
         </is>
       </c>
       <c r="B221" t="n">
         <v>2018</v>
       </c>
       <c r="C221" t="n">
-        <v>6.67</v>
+        <v>5.08</v>
       </c>
       <c r="D221" t="n">
-        <v>5.26</v>
+        <v>3.91</v>
       </c>
       <c r="E221" t="n">
-        <v>8.109999999999999</v>
+        <v>6.43</v>
       </c>
       <c r="F221" t="n">
-        <v>2.85</v>
+        <v>2.52</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
@@ -6396,23 +6396,23 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Macedonia del Norte</t>
         </is>
       </c>
       <c r="B222" t="n">
         <v>2019</v>
       </c>
       <c r="C222" t="n">
-        <v>6.9</v>
+        <v>5.43</v>
       </c>
       <c r="D222" t="n">
-        <v>5.57</v>
+        <v>4.2</v>
       </c>
       <c r="E222" t="n">
-        <v>8.27</v>
+        <v>6.77</v>
       </c>
       <c r="F222" t="n">
-        <v>2.71</v>
+        <v>2.56</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
@@ -6423,23 +6423,23 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Macedonia del Norte</t>
         </is>
       </c>
       <c r="B223" t="n">
         <v>2020</v>
       </c>
       <c r="C223" t="n">
-        <v>7.35</v>
+        <v>5.79</v>
       </c>
       <c r="D223" t="n">
-        <v>5.99</v>
+        <v>4.56</v>
       </c>
       <c r="E223" t="n">
-        <v>8.75</v>
+        <v>7.18</v>
       </c>
       <c r="F223" t="n">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
@@ -6450,23 +6450,23 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Macedonia del Norte</t>
         </is>
       </c>
       <c r="B224" t="n">
         <v>2021</v>
       </c>
       <c r="C224" t="n">
-        <v>7.48</v>
+        <v>5.76</v>
       </c>
       <c r="D224" t="n">
-        <v>6.14</v>
+        <v>4.39</v>
       </c>
       <c r="E224" t="n">
-        <v>8.970000000000001</v>
+        <v>7.06</v>
       </c>
       <c r="F224" t="n">
-        <v>2.83</v>
+        <v>2.67</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
@@ -6477,23 +6477,23 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Macedonia del Norte</t>
         </is>
       </c>
       <c r="B225" t="n">
         <v>2022</v>
       </c>
       <c r="C225" t="n">
-        <v>7.48</v>
+        <v>5.76</v>
       </c>
       <c r="D225" t="n">
-        <v>6.14</v>
+        <v>4.39</v>
       </c>
       <c r="E225" t="n">
-        <v>8.970000000000001</v>
+        <v>7.06</v>
       </c>
       <c r="F225" t="n">
-        <v>2.83</v>
+        <v>2.67</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
@@ -6504,23 +6504,23 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="B226" t="n">
         <v>2016</v>
       </c>
       <c r="C226" t="n">
-        <v>11.81</v>
+        <v>7.91</v>
       </c>
       <c r="D226" t="n">
-        <v>9.93</v>
+        <v>6.34</v>
       </c>
       <c r="E226" t="n">
-        <v>13.57</v>
+        <v>9.59</v>
       </c>
       <c r="F226" t="n">
-        <v>3.64</v>
+        <v>3.25</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
@@ -6531,23 +6531,23 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="B227" t="n">
         <v>2017</v>
       </c>
       <c r="C227" t="n">
-        <v>11.83</v>
+        <v>7.96</v>
       </c>
       <c r="D227" t="n">
-        <v>10.02</v>
+        <v>6.48</v>
       </c>
       <c r="E227" t="n">
-        <v>13.85</v>
+        <v>9.68</v>
       </c>
       <c r="F227" t="n">
-        <v>3.83</v>
+        <v>3.21</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
@@ -6558,23 +6558,23 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="B228" t="n">
         <v>2018</v>
       </c>
       <c r="C228" t="n">
-        <v>11.97</v>
+        <v>7.78</v>
       </c>
       <c r="D228" t="n">
-        <v>10.1</v>
+        <v>6.17</v>
       </c>
       <c r="E228" t="n">
-        <v>13.96</v>
+        <v>9.51</v>
       </c>
       <c r="F228" t="n">
-        <v>3.86</v>
+        <v>3.34</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
@@ -6585,23 +6585,23 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="B229" t="n">
         <v>2019</v>
       </c>
       <c r="C229" t="n">
-        <v>12.04</v>
+        <v>7.03</v>
       </c>
       <c r="D229" t="n">
-        <v>10.26</v>
+        <v>5.55</v>
       </c>
       <c r="E229" t="n">
-        <v>14.12</v>
+        <v>8.65</v>
       </c>
       <c r="F229" t="n">
-        <v>3.86</v>
+        <v>3.11</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
@@ -6612,23 +6612,23 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="B230" t="n">
         <v>2020</v>
       </c>
       <c r="C230" t="n">
-        <v>12.11</v>
+        <v>6.47</v>
       </c>
       <c r="D230" t="n">
-        <v>10.35</v>
+        <v>5.02</v>
       </c>
       <c r="E230" t="n">
-        <v>14.05</v>
+        <v>7.95</v>
       </c>
       <c r="F230" t="n">
-        <v>3.71</v>
+        <v>2.93</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
@@ -6639,23 +6639,23 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="B231" t="n">
         <v>2021</v>
       </c>
       <c r="C231" t="n">
-        <v>11.92</v>
+        <v>6.2</v>
       </c>
       <c r="D231" t="n">
-        <v>10.15</v>
+        <v>4.86</v>
       </c>
       <c r="E231" t="n">
-        <v>13.87</v>
+        <v>7.64</v>
       </c>
       <c r="F231" t="n">
-        <v>3.72</v>
+        <v>2.79</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
@@ -6666,23 +6666,23 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="B232" t="n">
         <v>2022</v>
       </c>
       <c r="C232" t="n">
-        <v>11.92</v>
+        <v>6.2</v>
       </c>
       <c r="D232" t="n">
-        <v>10.15</v>
+        <v>4.86</v>
       </c>
       <c r="E232" t="n">
-        <v>13.87</v>
+        <v>7.64</v>
       </c>
       <c r="F232" t="n">
-        <v>3.72</v>
+        <v>2.79</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
@@ -6693,23 +6693,23 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Montenegro</t>
         </is>
       </c>
       <c r="B233" t="n">
         <v>2016</v>
       </c>
       <c r="C233" t="n">
-        <v>11.04</v>
+        <v>8.91</v>
       </c>
       <c r="D233" t="n">
-        <v>9.359999999999999</v>
+        <v>7.29</v>
       </c>
       <c r="E233" t="n">
-        <v>12.83</v>
+        <v>10.74</v>
       </c>
       <c r="F233" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
@@ -6720,23 +6720,23 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Montenegro</t>
         </is>
       </c>
       <c r="B234" t="n">
         <v>2017</v>
       </c>
       <c r="C234" t="n">
-        <v>11.01</v>
+        <v>9.15</v>
       </c>
       <c r="D234" t="n">
-        <v>9.27</v>
+        <v>7.42</v>
       </c>
       <c r="E234" t="n">
-        <v>12.91</v>
+        <v>10.97</v>
       </c>
       <c r="F234" t="n">
-        <v>3.64</v>
+        <v>3.55</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
@@ -6747,23 +6747,23 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Montenegro</t>
         </is>
       </c>
       <c r="B235" t="n">
         <v>2018</v>
       </c>
       <c r="C235" t="n">
-        <v>11.36</v>
+        <v>9.23</v>
       </c>
       <c r="D235" t="n">
-        <v>9.6</v>
+        <v>7.55</v>
       </c>
       <c r="E235" t="n">
-        <v>13.18</v>
+        <v>10.98</v>
       </c>
       <c r="F235" t="n">
-        <v>3.58</v>
+        <v>3.43</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
@@ -6774,23 +6774,23 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Montenegro</t>
         </is>
       </c>
       <c r="B236" t="n">
         <v>2019</v>
       </c>
       <c r="C236" t="n">
-        <v>10.8</v>
+        <v>8.77</v>
       </c>
       <c r="D236" t="n">
-        <v>9.130000000000001</v>
+        <v>7.02</v>
       </c>
       <c r="E236" t="n">
-        <v>12.42</v>
+        <v>10.5</v>
       </c>
       <c r="F236" t="n">
-        <v>3.29</v>
+        <v>3.48</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
@@ -6801,23 +6801,23 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Montenegro</t>
         </is>
       </c>
       <c r="B237" t="n">
         <v>2020</v>
       </c>
       <c r="C237" t="n">
-        <v>10.88</v>
+        <v>8.32</v>
       </c>
       <c r="D237" t="n">
-        <v>9.17</v>
+        <v>6.66</v>
       </c>
       <c r="E237" t="n">
-        <v>12.59</v>
+        <v>9.9</v>
       </c>
       <c r="F237" t="n">
-        <v>3.42</v>
+        <v>3.24</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
@@ -6828,23 +6828,23 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Montenegro</t>
         </is>
       </c>
       <c r="B238" t="n">
         <v>2021</v>
       </c>
       <c r="C238" t="n">
-        <v>11.22</v>
+        <v>8.01</v>
       </c>
       <c r="D238" t="n">
-        <v>9.460000000000001</v>
+        <v>6.47</v>
       </c>
       <c r="E238" t="n">
-        <v>12.97</v>
+        <v>9.65</v>
       </c>
       <c r="F238" t="n">
-        <v>3.52</v>
+        <v>3.18</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
@@ -6855,23 +6855,23 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Montenegro</t>
         </is>
       </c>
       <c r="B239" t="n">
         <v>2022</v>
       </c>
       <c r="C239" t="n">
-        <v>11.22</v>
+        <v>8.01</v>
       </c>
       <c r="D239" t="n">
-        <v>9.460000000000001</v>
+        <v>6.47</v>
       </c>
       <c r="E239" t="n">
-        <v>12.97</v>
+        <v>9.65</v>
       </c>
       <c r="F239" t="n">
-        <v>3.52</v>
+        <v>3.18</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
@@ -6882,23 +6882,23 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="B240" t="n">
         <v>2016</v>
       </c>
       <c r="C240" t="n">
-        <v>16.89</v>
+        <v>6.67</v>
       </c>
       <c r="D240" t="n">
-        <v>14.33</v>
+        <v>5.33</v>
       </c>
       <c r="E240" t="n">
-        <v>19.51</v>
+        <v>8.06</v>
       </c>
       <c r="F240" t="n">
-        <v>5.18</v>
+        <v>2.73</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
@@ -6909,23 +6909,23 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="B241" t="n">
         <v>2017</v>
       </c>
       <c r="C241" t="n">
-        <v>17.1</v>
+        <v>6.67</v>
       </c>
       <c r="D241" t="n">
-        <v>14.62</v>
+        <v>5.39</v>
       </c>
       <c r="E241" t="n">
-        <v>19.98</v>
+        <v>8.09</v>
       </c>
       <c r="F241" t="n">
-        <v>5.36</v>
+        <v>2.7</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
@@ -6936,23 +6936,23 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="B242" t="n">
         <v>2018</v>
       </c>
       <c r="C242" t="n">
-        <v>17.22</v>
+        <v>6.67</v>
       </c>
       <c r="D242" t="n">
-        <v>14.72</v>
+        <v>5.26</v>
       </c>
       <c r="E242" t="n">
-        <v>19.81</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="F242" t="n">
-        <v>5.09</v>
+        <v>2.85</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
@@ -6963,23 +6963,23 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="B243" t="n">
         <v>2019</v>
       </c>
       <c r="C243" t="n">
-        <v>17.11</v>
+        <v>6.9</v>
       </c>
       <c r="D243" t="n">
-        <v>14.51</v>
+        <v>5.57</v>
       </c>
       <c r="E243" t="n">
-        <v>19.85</v>
+        <v>8.27</v>
       </c>
       <c r="F243" t="n">
-        <v>5.34</v>
+        <v>2.71</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
@@ -6990,23 +6990,23 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="B244" t="n">
         <v>2020</v>
       </c>
       <c r="C244" t="n">
-        <v>17.09</v>
+        <v>7.35</v>
       </c>
       <c r="D244" t="n">
-        <v>14.33</v>
+        <v>5.99</v>
       </c>
       <c r="E244" t="n">
-        <v>19.57</v>
+        <v>8.75</v>
       </c>
       <c r="F244" t="n">
-        <v>5.24</v>
+        <v>2.76</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
@@ -7017,23 +7017,23 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="B245" t="n">
         <v>2021</v>
       </c>
       <c r="C245" t="n">
-        <v>17.06</v>
+        <v>7.48</v>
       </c>
       <c r="D245" t="n">
-        <v>14.56</v>
+        <v>6.14</v>
       </c>
       <c r="E245" t="n">
-        <v>19.79</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="F245" t="n">
-        <v>5.23</v>
+        <v>2.83</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
@@ -7044,23 +7044,23 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="B246" t="n">
         <v>2022</v>
       </c>
       <c r="C246" t="n">
-        <v>17.06</v>
+        <v>7.48</v>
       </c>
       <c r="D246" t="n">
-        <v>14.56</v>
+        <v>6.14</v>
       </c>
       <c r="E246" t="n">
-        <v>19.79</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="F246" t="n">
-        <v>5.23</v>
+        <v>2.83</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
@@ -7071,23 +7071,23 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Russian Federation</t>
+          <t>Países Bajos</t>
         </is>
       </c>
       <c r="B247" t="n">
         <v>2016</v>
       </c>
       <c r="C247" t="n">
-        <v>11.21</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="D247" t="n">
-        <v>9.119999999999999</v>
+        <v>7.52</v>
       </c>
       <c r="E247" t="n">
-        <v>13.15</v>
+        <v>10.65</v>
       </c>
       <c r="F247" t="n">
-        <v>4.04</v>
+        <v>3.14</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
@@ -7098,23 +7098,23 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Russian Federation</t>
+          <t>Países Bajos</t>
         </is>
       </c>
       <c r="B248" t="n">
         <v>2017</v>
       </c>
       <c r="C248" t="n">
-        <v>10.92</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="D248" t="n">
-        <v>8.92</v>
+        <v>7.55</v>
       </c>
       <c r="E248" t="n">
-        <v>12.87</v>
+        <v>10.53</v>
       </c>
       <c r="F248" t="n">
-        <v>3.95</v>
+        <v>2.98</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
@@ -7125,23 +7125,23 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Russian Federation</t>
+          <t>Países Bajos</t>
         </is>
       </c>
       <c r="B249" t="n">
         <v>2018</v>
       </c>
       <c r="C249" t="n">
-        <v>10.72</v>
+        <v>8.94</v>
       </c>
       <c r="D249" t="n">
-        <v>8.800000000000001</v>
+        <v>7.32</v>
       </c>
       <c r="E249" t="n">
-        <v>12.72</v>
+        <v>10.57</v>
       </c>
       <c r="F249" t="n">
-        <v>3.93</v>
+        <v>3.24</v>
       </c>
       <c r="G249" t="inlineStr">
         <is>
@@ -7152,23 +7152,23 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Russian Federation</t>
+          <t>Países Bajos</t>
         </is>
       </c>
       <c r="B250" t="n">
         <v>2019</v>
       </c>
       <c r="C250" t="n">
-        <v>10.67</v>
+        <v>8.77</v>
       </c>
       <c r="D250" t="n">
-        <v>8.779999999999999</v>
+        <v>7.25</v>
       </c>
       <c r="E250" t="n">
-        <v>12.71</v>
+        <v>10.38</v>
       </c>
       <c r="F250" t="n">
-        <v>3.93</v>
+        <v>3.13</v>
       </c>
       <c r="G250" t="inlineStr">
         <is>
@@ -7179,23 +7179,23 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Russian Federation</t>
+          <t>Países Bajos</t>
         </is>
       </c>
       <c r="B251" t="n">
         <v>2020</v>
       </c>
       <c r="C251" t="n">
-        <v>10.56</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="D251" t="n">
-        <v>8.65</v>
+        <v>7.28</v>
       </c>
       <c r="E251" t="n">
-        <v>12.61</v>
+        <v>10.27</v>
       </c>
       <c r="F251" t="n">
-        <v>3.96</v>
+        <v>2.99</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
@@ -7206,23 +7206,23 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Russian Federation</t>
+          <t>Países Bajos</t>
         </is>
       </c>
       <c r="B252" t="n">
         <v>2021</v>
       </c>
       <c r="C252" t="n">
-        <v>10.51</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D252" t="n">
-        <v>8.550000000000001</v>
+        <v>7.19</v>
       </c>
       <c r="E252" t="n">
-        <v>12.52</v>
+        <v>10.23</v>
       </c>
       <c r="F252" t="n">
-        <v>3.97</v>
+        <v>3.04</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
@@ -7233,23 +7233,23 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Russian Federation</t>
+          <t>Países Bajos</t>
         </is>
       </c>
       <c r="B253" t="n">
         <v>2022</v>
       </c>
       <c r="C253" t="n">
-        <v>10.51</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D253" t="n">
-        <v>8.550000000000001</v>
+        <v>7.19</v>
       </c>
       <c r="E253" t="n">
-        <v>12.52</v>
+        <v>10.23</v>
       </c>
       <c r="F253" t="n">
-        <v>3.97</v>
+        <v>3.04</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
@@ -7260,23 +7260,23 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Polonia</t>
         </is>
       </c>
       <c r="B254" t="n">
         <v>2016</v>
       </c>
       <c r="C254" t="n">
-        <v>9.289999999999999</v>
+        <v>11.81</v>
       </c>
       <c r="D254" t="n">
-        <v>7.65</v>
+        <v>9.93</v>
       </c>
       <c r="E254" t="n">
-        <v>11.04</v>
+        <v>13.57</v>
       </c>
       <c r="F254" t="n">
-        <v>3.38</v>
+        <v>3.64</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
@@ -7287,23 +7287,23 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Polonia</t>
         </is>
       </c>
       <c r="B255" t="n">
         <v>2017</v>
       </c>
       <c r="C255" t="n">
-        <v>9.369999999999999</v>
+        <v>11.83</v>
       </c>
       <c r="D255" t="n">
-        <v>7.81</v>
+        <v>10.02</v>
       </c>
       <c r="E255" t="n">
-        <v>11.11</v>
+        <v>13.85</v>
       </c>
       <c r="F255" t="n">
-        <v>3.29</v>
+        <v>3.83</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
@@ -7314,23 +7314,23 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Polonia</t>
         </is>
       </c>
       <c r="B256" t="n">
         <v>2018</v>
       </c>
       <c r="C256" t="n">
-        <v>9.43</v>
+        <v>11.97</v>
       </c>
       <c r="D256" t="n">
-        <v>7.86</v>
+        <v>10.1</v>
       </c>
       <c r="E256" t="n">
-        <v>11.08</v>
+        <v>13.96</v>
       </c>
       <c r="F256" t="n">
-        <v>3.22</v>
+        <v>3.86</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
@@ -7341,23 +7341,23 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Polonia</t>
         </is>
       </c>
       <c r="B257" t="n">
         <v>2019</v>
       </c>
       <c r="C257" t="n">
-        <v>9.27</v>
+        <v>12.04</v>
       </c>
       <c r="D257" t="n">
-        <v>7.69</v>
+        <v>10.26</v>
       </c>
       <c r="E257" t="n">
-        <v>10.93</v>
+        <v>14.12</v>
       </c>
       <c r="F257" t="n">
-        <v>3.24</v>
+        <v>3.86</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
@@ -7368,23 +7368,23 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Polonia</t>
         </is>
       </c>
       <c r="B258" t="n">
         <v>2020</v>
       </c>
       <c r="C258" t="n">
-        <v>9.09</v>
+        <v>12.11</v>
       </c>
       <c r="D258" t="n">
-        <v>7.33</v>
+        <v>10.35</v>
       </c>
       <c r="E258" t="n">
-        <v>10.71</v>
+        <v>14.05</v>
       </c>
       <c r="F258" t="n">
-        <v>3.37</v>
+        <v>3.71</v>
       </c>
       <c r="G258" t="inlineStr">
         <is>
@@ -7395,23 +7395,23 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Polonia</t>
         </is>
       </c>
       <c r="B259" t="n">
         <v>2021</v>
       </c>
       <c r="C259" t="n">
-        <v>9.029999999999999</v>
+        <v>11.92</v>
       </c>
       <c r="D259" t="n">
-        <v>7.39</v>
+        <v>10.15</v>
       </c>
       <c r="E259" t="n">
-        <v>10.75</v>
+        <v>13.87</v>
       </c>
       <c r="F259" t="n">
-        <v>3.36</v>
+        <v>3.72</v>
       </c>
       <c r="G259" t="inlineStr">
         <is>
@@ -7422,23 +7422,23 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Polonia</t>
         </is>
       </c>
       <c r="B260" t="n">
         <v>2022</v>
       </c>
       <c r="C260" t="n">
-        <v>9.029999999999999</v>
+        <v>11.92</v>
       </c>
       <c r="D260" t="n">
-        <v>7.39</v>
+        <v>10.15</v>
       </c>
       <c r="E260" t="n">
-        <v>10.75</v>
+        <v>13.87</v>
       </c>
       <c r="F260" t="n">
-        <v>3.36</v>
+        <v>3.72</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
@@ -7449,23 +7449,23 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B261" t="n">
         <v>2016</v>
       </c>
       <c r="C261" t="n">
-        <v>11.09</v>
+        <v>11.04</v>
       </c>
       <c r="D261" t="n">
-        <v>9.41</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="E261" t="n">
-        <v>12.81</v>
+        <v>12.83</v>
       </c>
       <c r="F261" t="n">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
@@ -7476,23 +7476,23 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B262" t="n">
         <v>2017</v>
       </c>
       <c r="C262" t="n">
-        <v>11.03</v>
+        <v>11.01</v>
       </c>
       <c r="D262" t="n">
-        <v>9.23</v>
+        <v>9.27</v>
       </c>
       <c r="E262" t="n">
-        <v>12.82</v>
+        <v>12.91</v>
       </c>
       <c r="F262" t="n">
-        <v>3.59</v>
+        <v>3.64</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
@@ -7503,23 +7503,23 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B263" t="n">
         <v>2018</v>
       </c>
       <c r="C263" t="n">
-        <v>11.19</v>
+        <v>11.36</v>
       </c>
       <c r="D263" t="n">
-        <v>9.48</v>
+        <v>9.6</v>
       </c>
       <c r="E263" t="n">
-        <v>12.91</v>
+        <v>13.18</v>
       </c>
       <c r="F263" t="n">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="G263" t="inlineStr">
         <is>
@@ -7530,23 +7530,23 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B264" t="n">
         <v>2019</v>
       </c>
       <c r="C264" t="n">
-        <v>11.25</v>
+        <v>10.8</v>
       </c>
       <c r="D264" t="n">
-        <v>9.49</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="E264" t="n">
-        <v>12.93</v>
+        <v>12.42</v>
       </c>
       <c r="F264" t="n">
-        <v>3.43</v>
+        <v>3.29</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
@@ -7557,23 +7557,23 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B265" t="n">
         <v>2020</v>
       </c>
       <c r="C265" t="n">
-        <v>11.11</v>
+        <v>10.88</v>
       </c>
       <c r="D265" t="n">
-        <v>9.359999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="E265" t="n">
-        <v>12.8</v>
+        <v>12.59</v>
       </c>
       <c r="F265" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="G265" t="inlineStr">
         <is>
@@ -7584,23 +7584,23 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B266" t="n">
         <v>2021</v>
       </c>
       <c r="C266" t="n">
-        <v>10.97</v>
+        <v>11.22</v>
       </c>
       <c r="D266" t="n">
-        <v>9.25</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="E266" t="n">
-        <v>12.78</v>
+        <v>12.97</v>
       </c>
       <c r="F266" t="n">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
@@ -7611,23 +7611,23 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B267" t="n">
         <v>2022</v>
       </c>
       <c r="C267" t="n">
-        <v>10.97</v>
+        <v>11.22</v>
       </c>
       <c r="D267" t="n">
-        <v>9.25</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="E267" t="n">
-        <v>12.78</v>
+        <v>12.97</v>
       </c>
       <c r="F267" t="n">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="G267" t="inlineStr">
         <is>
@@ -7638,23 +7638,23 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Reino Unido</t>
         </is>
       </c>
       <c r="B268" t="n">
         <v>2016</v>
       </c>
       <c r="C268" t="n">
-        <v>11.53</v>
+        <v>10.59</v>
       </c>
       <c r="D268" t="n">
-        <v>9.75</v>
+        <v>8.92</v>
       </c>
       <c r="E268" t="n">
-        <v>13.36</v>
+        <v>12.53</v>
       </c>
       <c r="F268" t="n">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
@@ -7665,23 +7665,23 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Reino Unido</t>
         </is>
       </c>
       <c r="B269" t="n">
         <v>2017</v>
       </c>
       <c r="C269" t="n">
-        <v>11</v>
+        <v>10.71</v>
       </c>
       <c r="D269" t="n">
-        <v>9.34</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="E269" t="n">
-        <v>12.82</v>
+        <v>12.42</v>
       </c>
       <c r="F269" t="n">
-        <v>3.48</v>
+        <v>3.37</v>
       </c>
       <c r="G269" t="inlineStr">
         <is>
@@ -7692,23 +7692,23 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Reino Unido</t>
         </is>
       </c>
       <c r="B270" t="n">
         <v>2018</v>
       </c>
       <c r="C270" t="n">
-        <v>11.15</v>
+        <v>10.77</v>
       </c>
       <c r="D270" t="n">
-        <v>9.4</v>
+        <v>9.09</v>
       </c>
       <c r="E270" t="n">
-        <v>13.02</v>
+        <v>12.51</v>
       </c>
       <c r="F270" t="n">
-        <v>3.62</v>
+        <v>3.41</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
@@ -7719,23 +7719,23 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Reino Unido</t>
         </is>
       </c>
       <c r="B271" t="n">
         <v>2019</v>
       </c>
       <c r="C271" t="n">
-        <v>11.08</v>
+        <v>10.74</v>
       </c>
       <c r="D271" t="n">
-        <v>9.43</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="E271" t="n">
-        <v>12.93</v>
+        <v>12.45</v>
       </c>
       <c r="F271" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="G271" t="inlineStr">
         <is>
@@ -7746,23 +7746,23 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Reino Unido</t>
         </is>
       </c>
       <c r="B272" t="n">
         <v>2020</v>
       </c>
       <c r="C272" t="n">
-        <v>11.29</v>
+        <v>10.79</v>
       </c>
       <c r="D272" t="n">
-        <v>9.56</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="E272" t="n">
-        <v>13.24</v>
+        <v>12.59</v>
       </c>
       <c r="F272" t="n">
-        <v>3.67</v>
+        <v>3.56</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -7773,23 +7773,23 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Reino Unido</t>
         </is>
       </c>
       <c r="B273" t="n">
         <v>2021</v>
       </c>
       <c r="C273" t="n">
-        <v>10.9</v>
+        <v>10.86</v>
       </c>
       <c r="D273" t="n">
-        <v>9.119999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E273" t="n">
-        <v>12.63</v>
+        <v>12.56</v>
       </c>
       <c r="F273" t="n">
-        <v>3.51</v>
+        <v>3.36</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -7800,23 +7800,23 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Reino Unido</t>
         </is>
       </c>
       <c r="B274" t="n">
         <v>2022</v>
       </c>
       <c r="C274" t="n">
-        <v>10.9</v>
+        <v>10.86</v>
       </c>
       <c r="D274" t="n">
-        <v>9.119999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E274" t="n">
-        <v>12.63</v>
+        <v>12.56</v>
       </c>
       <c r="F274" t="n">
-        <v>3.51</v>
+        <v>3.36</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -7827,23 +7827,23 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Rumanía</t>
         </is>
       </c>
       <c r="B275" t="n">
         <v>2016</v>
       </c>
       <c r="C275" t="n">
-        <v>11.36</v>
+        <v>16.89</v>
       </c>
       <c r="D275" t="n">
-        <v>9.69</v>
+        <v>14.33</v>
       </c>
       <c r="E275" t="n">
-        <v>13.16</v>
+        <v>19.51</v>
       </c>
       <c r="F275" t="n">
-        <v>3.47</v>
+        <v>5.18</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -7854,23 +7854,23 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Rumanía</t>
         </is>
       </c>
       <c r="B276" t="n">
         <v>2017</v>
       </c>
       <c r="C276" t="n">
-        <v>11.34</v>
+        <v>17.1</v>
       </c>
       <c r="D276" t="n">
-        <v>9.65</v>
+        <v>14.62</v>
       </c>
       <c r="E276" t="n">
-        <v>13.17</v>
+        <v>19.98</v>
       </c>
       <c r="F276" t="n">
-        <v>3.51</v>
+        <v>5.36</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -7881,23 +7881,23 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Rumanía</t>
         </is>
       </c>
       <c r="B277" t="n">
         <v>2018</v>
       </c>
       <c r="C277" t="n">
-        <v>11.27</v>
+        <v>17.22</v>
       </c>
       <c r="D277" t="n">
-        <v>9.56</v>
+        <v>14.72</v>
       </c>
       <c r="E277" t="n">
-        <v>13.27</v>
+        <v>19.81</v>
       </c>
       <c r="F277" t="n">
-        <v>3.71</v>
+        <v>5.09</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -7908,23 +7908,23 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Rumanía</t>
         </is>
       </c>
       <c r="B278" t="n">
         <v>2019</v>
       </c>
       <c r="C278" t="n">
-        <v>10.61</v>
+        <v>17.11</v>
       </c>
       <c r="D278" t="n">
-        <v>8.98</v>
+        <v>14.51</v>
       </c>
       <c r="E278" t="n">
-        <v>12.48</v>
+        <v>19.85</v>
       </c>
       <c r="F278" t="n">
-        <v>3.5</v>
+        <v>5.34</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -7935,23 +7935,23 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Rumanía</t>
         </is>
       </c>
       <c r="B279" t="n">
         <v>2020</v>
       </c>
       <c r="C279" t="n">
-        <v>10.66</v>
+        <v>17.09</v>
       </c>
       <c r="D279" t="n">
-        <v>8.92</v>
+        <v>14.33</v>
       </c>
       <c r="E279" t="n">
-        <v>12.37</v>
+        <v>19.57</v>
       </c>
       <c r="F279" t="n">
-        <v>3.44</v>
+        <v>5.24</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -7962,23 +7962,23 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Rumanía</t>
         </is>
       </c>
       <c r="B280" t="n">
         <v>2021</v>
       </c>
       <c r="C280" t="n">
-        <v>10.97</v>
+        <v>17.06</v>
       </c>
       <c r="D280" t="n">
-        <v>9.24</v>
+        <v>14.56</v>
       </c>
       <c r="E280" t="n">
-        <v>12.66</v>
+        <v>19.79</v>
       </c>
       <c r="F280" t="n">
-        <v>3.42</v>
+        <v>5.23</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -7989,23 +7989,23 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Rumanía</t>
         </is>
       </c>
       <c r="B281" t="n">
         <v>2022</v>
       </c>
       <c r="C281" t="n">
-        <v>10.97</v>
+        <v>17.06</v>
       </c>
       <c r="D281" t="n">
-        <v>9.24</v>
+        <v>14.56</v>
       </c>
       <c r="E281" t="n">
-        <v>12.66</v>
+        <v>19.79</v>
       </c>
       <c r="F281" t="n">
-        <v>3.42</v>
+        <v>5.23</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -8016,23 +8016,23 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="B282" t="n">
         <v>2016</v>
       </c>
       <c r="C282" t="n">
-        <v>9.449999999999999</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="D282" t="n">
-        <v>7.59</v>
+        <v>7.65</v>
       </c>
       <c r="E282" t="n">
-        <v>11.35</v>
+        <v>11.04</v>
       </c>
       <c r="F282" t="n">
-        <v>3.76</v>
+        <v>3.38</v>
       </c>
       <c r="G282" t="inlineStr">
         <is>
@@ -8043,23 +8043,23 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="B283" t="n">
         <v>2017</v>
       </c>
       <c r="C283" t="n">
-        <v>9.44</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="D283" t="n">
-        <v>7.59</v>
+        <v>7.81</v>
       </c>
       <c r="E283" t="n">
-        <v>11.34</v>
+        <v>11.11</v>
       </c>
       <c r="F283" t="n">
-        <v>3.75</v>
+        <v>3.29</v>
       </c>
       <c r="G283" t="inlineStr">
         <is>
@@ -8070,23 +8070,23 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="B284" t="n">
         <v>2018</v>
       </c>
       <c r="C284" t="n">
-        <v>9.390000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="D284" t="n">
-        <v>7.67</v>
+        <v>7.86</v>
       </c>
       <c r="E284" t="n">
-        <v>11.25</v>
+        <v>11.08</v>
       </c>
       <c r="F284" t="n">
-        <v>3.58</v>
+        <v>3.22</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
@@ -8097,23 +8097,23 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="B285" t="n">
         <v>2019</v>
       </c>
       <c r="C285" t="n">
-        <v>9.48</v>
+        <v>9.27</v>
       </c>
       <c r="D285" t="n">
-        <v>7.79</v>
+        <v>7.69</v>
       </c>
       <c r="E285" t="n">
-        <v>11.23</v>
+        <v>10.93</v>
       </c>
       <c r="F285" t="n">
-        <v>3.44</v>
+        <v>3.24</v>
       </c>
       <c r="G285" t="inlineStr">
         <is>
@@ -8124,23 +8124,23 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="B286" t="n">
         <v>2020</v>
       </c>
       <c r="C286" t="n">
-        <v>9.539999999999999</v>
+        <v>9.09</v>
       </c>
       <c r="D286" t="n">
-        <v>7.88</v>
+        <v>7.33</v>
       </c>
       <c r="E286" t="n">
-        <v>11.34</v>
+        <v>10.71</v>
       </c>
       <c r="F286" t="n">
-        <v>3.46</v>
+        <v>3.37</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
@@ -8151,23 +8151,23 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="B287" t="n">
         <v>2021</v>
       </c>
       <c r="C287" t="n">
-        <v>9.609999999999999</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="D287" t="n">
-        <v>7.78</v>
+        <v>7.39</v>
       </c>
       <c r="E287" t="n">
-        <v>11.39</v>
+        <v>10.75</v>
       </c>
       <c r="F287" t="n">
-        <v>3.61</v>
+        <v>3.36</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
@@ -8178,23 +8178,23 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="B288" t="n">
         <v>2022</v>
       </c>
       <c r="C288" t="n">
-        <v>9.609999999999999</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="D288" t="n">
-        <v>7.78</v>
+        <v>7.39</v>
       </c>
       <c r="E288" t="n">
-        <v>11.39</v>
+        <v>10.75</v>
       </c>
       <c r="F288" t="n">
-        <v>3.61</v>
+        <v>3.36</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
@@ -8205,23 +8205,23 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Suecia</t>
         </is>
       </c>
       <c r="B289" t="n">
         <v>2016</v>
       </c>
       <c r="C289" t="n">
-        <v>9.529999999999999</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="D289" t="n">
-        <v>7.81</v>
+        <v>7.59</v>
       </c>
       <c r="E289" t="n">
-        <v>11.19</v>
+        <v>11.35</v>
       </c>
       <c r="F289" t="n">
-        <v>3.38</v>
+        <v>3.76</v>
       </c>
       <c r="G289" t="inlineStr">
         <is>
@@ -8232,23 +8232,23 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Suecia</t>
         </is>
       </c>
       <c r="B290" t="n">
         <v>2017</v>
       </c>
       <c r="C290" t="n">
-        <v>9.34</v>
+        <v>9.44</v>
       </c>
       <c r="D290" t="n">
-        <v>7.71</v>
+        <v>7.59</v>
       </c>
       <c r="E290" t="n">
-        <v>10.96</v>
+        <v>11.34</v>
       </c>
       <c r="F290" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
@@ -8259,23 +8259,23 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Suecia</t>
         </is>
       </c>
       <c r="B291" t="n">
         <v>2018</v>
       </c>
       <c r="C291" t="n">
-        <v>9.289999999999999</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="D291" t="n">
-        <v>7.7</v>
+        <v>7.67</v>
       </c>
       <c r="E291" t="n">
-        <v>11.03</v>
+        <v>11.25</v>
       </c>
       <c r="F291" t="n">
-        <v>3.32</v>
+        <v>3.58</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
@@ -8286,23 +8286,23 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Suecia</t>
         </is>
       </c>
       <c r="B292" t="n">
         <v>2019</v>
       </c>
       <c r="C292" t="n">
-        <v>9.24</v>
+        <v>9.48</v>
       </c>
       <c r="D292" t="n">
-        <v>7.58</v>
+        <v>7.79</v>
       </c>
       <c r="E292" t="n">
-        <v>10.76</v>
+        <v>11.23</v>
       </c>
       <c r="F292" t="n">
-        <v>3.18</v>
+        <v>3.44</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
@@ -8313,23 +8313,23 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Suecia</t>
         </is>
       </c>
       <c r="B293" t="n">
         <v>2020</v>
       </c>
       <c r="C293" t="n">
-        <v>9.26</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="D293" t="n">
-        <v>7.8</v>
+        <v>7.88</v>
       </c>
       <c r="E293" t="n">
-        <v>10.91</v>
+        <v>11.34</v>
       </c>
       <c r="F293" t="n">
-        <v>3.11</v>
+        <v>3.46</v>
       </c>
       <c r="G293" t="inlineStr">
         <is>
@@ -8340,23 +8340,23 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Suecia</t>
         </is>
       </c>
       <c r="B294" t="n">
         <v>2021</v>
       </c>
       <c r="C294" t="n">
-        <v>9.16</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="D294" t="n">
-        <v>7.68</v>
+        <v>7.78</v>
       </c>
       <c r="E294" t="n">
-        <v>10.87</v>
+        <v>11.39</v>
       </c>
       <c r="F294" t="n">
-        <v>3.19</v>
+        <v>3.61</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
@@ -8367,23 +8367,23 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Suecia</t>
         </is>
       </c>
       <c r="B295" t="n">
         <v>2022</v>
       </c>
       <c r="C295" t="n">
-        <v>9.16</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="D295" t="n">
-        <v>7.68</v>
+        <v>7.78</v>
       </c>
       <c r="E295" t="n">
-        <v>10.87</v>
+        <v>11.39</v>
       </c>
       <c r="F295" t="n">
-        <v>3.19</v>
+        <v>3.61</v>
       </c>
       <c r="G295" t="inlineStr">
         <is>
@@ -8394,23 +8394,23 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Suiza</t>
         </is>
       </c>
       <c r="B296" t="n">
         <v>2016</v>
       </c>
       <c r="C296" t="n">
-        <v>2.09</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="D296" t="n">
-        <v>1.33</v>
+        <v>7.81</v>
       </c>
       <c r="E296" t="n">
-        <v>2.92</v>
+        <v>11.19</v>
       </c>
       <c r="F296" t="n">
-        <v>1.6</v>
+        <v>3.38</v>
       </c>
       <c r="G296" t="inlineStr">
         <is>
@@ -8421,23 +8421,23 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Suiza</t>
         </is>
       </c>
       <c r="B297" t="n">
         <v>2017</v>
       </c>
       <c r="C297" t="n">
-        <v>2.13</v>
+        <v>9.34</v>
       </c>
       <c r="D297" t="n">
-        <v>1.34</v>
+        <v>7.71</v>
       </c>
       <c r="E297" t="n">
-        <v>3</v>
+        <v>10.96</v>
       </c>
       <c r="F297" t="n">
-        <v>1.67</v>
+        <v>3.25</v>
       </c>
       <c r="G297" t="inlineStr">
         <is>
@@ -8448,23 +8448,23 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Suiza</t>
         </is>
       </c>
       <c r="B298" t="n">
         <v>2018</v>
       </c>
       <c r="C298" t="n">
-        <v>2.11</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="D298" t="n">
-        <v>1.34</v>
+        <v>7.7</v>
       </c>
       <c r="E298" t="n">
-        <v>3.03</v>
+        <v>11.03</v>
       </c>
       <c r="F298" t="n">
-        <v>1.69</v>
+        <v>3.32</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
@@ -8475,23 +8475,23 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Suiza</t>
         </is>
       </c>
       <c r="B299" t="n">
         <v>2019</v>
       </c>
       <c r="C299" t="n">
-        <v>2.07</v>
+        <v>9.24</v>
       </c>
       <c r="D299" t="n">
-        <v>1.31</v>
+        <v>7.58</v>
       </c>
       <c r="E299" t="n">
-        <v>2.97</v>
+        <v>10.76</v>
       </c>
       <c r="F299" t="n">
-        <v>1.65</v>
+        <v>3.18</v>
       </c>
       <c r="G299" t="inlineStr">
         <is>
@@ -8502,23 +8502,23 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Suiza</t>
         </is>
       </c>
       <c r="B300" t="n">
         <v>2020</v>
       </c>
       <c r="C300" t="n">
-        <v>2.08</v>
+        <v>9.26</v>
       </c>
       <c r="D300" t="n">
-        <v>1.29</v>
+        <v>7.8</v>
       </c>
       <c r="E300" t="n">
-        <v>3.05</v>
+        <v>10.91</v>
       </c>
       <c r="F300" t="n">
-        <v>1.76</v>
+        <v>3.11</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
@@ -8529,23 +8529,23 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Suiza</t>
         </is>
       </c>
       <c r="B301" t="n">
         <v>2021</v>
       </c>
       <c r="C301" t="n">
-        <v>2.2</v>
+        <v>9.16</v>
       </c>
       <c r="D301" t="n">
-        <v>1.4</v>
+        <v>7.68</v>
       </c>
       <c r="E301" t="n">
-        <v>3.09</v>
+        <v>10.87</v>
       </c>
       <c r="F301" t="n">
-        <v>1.68</v>
+        <v>3.19</v>
       </c>
       <c r="G301" t="inlineStr">
         <is>
@@ -8556,23 +8556,23 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Suiza</t>
         </is>
       </c>
       <c r="B302" t="n">
         <v>2022</v>
       </c>
       <c r="C302" t="n">
-        <v>2.2</v>
+        <v>9.16</v>
       </c>
       <c r="D302" t="n">
-        <v>1.4</v>
+        <v>7.68</v>
       </c>
       <c r="E302" t="n">
-        <v>3.09</v>
+        <v>10.87</v>
       </c>
       <c r="F302" t="n">
-        <v>1.68</v>
+        <v>3.19</v>
       </c>
       <c r="G302" t="inlineStr">
         <is>
@@ -8583,23 +8583,23 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Turquía</t>
         </is>
       </c>
       <c r="B303" t="n">
         <v>2016</v>
       </c>
       <c r="C303" t="n">
-        <v>8.99</v>
+        <v>2.09</v>
       </c>
       <c r="D303" t="n">
-        <v>7.3</v>
+        <v>1.33</v>
       </c>
       <c r="E303" t="n">
-        <v>10.89</v>
+        <v>2.92</v>
       </c>
       <c r="F303" t="n">
-        <v>3.59</v>
+        <v>1.6</v>
       </c>
       <c r="G303" t="inlineStr">
         <is>
@@ -8610,23 +8610,23 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Turquía</t>
         </is>
       </c>
       <c r="B304" t="n">
         <v>2017</v>
       </c>
       <c r="C304" t="n">
-        <v>8.76</v>
+        <v>2.13</v>
       </c>
       <c r="D304" t="n">
-        <v>6.96</v>
+        <v>1.34</v>
       </c>
       <c r="E304" t="n">
-        <v>10.58</v>
+        <v>3</v>
       </c>
       <c r="F304" t="n">
-        <v>3.62</v>
+        <v>1.67</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
@@ -8637,23 +8637,23 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Turquía</t>
         </is>
       </c>
       <c r="B305" t="n">
         <v>2018</v>
       </c>
       <c r="C305" t="n">
-        <v>8.74</v>
+        <v>2.11</v>
       </c>
       <c r="D305" t="n">
-        <v>6.77</v>
+        <v>1.34</v>
       </c>
       <c r="E305" t="n">
-        <v>10.53</v>
+        <v>3.03</v>
       </c>
       <c r="F305" t="n">
-        <v>3.76</v>
+        <v>1.69</v>
       </c>
       <c r="G305" t="inlineStr">
         <is>
@@ -8664,23 +8664,23 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Turquía</t>
         </is>
       </c>
       <c r="B306" t="n">
         <v>2019</v>
       </c>
       <c r="C306" t="n">
-        <v>8.99</v>
+        <v>2.07</v>
       </c>
       <c r="D306" t="n">
-        <v>7.21</v>
+        <v>1.31</v>
       </c>
       <c r="E306" t="n">
-        <v>10.83</v>
+        <v>2.97</v>
       </c>
       <c r="F306" t="n">
-        <v>3.62</v>
+        <v>1.65</v>
       </c>
       <c r="G306" t="inlineStr">
         <is>
@@ -8691,23 +8691,23 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Turquía</t>
         </is>
       </c>
       <c r="B307" t="n">
         <v>2020</v>
       </c>
       <c r="C307" t="n">
-        <v>8.44</v>
+        <v>2.08</v>
       </c>
       <c r="D307" t="n">
-        <v>6.63</v>
+        <v>1.29</v>
       </c>
       <c r="E307" t="n">
-        <v>10.18</v>
+        <v>3.05</v>
       </c>
       <c r="F307" t="n">
-        <v>3.54</v>
+        <v>1.76</v>
       </c>
       <c r="G307" t="inlineStr">
         <is>
@@ -8718,23 +8718,23 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Turquía</t>
         </is>
       </c>
       <c r="B308" t="n">
         <v>2021</v>
       </c>
       <c r="C308" t="n">
-        <v>7.43</v>
+        <v>2.2</v>
       </c>
       <c r="D308" t="n">
-        <v>5.69</v>
+        <v>1.4</v>
       </c>
       <c r="E308" t="n">
-        <v>9.109999999999999</v>
+        <v>3.09</v>
       </c>
       <c r="F308" t="n">
-        <v>3.42</v>
+        <v>1.68</v>
       </c>
       <c r="G308" t="inlineStr">
         <is>
@@ -8745,23 +8745,23 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Turquía</t>
         </is>
       </c>
       <c r="B309" t="n">
         <v>2022</v>
       </c>
       <c r="C309" t="n">
-        <v>7.43</v>
+        <v>2.2</v>
       </c>
       <c r="D309" t="n">
-        <v>5.69</v>
+        <v>1.4</v>
       </c>
       <c r="E309" t="n">
-        <v>9.109999999999999</v>
+        <v>3.09</v>
       </c>
       <c r="F309" t="n">
-        <v>3.42</v>
+        <v>1.68</v>
       </c>
       <c r="G309" t="inlineStr">
         <is>
@@ -8772,23 +8772,23 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Ucrania</t>
         </is>
       </c>
       <c r="B310" t="n">
         <v>2016</v>
       </c>
       <c r="C310" t="n">
-        <v>10.59</v>
+        <v>8.99</v>
       </c>
       <c r="D310" t="n">
-        <v>8.92</v>
+        <v>7.3</v>
       </c>
       <c r="E310" t="n">
-        <v>12.53</v>
+        <v>10.89</v>
       </c>
       <c r="F310" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="G310" t="inlineStr">
         <is>
@@ -8799,23 +8799,23 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Ucrania</t>
         </is>
       </c>
       <c r="B311" t="n">
         <v>2017</v>
       </c>
       <c r="C311" t="n">
-        <v>10.71</v>
+        <v>8.76</v>
       </c>
       <c r="D311" t="n">
-        <v>9.050000000000001</v>
+        <v>6.96</v>
       </c>
       <c r="E311" t="n">
-        <v>12.42</v>
+        <v>10.58</v>
       </c>
       <c r="F311" t="n">
-        <v>3.37</v>
+        <v>3.62</v>
       </c>
       <c r="G311" t="inlineStr">
         <is>
@@ -8826,23 +8826,23 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Ucrania</t>
         </is>
       </c>
       <c r="B312" t="n">
         <v>2018</v>
       </c>
       <c r="C312" t="n">
-        <v>10.77</v>
+        <v>8.74</v>
       </c>
       <c r="D312" t="n">
-        <v>9.09</v>
+        <v>6.77</v>
       </c>
       <c r="E312" t="n">
-        <v>12.51</v>
+        <v>10.53</v>
       </c>
       <c r="F312" t="n">
-        <v>3.41</v>
+        <v>3.76</v>
       </c>
       <c r="G312" t="inlineStr">
         <is>
@@ -8853,23 +8853,23 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Ucrania</t>
         </is>
       </c>
       <c r="B313" t="n">
         <v>2019</v>
       </c>
       <c r="C313" t="n">
-        <v>10.74</v>
+        <v>8.99</v>
       </c>
       <c r="D313" t="n">
-        <v>9.119999999999999</v>
+        <v>7.21</v>
       </c>
       <c r="E313" t="n">
-        <v>12.45</v>
+        <v>10.83</v>
       </c>
       <c r="F313" t="n">
-        <v>3.33</v>
+        <v>3.62</v>
       </c>
       <c r="G313" t="inlineStr">
         <is>
@@ -8880,23 +8880,23 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Ucrania</t>
         </is>
       </c>
       <c r="B314" t="n">
         <v>2020</v>
       </c>
       <c r="C314" t="n">
-        <v>10.79</v>
+        <v>8.44</v>
       </c>
       <c r="D314" t="n">
-        <v>9.029999999999999</v>
+        <v>6.63</v>
       </c>
       <c r="E314" t="n">
-        <v>12.59</v>
+        <v>10.18</v>
       </c>
       <c r="F314" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
@@ -8907,23 +8907,23 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Ucrania</t>
         </is>
       </c>
       <c r="B315" t="n">
         <v>2021</v>
       </c>
       <c r="C315" t="n">
-        <v>10.86</v>
+        <v>7.43</v>
       </c>
       <c r="D315" t="n">
-        <v>9.199999999999999</v>
+        <v>5.69</v>
       </c>
       <c r="E315" t="n">
-        <v>12.56</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="F315" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="G315" t="inlineStr">
         <is>
@@ -8934,23 +8934,23 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Ucrania</t>
         </is>
       </c>
       <c r="B316" t="n">
         <v>2022</v>
       </c>
       <c r="C316" t="n">
-        <v>10.86</v>
+        <v>7.43</v>
       </c>
       <c r="D316" t="n">
-        <v>9.199999999999999</v>
+        <v>5.69</v>
       </c>
       <c r="E316" t="n">
-        <v>12.56</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="F316" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="G316" t="inlineStr">
         <is>
